--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB70D57A-12DA-4020-A28A-A55205612796}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4F5BA2-7989-4F0D-925E-AB6AD2F2AD00}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="16" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -261,9 +261,6 @@
     <t>fieldInternalOrganization__c</t>
   </si>
   <si>
-    <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
-  </si>
-  <si>
     <t>Program__c</t>
   </si>
   <si>
@@ -280,13 +277,16 @@
   </si>
   <si>
     <t>Automation award for PR</t>
+  </si>
+  <si>
+    <t>Southside Community Criminal Justice Board</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,6 +303,13 @@
     <font>
       <sz val="9"/>
       <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -327,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -343,6 +350,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,14 +668,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -676,7 +686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -687,7 +697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -698,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -709,7 +719,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -729,13 +739,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -746,7 +756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -757,7 +767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -768,7 +778,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -779,7 +789,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -790,7 +800,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -801,7 +811,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -820,13 +830,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -837,7 +847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -848,7 +858,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -859,7 +869,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -870,7 +880,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -881,7 +891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -892,7 +902,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -903,37 +913,37 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I17" s="1"/>
       <c r="J17" s="2"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="6"/>
@@ -947,14 +957,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="158" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -965,7 +975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -976,7 +986,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -987,7 +997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -998,7 +1008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1009,7 +1019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1020,7 +1030,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1039,13 +1049,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1056,7 +1066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1067,7 +1077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1078,7 +1088,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1089,7 +1099,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,13 +1118,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1126,7 +1136,7 @@
       </c>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1134,11 +1144,11 @@
         <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1150,7 +1160,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1162,7 +1172,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,7 +1184,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1186,49 +1196,49 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1242,13 +1252,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1259,7 +1269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1270,7 +1280,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1281,7 +1291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1295,7 +1305,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1306,7 +1316,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1317,7 +1327,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1328,7 +1338,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1339,7 +1349,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1350,7 +1360,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1361,7 +1371,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1372,7 +1382,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1383,7 +1393,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1402,12 +1412,12 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1418,7 +1428,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1426,10 +1436,10 @@
         <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1440,7 +1450,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1451,7 +1461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1462,7 +1472,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1473,37 +1483,37 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1514,13 +1524,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1531,7 +1541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1539,10 +1549,10 @@
         <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1553,7 +1563,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1564,7 +1574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1575,7 +1585,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1586,55 +1596,56 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1645,7 +1656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1656,7 +1667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1667,7 +1678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1678,7 +1689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1689,7 +1700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1709,15 +1720,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1728,7 +1739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1739,7 +1750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1750,7 +1761,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1769,15 +1780,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1788,7 +1799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1799,7 +1810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1810,7 +1821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1829,15 +1840,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1848,7 +1859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1859,7 +1870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1870,7 +1881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1889,13 +1900,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1906,7 +1917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1917,7 +1928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1928,7 +1939,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1947,13 +1958,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1964,7 +1975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1975,7 +1986,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1986,7 +1997,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1997,7 +2008,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2008,7 +2019,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2019,7 +2030,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2039,13 +2050,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2056,7 +2067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2067,7 +2078,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -2078,7 +2089,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2089,7 +2100,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2100,7 +2111,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2111,7 +2122,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2130,13 +2141,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2147,7 +2158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2158,7 +2169,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -2169,7 +2180,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2180,7 +2191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2191,7 +2202,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2202,7 +2213,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB70D57A-12DA-4020-A28A-A55205612796}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96317787-37C9-421F-A0DC-043CD533A2BE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="16" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="9" activeTab="11" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -36,17 +36,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="82">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -102,12 +97,6 @@
     <t>the major changes in the organization’s capacity over the past year that have impacted or may impact the progress of the funded project, including changes</t>
   </si>
   <si>
-    <t>PatientPopulationTarget__c</t>
-  </si>
-  <si>
-    <t>NoOfPatientsServedInQuarter__c</t>
-  </si>
-  <si>
     <t>GoverningOrganizationReportDate__c</t>
   </si>
   <si>
@@ -280,6 +269,24 @@
   </si>
   <si>
     <t>Automation award for PR</t>
+  </si>
+  <si>
+    <t>fieldProjectNarrative__c</t>
+  </si>
+  <si>
+    <t>fieldOrganizationalCapacity__c</t>
+  </si>
+  <si>
+    <t>fieldPatientPopulationTarget__c</t>
+  </si>
+  <si>
+    <t>fieldNoOfPatientsServedInQuarter__c</t>
+  </si>
+  <si>
+    <t>fieldGoverningOrganizationReportDate__c</t>
+  </si>
+  <si>
+    <t>fieldBoardInformation__c</t>
   </si>
 </sst>
 </file>
@@ -751,10 +758,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -762,10 +769,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -773,10 +780,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -784,10 +791,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -795,10 +802,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -806,10 +813,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -842,10 +849,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -853,10 +860,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -864,10 +871,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -875,10 +882,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -886,10 +893,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -897,10 +904,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -970,7 +977,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>15</v>
@@ -981,7 +988,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>17</v>
@@ -992,7 +999,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="C4" s="4">
         <v>3</v>
@@ -1003,7 +1010,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
@@ -1014,7 +1021,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C6" s="4">
         <v>-2</v>
@@ -1025,10 +1032,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1083,7 +1090,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" s="4">
         <v>-2</v>
@@ -1094,10 +1101,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1131,10 +1138,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1"/>
     </row>
@@ -1143,10 +1150,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -1155,7 +1162,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1167,7 +1174,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1">
         <v>3650</v>
@@ -1179,10 +1186,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D6" s="1"/>
     </row>
@@ -1191,10 +1198,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -1203,10 +1210,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D8" s="1"/>
     </row>
@@ -1215,10 +1222,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D9" s="1"/>
     </row>
@@ -1264,10 +1271,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -1275,7 +1282,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -1286,13 +1293,13 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1300,10 +1307,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -1311,10 +1318,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -1322,10 +1329,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -1333,10 +1340,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1344,10 +1351,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -1355,10 +1362,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -1366,10 +1373,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -1377,10 +1384,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -1388,10 +1395,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1423,10 +1430,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1434,10 +1441,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1445,7 +1452,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1456,7 +1463,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1">
         <v>3650</v>
@@ -1467,10 +1474,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1478,10 +1485,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1489,10 +1496,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1500,10 +1507,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1536,10 +1543,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1547,10 +1554,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1558,7 +1565,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1569,7 +1576,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1">
         <v>3650</v>
@@ -1580,10 +1587,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1591,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1602,10 +1609,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1613,10 +1620,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1661,7 +1668,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -1969,10 +1976,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1980,10 +1987,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1991,10 +1998,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2002,10 +2009,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2013,10 +2020,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2024,10 +2031,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2061,10 +2068,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2072,10 +2079,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2083,10 +2090,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2094,10 +2101,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2105,10 +2112,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2116,10 +2123,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2152,10 +2159,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2163,10 +2170,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2174,10 +2181,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2185,10 +2192,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2196,10 +2203,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2207,10 +2214,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B29898-1937-483A-AD2F-AC155DB4E0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6561DB-EB7B-4F5A-A1F8-54680C334475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="10" activeTab="12" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="11" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -66,6 +66,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -73,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="311">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1000,6 +1006,12 @@
   </si>
   <si>
     <t>fieldSignatureofAuthorized__c</t>
+  </si>
+  <si>
+    <t>GoverningOrganizationReportDate__c</t>
+  </si>
+  <si>
+    <t>BoardInformation__c</t>
   </si>
 </sst>
 </file>
@@ -1126,9 +1138,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1166,7 +1178,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1272,7 +1284,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1414,7 +1426,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1423,11 +1435,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1494,7 +1506,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1585,7 +1597,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1694,10 +1706,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="158" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1761,7 +1773,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>75</v>
+        <v>309</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1772,7 +1784,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>76</v>
+        <v>310</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -1786,10 +1798,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C922EE-7D55-45ED-84C0-E643E295F423}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1866,10 +1878,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1935,10 +1947,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2048,9 +2060,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2208,10 +2220,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2321,10 +2333,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2434,10 +2446,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5CE5DD-3172-4B5D-9DF0-D4E246B7968A}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2746,10 +2758,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2828,9 +2840,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB2637BC-983B-4C46-AEC7-148BA71B263A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2864,10 +2876,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3109,7 +3121,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
@@ -3443,9 +3455,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785359D0-8BDB-4028-AD4B-2C0A4BB56435}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3505,7 +3517,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B546E08-B445-4CFC-AE7C-A360990A58B3}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
@@ -3574,10 +3586,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08315C1-DA1D-48F4-A0A8-4BB13DC3E452}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="125.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="125.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3688,10 +3700,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048DF57C-BB9A-45F0-8668-498DC1298DA0}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4000,10 +4012,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8693D5-27C5-4228-92A0-224F98BEF54A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4246,10 +4258,10 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702E2C7F-ACEF-451E-A257-8D7A1D64246B}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4580,10 +4592,10 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18586F6-6D9E-4DD3-97F2-036CA4FFCAFA}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4880,11 +4892,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4939,10 +4951,10 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5261,9 +5273,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5341,10 +5353,10 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5DAE-E2BF-47B3-A1C9-7C4F12E126E5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5421,10 +5433,10 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF0C752-B8E1-4378-AC7E-8304285A9B90}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5831,10 +5843,10 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E20211-1D84-48FF-8A84-AC0AE11DA487}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6164,10 +6176,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDEAA85-D896-403F-9A59-1E6EC90F5CC2}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6651,10 +6663,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3C73BB-4FB2-4E8F-8651-A6AF93AAD260}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7006,10 +7018,10 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7695C766-C8BF-4FC6-94BA-EF5703D41976}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7516,10 +7528,10 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89650214-A8DD-44FC-9DFA-301D63E80C53}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7640,10 +7652,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE9724B-3165-4EC7-A43C-010FD17B4AF6}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7996,11 +8008,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8055,10 +8067,10 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8465,10 +8477,10 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87CE4365-F4A6-44A6-8070-7113DA611997}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8589,10 +8601,10 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8857,10 +8869,10 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B75E61-DAA5-4C75-9938-082F14D489D1}">
   <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="40.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9421,10 +9433,10 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F13134-7D58-41D3-85C8-A2B7688C4794}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9798,11 +9810,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9857,9 +9869,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9915,7 +9927,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -9976,7 +9988,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" ht="15">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9987,7 +9999,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" ht="15">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -10007,7 +10019,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -10068,7 +10080,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" ht="15">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -10079,7 +10091,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" ht="15">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -10098,7 +10110,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6561DB-EB7B-4F5A-A1F8-54680C334475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CC172E-E146-406E-9D54-BE05044B363E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="11" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="7" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="313">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1012,6 +1012,12 @@
   </si>
   <si>
     <t>BoardInformation__c</t>
+  </si>
+  <si>
+    <t>CalReportingStartDate__c</t>
+  </si>
+  <si>
+    <t>CalReportingEndDate__c</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1027,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00;[Red]0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1072,6 +1078,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1093,7 +1105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1120,6 +1132,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1435,11 +1448,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1506,7 +1519,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1597,7 +1610,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1706,10 +1719,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="158" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1798,10 +1811,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C922EE-7D55-45ED-84C0-E643E295F423}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1878,10 +1891,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1947,10 +1960,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2060,9 +2073,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2220,10 +2233,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2333,10 +2346,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2446,10 +2459,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5CE5DD-3172-4B5D-9DF0-D4E246B7968A}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2758,10 +2771,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2840,9 +2853,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB2637BC-983B-4C46-AEC7-148BA71B263A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2876,10 +2889,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3121,7 +3134,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
@@ -3455,9 +3468,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785359D0-8BDB-4028-AD4B-2C0A4BB56435}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3517,7 +3530,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B546E08-B445-4CFC-AE7C-A360990A58B3}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
@@ -3586,10 +3599,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08315C1-DA1D-48F4-A0A8-4BB13DC3E452}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="125.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="125.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3700,10 +3713,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048DF57C-BB9A-45F0-8668-498DC1298DA0}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4012,10 +4025,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8693D5-27C5-4228-92A0-224F98BEF54A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4258,10 +4271,10 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702E2C7F-ACEF-451E-A257-8D7A1D64246B}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4592,10 +4605,10 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18586F6-6D9E-4DD3-97F2-036CA4FFCAFA}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4892,11 +4905,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4951,10 +4964,10 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5273,9 +5286,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5353,10 +5366,10 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5DAE-E2BF-47B3-A1C9-7C4F12E126E5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5433,10 +5446,10 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF0C752-B8E1-4378-AC7E-8304285A9B90}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5843,10 +5856,10 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E20211-1D84-48FF-8A84-AC0AE11DA487}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6176,10 +6189,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDEAA85-D896-403F-9A59-1E6EC90F5CC2}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="44.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6663,10 +6676,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3C73BB-4FB2-4E8F-8651-A6AF93AAD260}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7018,10 +7031,10 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7695C766-C8BF-4FC6-94BA-EF5703D41976}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7528,10 +7541,10 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89650214-A8DD-44FC-9DFA-301D63E80C53}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7652,10 +7665,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE9724B-3165-4EC7-A43C-010FD17B4AF6}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8008,11 +8021,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8067,10 +8080,10 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8477,10 +8490,10 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87CE4365-F4A6-44A6-8070-7113DA611997}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8601,10 +8614,10 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8869,10 +8882,10 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B75E61-DAA5-4C75-9938-082F14D489D1}">
   <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="40.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9433,10 +9446,10 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F13134-7D58-41D3-85C8-A2B7688C4794}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9810,11 +9823,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9869,9 +9882,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9927,7 +9940,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -9988,7 +10001,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9999,7 +10012,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -10019,7 +10032,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -10062,7 +10075,7 @@
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
@@ -10080,23 +10093,23 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>77</v>
+      <c r="B6" s="16" t="s">
+        <v>311</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>78</v>
+      <c r="B7" s="16" t="s">
+        <v>312</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>41</v>
@@ -10110,7 +10123,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CC172E-E146-406E-9D54-BE05044B363E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7396E0-B519-472B-B0C9-11B5BC692C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="7" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="16" activeTab="18" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="340">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -351,9 +351,6 @@
     <t>(i) Sale Proceeds OR</t>
   </si>
   <si>
-    <t>fieldSaleProceedsMarketValue__c</t>
-  </si>
-  <si>
     <t>fieldPercentageofFederalParticipation__c</t>
   </si>
   <si>
@@ -1018,6 +1015,90 @@
   </si>
   <si>
     <t>CalReportingEndDate__c</t>
+  </si>
+  <si>
+    <t>FederalGrantIdentifyingNumbe__c</t>
+  </si>
+  <si>
+    <t>RequestFederalAgencyDispositionInstr__c</t>
+  </si>
+  <si>
+    <t>Other__c</t>
+  </si>
+  <si>
+    <t>RequestApprovalSF428C__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> API Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Value</t>
+  </si>
+  <si>
+    <t>RequestApproval2SF428C__c</t>
+  </si>
+  <si>
+    <t>RequestUnconditionalTransferSF428C__c</t>
+  </si>
+  <si>
+    <t>RequestAcquiredEquipmentSF428C__c</t>
+  </si>
+  <si>
+    <t>RetentionAcquiredEquipmentSF428C__c</t>
+  </si>
+  <si>
+    <t>SaleAcquiredEquipmentSF428C__c</t>
+  </si>
+  <si>
+    <t>SaleProceedsrEstimateofCurrentFai__c</t>
+  </si>
+  <si>
+    <t>SaleProceedsMarketValue__c</t>
+  </si>
+  <si>
+    <t>PercentageofFederalParticipation__c</t>
+  </si>
+  <si>
+    <t>FederalShare__c</t>
+  </si>
+  <si>
+    <t>SellingandHandlingAllowance__c</t>
+  </si>
+  <si>
+    <t>ReportLoss__c</t>
+  </si>
+  <si>
+    <t>Comments__c</t>
+  </si>
+  <si>
+    <t>Agencyresponsetorequested__c</t>
+  </si>
+  <si>
+    <t>Agencyresponse__c</t>
+  </si>
+  <si>
+    <t>Disposeinaccordance__c</t>
+  </si>
+  <si>
+    <t>Disposeinaccordancewithattached__c</t>
+  </si>
+  <si>
+    <t>AORSignature__c</t>
+  </si>
+  <si>
+    <t>AcquisitionDateSF428A__c</t>
+  </si>
+  <si>
+    <t>Name428B__c</t>
+  </si>
+  <si>
+    <t>Telephone2__c</t>
+  </si>
+  <si>
+    <t>Title__c</t>
+  </si>
+  <si>
+    <t>EmailAddress__c</t>
   </si>
 </sst>
 </file>
@@ -1786,7 +1867,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1797,7 +1878,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -2470,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>316</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2481,7 +2562,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2492,7 +2573,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>313</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2503,7 +2584,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2514,7 +2595,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2525,7 +2606,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2536,7 +2617,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>319</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2547,7 +2628,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2558,7 +2639,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>321</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2569,7 +2650,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>322</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2580,7 +2661,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>323</v>
       </c>
       <c r="C11" t="s">
         <v>89</v>
@@ -2591,7 +2672,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>324</v>
       </c>
       <c r="C12" s="10">
         <v>9999.99</v>
@@ -2602,7 +2683,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>325</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -2613,7 +2694,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>326</v>
       </c>
       <c r="C14" s="10">
         <v>9999.99</v>
@@ -2624,7 +2705,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>327</v>
       </c>
       <c r="C15" s="10">
         <v>1000</v>
@@ -2635,7 +2716,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>328</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>5</v>
@@ -2646,10 +2727,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C17" t="s">
         <v>95</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2657,10 +2738,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
+        <v>330</v>
+      </c>
+      <c r="C18" t="s">
         <v>97</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2668,10 +2749,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>331</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2679,7 +2760,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>332</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>5</v>
@@ -2690,7 +2771,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>333</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>5</v>
@@ -2701,10 +2782,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
+        <v>334</v>
+      </c>
+      <c r="C22" t="s">
         <v>102</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2712,7 +2793,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>335</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2723,10 +2804,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>336</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2734,7 +2815,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>337</v>
       </c>
       <c r="C25">
         <v>8967045891</v>
@@ -2745,10 +2826,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>338</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2756,10 +2837,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
+        <v>339</v>
+      </c>
+      <c r="C27" t="s">
         <v>108</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3010,7 +3091,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>5</v>
@@ -3021,10 +3102,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" t="s">
         <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3032,10 +3113,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3043,7 +3124,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -3054,7 +3135,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -3065,10 +3146,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" t="s">
         <v>102</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3076,7 +3157,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3087,10 +3168,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3098,7 +3179,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C19">
         <v>8967045891</v>
@@ -3109,10 +3190,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3120,10 +3201,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
         <v>108</v>
-      </c>
-      <c r="C21" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3156,10 +3237,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3170,7 +3251,7 @@
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3178,10 +3259,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3189,10 +3270,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3200,7 +3281,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -3211,7 +3292,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -3222,7 +3303,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3233,10 +3314,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3244,7 +3325,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3255,10 +3336,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3266,10 +3347,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3277,10 +3358,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3288,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" t="s">
         <v>120</v>
-      </c>
-      <c r="C14" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3299,10 +3380,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" t="s">
         <v>122</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3310,10 +3391,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" t="s">
         <v>124</v>
-      </c>
-      <c r="C16" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3321,10 +3402,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" t="s">
         <v>126</v>
-      </c>
-      <c r="C17" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3332,10 +3413,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3343,7 +3424,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3354,10 +3435,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" t="s">
         <v>130</v>
-      </c>
-      <c r="C20" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3365,10 +3446,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" t="s">
         <v>132</v>
-      </c>
-      <c r="C21" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3376,10 +3457,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" t="s">
         <v>134</v>
-      </c>
-      <c r="C22" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3387,10 +3468,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" t="s">
         <v>136</v>
-      </c>
-      <c r="C23" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3398,10 +3479,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" t="s">
         <v>138</v>
-      </c>
-      <c r="C24" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3409,10 +3490,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" t="s">
         <v>140</v>
-      </c>
-      <c r="C25" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3420,10 +3501,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3431,7 +3512,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C27">
         <v>2122342342</v>
@@ -3442,10 +3523,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" t="s">
         <v>108</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3453,7 +3534,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3490,10 +3571,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3501,10 +3582,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3512,7 +3593,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="11">
         <v>50</v>
@@ -3563,7 +3644,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3574,7 +3655,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3585,7 +3666,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3621,10 +3702,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3632,10 +3713,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>156</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3643,10 +3724,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3654,10 +3735,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3665,7 +3746,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C6" s="3">
         <v>25</v>
@@ -3676,10 +3757,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3687,7 +3768,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C8" s="13">
         <v>9999.99</v>
@@ -3698,10 +3779,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3746,7 +3827,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3757,7 +3838,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3768,7 +3849,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3779,7 +3860,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -3790,10 +3871,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3801,7 +3882,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -3823,7 +3904,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -3856,7 +3937,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C13">
         <v>85</v>
@@ -3867,7 +3948,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14">
         <v>85</v>
@@ -3878,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15">
         <v>9999.99</v>
@@ -3889,7 +3970,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16">
         <v>9999.99</v>
@@ -3900,10 +3981,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
         <v>95</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3911,10 +3992,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
         <v>97</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3922,10 +4003,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3933,7 +4014,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -3944,7 +4025,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -3955,10 +4036,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3966,7 +4047,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3977,10 +4058,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3988,7 +4069,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C25">
         <v>9867589302</v>
@@ -3999,10 +4080,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4010,10 +4091,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -4058,7 +4139,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -4069,7 +4150,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4080,7 +4161,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4091,7 +4172,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -4102,7 +4183,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -4124,7 +4205,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -4146,10 +4227,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" t="s">
         <v>95</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4157,10 +4238,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" t="s">
         <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4168,10 +4249,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4179,7 +4260,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4190,7 +4271,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4201,10 +4282,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4212,7 +4293,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -4223,10 +4304,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4234,7 +4315,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19">
         <v>9867589302</v>
@@ -4245,10 +4326,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4256,10 +4337,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -4293,10 +4374,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4304,7 +4385,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4315,10 +4396,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4326,7 +4407,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4337,10 +4418,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4348,10 +4429,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4359,10 +4440,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4370,10 +4451,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" t="s">
         <v>120</v>
-      </c>
-      <c r="C9" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4381,10 +4462,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" t="s">
         <v>122</v>
-      </c>
-      <c r="C10" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4392,10 +4473,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" t="s">
         <v>124</v>
-      </c>
-      <c r="C11" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4403,10 +4484,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" t="s">
         <v>126</v>
-      </c>
-      <c r="C12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4414,7 +4495,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4425,7 +4506,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4436,7 +4517,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4447,7 +4528,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -4458,7 +4539,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
@@ -4469,10 +4550,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4480,10 +4561,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" t="s">
         <v>130</v>
-      </c>
-      <c r="C19" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4491,10 +4572,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" t="s">
         <v>132</v>
-      </c>
-      <c r="C20" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4502,10 +4583,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" t="s">
         <v>134</v>
-      </c>
-      <c r="C21" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4513,10 +4594,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" t="s">
         <v>136</v>
-      </c>
-      <c r="C22" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4524,10 +4605,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" t="s">
         <v>138</v>
-      </c>
-      <c r="C23" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4535,10 +4616,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" t="s">
         <v>140</v>
-      </c>
-      <c r="C24" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4546,10 +4627,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4557,7 +4638,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C26">
         <v>2122342342</v>
@@ -4568,10 +4649,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" t="s">
         <v>108</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4579,7 +4660,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4590,10 +4671,10 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -4627,10 +4708,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4638,7 +4719,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4649,10 +4730,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4660,7 +4741,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4671,10 +4752,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4682,10 +4763,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4693,10 +4774,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4704,10 +4785,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" t="s">
         <v>120</v>
-      </c>
-      <c r="C9" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4715,10 +4796,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" t="s">
         <v>122</v>
-      </c>
-      <c r="C10" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4726,10 +4807,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" t="s">
         <v>124</v>
-      </c>
-      <c r="C11" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4737,10 +4818,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" t="s">
         <v>126</v>
-      </c>
-      <c r="C12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4748,7 +4829,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4759,7 +4840,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
@@ -4770,10 +4851,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4781,10 +4862,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" t="s">
         <v>130</v>
-      </c>
-      <c r="C16" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4792,10 +4873,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" t="s">
         <v>132</v>
-      </c>
-      <c r="C17" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4803,10 +4884,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" t="s">
         <v>134</v>
-      </c>
-      <c r="C18" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4814,10 +4895,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" t="s">
         <v>136</v>
-      </c>
-      <c r="C19" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4825,10 +4906,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" t="s">
         <v>138</v>
-      </c>
-      <c r="C20" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4836,10 +4917,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" t="s">
         <v>140</v>
-      </c>
-      <c r="C21" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4847,10 +4928,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4858,7 +4939,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C23">
         <v>2122342342</v>
@@ -4869,10 +4950,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s">
         <v>108</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4880,7 +4961,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -4891,10 +4972,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -4986,10 +5067,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4997,7 +5078,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -5008,10 +5089,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5019,7 +5100,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5030,10 +5111,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5041,10 +5122,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5052,10 +5133,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5063,10 +5144,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" t="s">
         <v>120</v>
-      </c>
-      <c r="C9" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5074,10 +5155,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" t="s">
         <v>122</v>
-      </c>
-      <c r="C10" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5085,10 +5166,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" t="s">
         <v>124</v>
-      </c>
-      <c r="C11" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5096,10 +5177,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" t="s">
         <v>126</v>
-      </c>
-      <c r="C12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5107,7 +5188,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -5118,7 +5199,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -5129,7 +5210,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -5140,7 +5221,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -5151,10 +5232,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5162,10 +5243,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" t="s">
         <v>130</v>
-      </c>
-      <c r="C18" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5173,10 +5254,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" t="s">
         <v>132</v>
-      </c>
-      <c r="C19" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5184,10 +5265,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" t="s">
         <v>134</v>
-      </c>
-      <c r="C20" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5195,10 +5276,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" t="s">
         <v>136</v>
-      </c>
-      <c r="C21" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5206,10 +5287,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" t="s">
         <v>138</v>
-      </c>
-      <c r="C22" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5217,10 +5298,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" t="s">
         <v>140</v>
-      </c>
-      <c r="C23" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5228,10 +5309,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5239,7 +5320,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C25">
         <v>2122342342</v>
@@ -5250,10 +5331,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
         <v>108</v>
-      </c>
-      <c r="C26" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5261,7 +5342,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5272,10 +5353,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -5308,7 +5389,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -5319,10 +5400,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>186</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5330,10 +5411,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5341,7 +5422,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C5">
         <v>1111</v>
@@ -5352,10 +5433,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -5388,10 +5469,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5399,10 +5480,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5410,7 +5491,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C4">
         <v>76578</v>
@@ -5421,7 +5502,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -5432,7 +5513,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -5468,10 +5549,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5479,7 +5560,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5490,10 +5571,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5501,7 +5582,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5512,10 +5593,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5523,10 +5604,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5534,10 +5615,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5545,10 +5626,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5556,10 +5637,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>122</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5567,10 +5648,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5578,10 +5659,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5589,10 +5670,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5600,10 +5681,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" t="s">
         <v>132</v>
-      </c>
-      <c r="C14" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5611,10 +5692,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5622,10 +5703,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>136</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5633,10 +5714,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>138</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5644,10 +5725,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>108</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5655,7 +5736,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -5666,7 +5747,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C20">
         <v>150</v>
@@ -5677,7 +5758,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
@@ -5688,7 +5769,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
@@ -5699,7 +5780,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -5710,10 +5791,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5721,7 +5802,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -5732,10 +5813,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5743,10 +5824,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5754,10 +5835,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5765,10 +5846,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5776,10 +5857,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5787,10 +5868,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5798,10 +5879,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5809,7 +5890,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C33" s="15">
         <v>2122342342</v>
@@ -5820,10 +5901,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5831,7 +5912,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5842,7 +5923,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -5878,10 +5959,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5889,7 +5970,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5900,10 +5981,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5911,7 +5992,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5922,10 +6003,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5933,10 +6014,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5944,10 +6025,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5955,10 +6036,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5966,10 +6047,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>122</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5977,10 +6058,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5988,10 +6069,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5999,10 +6080,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6010,10 +6091,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" t="s">
         <v>132</v>
-      </c>
-      <c r="C14" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6021,10 +6102,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6032,10 +6113,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>136</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6043,10 +6124,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>138</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6054,10 +6135,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>108</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6065,7 +6146,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -6076,10 +6157,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6087,10 +6168,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6098,10 +6179,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6109,10 +6190,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6120,10 +6201,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6131,10 +6212,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6142,10 +6223,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6153,7 +6234,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C27" s="15">
         <v>2122342342</v>
@@ -6164,10 +6245,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6175,7 +6256,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6211,7 +6292,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6222,7 +6303,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -6233,7 +6314,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -6244,10 +6325,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>210</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6255,10 +6336,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6266,7 +6347,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7">
         <v>123</v>
@@ -6277,10 +6358,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6288,10 +6369,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6299,10 +6380,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6310,10 +6391,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6321,10 +6402,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6332,10 +6413,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6343,10 +6424,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6354,7 +6435,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C15">
         <v>1234</v>
@@ -6365,7 +6446,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C16">
         <v>48</v>
@@ -6376,7 +6457,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C17">
         <v>35</v>
@@ -6387,7 +6468,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -6398,10 +6479,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>218</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6409,7 +6490,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -6420,7 +6501,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6431,10 +6512,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>222</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6442,7 +6523,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -6453,7 +6534,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C24">
         <v>789</v>
@@ -6464,7 +6545,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -6475,7 +6556,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C26">
         <v>456</v>
@@ -6486,7 +6567,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -6497,10 +6578,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6508,7 +6589,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C29" t="s">
         <v>51</v>
@@ -6519,7 +6600,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C30" t="s">
         <v>51</v>
@@ -6530,7 +6611,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C31" t="s">
         <v>51</v>
@@ -6541,7 +6622,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -6552,10 +6633,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6563,7 +6644,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C34" t="s">
         <v>45</v>
@@ -6574,10 +6655,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6585,10 +6666,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C36" s="11" t="s">
         <v>236</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6596,7 +6677,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C37">
         <v>10000</v>
@@ -6607,7 +6688,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C38">
         <v>8000</v>
@@ -6618,7 +6699,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C39">
         <v>6000</v>
@@ -6629,7 +6710,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -6640,7 +6721,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C41">
         <v>300</v>
@@ -6651,7 +6732,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -6662,10 +6743,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -6698,7 +6779,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6709,7 +6790,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -6720,10 +6801,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6731,10 +6812,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6742,10 +6823,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6753,10 +6834,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6764,10 +6845,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6775,10 +6856,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6786,7 +6867,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="12">
         <v>1234</v>
@@ -6797,7 +6878,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C11">
         <v>-8</v>
@@ -6808,7 +6889,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C12">
         <v>-300</v>
@@ -6819,7 +6900,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C13">
         <v>-200</v>
@@ -6830,7 +6911,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -6841,7 +6922,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15">
         <v>-818</v>
@@ -6852,7 +6933,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C16">
         <v>-8</v>
@@ -6863,7 +6944,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C17">
         <v>-767</v>
@@ -6874,7 +6955,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -6885,7 +6966,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>45</v>
@@ -6896,7 +6977,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -6907,7 +6988,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -6918,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -6929,10 +7010,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>236</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6940,7 +7021,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C24">
         <v>-1000</v>
@@ -6951,7 +7032,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C25">
         <v>-700</v>
@@ -6962,7 +7043,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C26">
         <v>-500</v>
@@ -6973,7 +7054,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C27">
         <v>-300</v>
@@ -6984,7 +7065,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -6995,7 +7076,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C29">
         <v>-150</v>
@@ -7006,7 +7087,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -7017,7 +7098,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C31">
         <v>-40</v>
@@ -7064,10 +7145,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7075,7 +7156,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7086,10 +7167,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7097,10 +7178,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7108,10 +7189,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7119,10 +7200,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7130,10 +7211,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7141,10 +7222,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7152,10 +7233,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7163,7 +7244,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -7174,7 +7255,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -7185,7 +7266,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -7196,10 +7277,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7207,7 +7288,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -7218,7 +7299,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -7229,7 +7310,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -7240,10 +7321,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7251,7 +7332,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -7262,7 +7343,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -7273,10 +7354,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7284,7 +7365,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C23">
         <v>789</v>
@@ -7295,7 +7376,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C24">
         <v>86</v>
@@ -7306,7 +7387,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C25">
         <v>456</v>
@@ -7317,7 +7398,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C26">
         <v>74</v>
@@ -7328,7 +7409,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
@@ -7339,7 +7420,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -7350,10 +7431,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7361,7 +7442,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -7372,10 +7453,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7405,7 +7486,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -7416,7 +7497,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -7427,7 +7508,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -7438,7 +7519,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -7449,7 +7530,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7460,7 +7541,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -7471,7 +7552,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -7482,10 +7563,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C41" t="s">
         <v>254</v>
-      </c>
-      <c r="C41" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7493,7 +7574,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C42">
         <v>400</v>
@@ -7504,7 +7585,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7515,7 +7596,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -7526,10 +7607,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" t="s">
         <v>95</v>
-      </c>
-      <c r="C45" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -7574,7 +7655,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -7585,10 +7666,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7596,10 +7677,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7607,10 +7688,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7618,10 +7699,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7629,10 +7710,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7640,10 +7721,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7651,10 +7732,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -7698,10 +7779,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7709,7 +7790,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7720,10 +7801,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7731,10 +7812,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7742,10 +7823,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7753,10 +7834,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7764,10 +7845,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7775,10 +7856,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7786,7 +7867,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="12">
         <v>1234</v>
@@ -7797,7 +7878,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -7808,7 +7889,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C13">
         <v>-466</v>
@@ -7819,7 +7900,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C14">
         <v>-500</v>
@@ -7830,7 +7911,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C15">
         <v>-400</v>
@@ -7841,7 +7922,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16">
         <v>-789</v>
@@ -7852,7 +7933,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C17">
         <v>-200</v>
@@ -7863,7 +7944,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C18">
         <v>-456</v>
@@ -7874,7 +7955,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C19">
         <v>-74</v>
@@ -7885,7 +7966,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -7896,7 +7977,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -7907,7 +7988,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C22">
         <v>-400</v>
@@ -7918,7 +7999,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C23">
         <v>-200</v>
@@ -7929,7 +8010,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C24">
         <v>-100</v>
@@ -7940,7 +8021,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C25">
         <v>-200</v>
@@ -7951,7 +8032,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C26">
         <v>-50</v>
@@ -7962,7 +8043,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C27">
         <v>-400</v>
@@ -7973,7 +8054,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C28">
         <v>-200</v>
@@ -7984,7 +8065,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C29">
         <v>-100</v>
@@ -7995,7 +8076,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C30">
         <v>-200</v>
@@ -8006,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -8102,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8113,10 +8194,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" t="s">
         <v>261</v>
-      </c>
-      <c r="C3" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8124,7 +8205,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -8135,10 +8216,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8146,10 +8227,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8157,10 +8238,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8168,10 +8249,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8179,10 +8260,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8190,10 +8271,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8201,10 +8282,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8212,7 +8293,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -8223,7 +8304,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -8234,7 +8315,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -8245,7 +8326,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C15">
         <v>500</v>
@@ -8256,10 +8337,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8267,7 +8348,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C17">
         <v>1000</v>
@@ -8278,7 +8359,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C18">
         <v>700</v>
@@ -8289,10 +8370,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8300,10 +8381,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>263</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8311,7 +8392,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C21">
         <v>1234</v>
@@ -8322,10 +8403,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8333,10 +8414,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8344,10 +8425,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8355,7 +8436,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C25">
         <v>300</v>
@@ -8366,7 +8447,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C26">
         <v>85</v>
@@ -8377,7 +8458,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -8388,7 +8469,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C28">
         <v>76</v>
@@ -8399,7 +8480,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>45</v>
@@ -8410,7 +8491,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>45</v>
@@ -8421,10 +8502,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8432,7 +8513,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>45</v>
@@ -8443,10 +8524,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8454,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>26</v>
@@ -8465,7 +8546,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>26</v>
@@ -8476,7 +8557,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>26</v>
@@ -8512,7 +8593,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8523,7 +8604,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -8534,10 +8615,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8545,10 +8626,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8556,10 +8637,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8567,10 +8648,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8578,10 +8659,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8589,10 +8670,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8600,10 +8681,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -8636,7 +8717,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C2" s="3">
         <v>1234</v>
@@ -8647,7 +8728,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3">
         <v>123</v>
@@ -8658,10 +8739,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8669,10 +8750,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8680,10 +8761,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8691,10 +8772,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>120</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8702,10 +8783,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8713,10 +8794,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>124</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8724,7 +8805,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="15">
         <v>12345</v>
@@ -8735,7 +8816,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C11" s="3">
         <v>-500</v>
@@ -8746,7 +8827,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C12" s="3">
         <v>-1000</v>
@@ -8757,7 +8838,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C13" s="3">
         <v>-700</v>
@@ -8768,7 +8849,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" s="3">
         <v>-300</v>
@@ -8779,7 +8860,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C15" s="3">
         <v>-85</v>
@@ -8790,7 +8871,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C16" s="3">
         <v>-200</v>
@@ -8801,7 +8882,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C17" s="3">
         <v>-76</v>
@@ -8812,7 +8893,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>45</v>
@@ -8823,7 +8904,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>45</v>
@@ -8834,10 +8915,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8845,10 +8926,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8856,10 +8937,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8867,10 +8948,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -8893,7 +8974,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8904,10 +8985,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8915,10 +8996,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8926,10 +9007,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8937,7 +9018,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C5" s="3">
         <v>1234</v>
@@ -8948,7 +9029,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C6" s="3">
         <v>8967589</v>
@@ -8959,7 +9040,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C7" s="3">
         <v>34567</v>
@@ -8970,7 +9051,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C8" s="3">
         <v>50</v>
@@ -8981,7 +9062,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C9" s="3">
         <v>100</v>
@@ -8992,10 +9073,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9003,7 +9084,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
@@ -9014,10 +9095,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9025,10 +9106,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9036,10 +9117,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9047,10 +9128,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9058,10 +9139,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9069,10 +9150,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9080,10 +9161,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9091,7 +9172,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C19" s="3">
         <v>123</v>
@@ -9102,10 +9183,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9113,10 +9194,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9124,10 +9205,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9135,10 +9216,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9146,10 +9227,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9157,10 +9238,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9168,10 +9249,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9179,10 +9260,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9190,10 +9271,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9201,7 +9282,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C29" s="3">
         <v>75</v>
@@ -9212,7 +9293,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
@@ -9223,7 +9304,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C31" s="3">
         <v>85</v>
@@ -9234,7 +9315,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C32" s="3">
         <v>55</v>
@@ -9245,7 +9326,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>5</v>
@@ -9256,10 +9337,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9267,7 +9348,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -9278,10 +9359,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9289,10 +9370,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9300,10 +9381,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9311,10 +9392,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9322,10 +9403,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9333,10 +9414,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9344,7 +9425,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C42" s="3">
         <v>9869875890</v>
@@ -9355,10 +9436,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9366,7 +9447,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C44" s="3">
         <v>20</v>
@@ -9377,10 +9458,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9388,10 +9469,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9399,10 +9480,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9410,10 +9491,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9421,10 +9502,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9432,7 +9513,7 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C50" s="3">
         <v>9869875890</v>
@@ -9457,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9468,10 +9549,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9479,10 +9560,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9490,10 +9571,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9501,7 +9582,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C5" s="3">
         <v>50</v>
@@ -9512,7 +9593,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C6" s="3">
         <v>100</v>
@@ -9523,10 +9604,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9534,7 +9615,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" s="3">
         <v>123</v>
@@ -9545,10 +9626,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9556,10 +9637,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9567,10 +9648,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9578,10 +9659,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9589,10 +9670,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9600,7 +9681,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C14" s="3">
         <v>12345</v>
@@ -9611,10 +9692,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9622,7 +9703,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C16" s="3">
         <v>123</v>
@@ -9633,10 +9714,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9644,10 +9725,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9655,10 +9736,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9666,10 +9747,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9677,10 +9758,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9688,7 +9769,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C22" s="3">
         <v>12345</v>
@@ -9699,10 +9780,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9710,10 +9791,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9721,10 +9802,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9732,7 +9813,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C26" s="3">
         <v>-75</v>
@@ -9743,7 +9824,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C27" s="3">
         <v>-65</v>
@@ -9754,7 +9835,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C28" s="3">
         <v>-85</v>
@@ -9765,7 +9846,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C29" s="3">
         <v>-55</v>
@@ -9776,10 +9857,10 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9787,7 +9868,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -9798,10 +9879,10 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9809,7 +9890,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C33" s="3">
         <v>20</v>
@@ -10098,7 +10179,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>42</v>
@@ -10109,7 +10190,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>41</v>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7396E0-B519-472B-B0C9-11B5BC692C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB208F1D-0131-47FD-A8A7-2FADFC42E67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="16" activeTab="18" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="21" activeTab="23" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="354">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -324,84 +324,30 @@
     <t>fieldRequestFederalAgencyDispositionInstr__c</t>
   </si>
   <si>
-    <t>fieldOther__c</t>
-  </si>
-  <si>
-    <t>fieldRequestApprovalSF428C__c</t>
-  </si>
-  <si>
-    <t>fieldRequestApproval2SF428C__c</t>
-  </si>
-  <si>
-    <t>fieldRequestUnconditionalTransferSF428C__c</t>
-  </si>
-  <si>
-    <t>fieldRequestAcquiredEquipmentSF428C__c</t>
-  </si>
-  <si>
-    <t>fieldRetentionAcquiredEquipmentSF428C__c</t>
-  </si>
-  <si>
-    <t>fieldSaleAcquiredEquipmentSF428C__c</t>
-  </si>
-  <si>
-    <t>fieldSaleProceedsrEstimateofCurrentFai__c</t>
-  </si>
-  <si>
     <t>(i) Sale Proceeds OR</t>
   </si>
   <si>
-    <t>fieldPercentageofFederalParticipation__c</t>
-  </si>
-  <si>
     <t>fieldFederalShare__c</t>
   </si>
   <si>
-    <t>fieldSellingandHandlingAllowance__c</t>
-  </si>
-  <si>
-    <t>fieldReportLoss__c</t>
-  </si>
-  <si>
     <t>fieldComments__c</t>
   </si>
   <si>
     <t>Automation Test</t>
   </si>
   <si>
-    <t>fieldAgencyresponsetorequested__c</t>
-  </si>
-  <si>
     <t>(i) Recipient request approved</t>
   </si>
   <si>
-    <t>fieldAgencyresponse__c</t>
-  </si>
-  <si>
-    <t>fieldDisposeinaccordance__c</t>
-  </si>
-  <si>
-    <t>fieldDisposeinaccordancewithattached__c</t>
-  </si>
-  <si>
-    <t>fieldAORSignature__c</t>
-  </si>
-  <si>
     <t>John Mathews</t>
   </si>
   <si>
     <t>fieldAcquisitionDateSF428A__c</t>
   </si>
   <si>
-    <t>fieldName428B__c</t>
-  </si>
-  <si>
     <t>fieldTelephone2__c</t>
   </si>
   <si>
-    <t>fieldTitle__c</t>
-  </si>
-  <si>
     <t>fieldEmailAddress__c</t>
   </si>
   <si>
@@ -531,9 +477,6 @@
     <t>fieldFederalAgencyandOrganizationalSF429__c</t>
   </si>
   <si>
-    <t>fieldDate__c</t>
-  </si>
-  <si>
     <t>fieldAnnualReportSF428A__c</t>
   </si>
   <si>
@@ -543,30 +486,9 @@
     <t>fieldDispositionReportRequestSF428C__c</t>
   </si>
   <si>
-    <t>fieldFederalAwardNumber__c</t>
-  </si>
-  <si>
-    <t>fieldGPACQ__c</t>
-  </si>
-  <si>
     <t>ACQ</t>
   </si>
   <si>
-    <t>fieldDescription__c</t>
-  </si>
-  <si>
-    <t>fieldIdentificationNumber__c</t>
-  </si>
-  <si>
-    <t>fieldConditionCode__c</t>
-  </si>
-  <si>
-    <t>fieldAcquisitionCost__c</t>
-  </si>
-  <si>
-    <t>fieldDispositionRequest__c</t>
-  </si>
-  <si>
     <t>eulkelendwdrgyethmgfmewoi</t>
   </si>
   <si>
@@ -579,30 +501,15 @@
     <t>gefakzgrpvjjbdneasuz</t>
   </si>
   <si>
-    <t>fieldFederallyownedProperty__c</t>
-  </si>
-  <si>
-    <t>fieldAcquiredEquipment__c</t>
-  </si>
-  <si>
-    <t>fieldResidualUnusedSupplies__c</t>
-  </si>
-  <si>
     <t>fieldRequestTransfertoAward__c</t>
   </si>
   <si>
     <t>fieldFederalAwardIdentifier__c</t>
   </si>
   <si>
-    <t>fieldRequestFederalAgency__c</t>
-  </si>
-  <si>
     <t>fieldAcknowledgeEquipment__c</t>
   </si>
   <si>
-    <t>fieldTotalAmount__c</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
@@ -636,27 +543,9 @@
     <t>fieldFederalGrantSF428A__c</t>
   </si>
   <si>
-    <t>fieldReportTypePiclikist__c</t>
-  </si>
-  <si>
     <t>(a) Individual (Reporting Federally-owned property for one award)</t>
   </si>
   <si>
-    <t>fieldReportAsOf__c</t>
-  </si>
-  <si>
-    <t>fieldSEP30__c</t>
-  </si>
-  <si>
-    <t>fieldName</t>
-  </si>
-  <si>
-    <t>fieldIdentification__c</t>
-  </si>
-  <si>
-    <t>fieldAcquisitionDate__c</t>
-  </si>
-  <si>
     <t>30 SEP</t>
   </si>
   <si>
@@ -1099,6 +988,159 @@
   </si>
   <si>
     <t>EmailAddress__c</t>
+  </si>
+  <si>
+    <t>FederalAwardNumber__c</t>
+  </si>
+  <si>
+    <t>GPACQ__c</t>
+  </si>
+  <si>
+    <t>IdentificationNumber__c</t>
+  </si>
+  <si>
+    <t>AcquiredDate__c</t>
+  </si>
+  <si>
+    <t>ConditionCode__c</t>
+  </si>
+  <si>
+    <t>AcquisitionCost__c</t>
+  </si>
+  <si>
+    <t>DispositionRequest__c</t>
+  </si>
+  <si>
+    <t>FederallyownedProperty__c</t>
+  </si>
+  <si>
+    <t>AcquiredEquipment__c</t>
+  </si>
+  <si>
+    <t>ResidualUnusedSupplies__c</t>
+  </si>
+  <si>
+    <t>RequestTransfertoAward__c</t>
+  </si>
+  <si>
+    <t>RequestFederalAgency__c</t>
+  </si>
+  <si>
+    <t>AcknowledgeEquipment__c</t>
+  </si>
+  <si>
+    <t>Telephone__c</t>
+  </si>
+  <si>
+    <t>FederalAwardIdentifier__c</t>
+  </si>
+  <si>
+    <t>TotalAmount__c</t>
+  </si>
+  <si>
+    <t>FederalGrantSF428A__c</t>
+  </si>
+  <si>
+    <t>ReportTypePiclikist__c</t>
+  </si>
+  <si>
+    <t>ReportAsOf__c</t>
+  </si>
+  <si>
+    <t>SEP30__c</t>
+  </si>
+  <si>
+    <t>CommentsSF428__c</t>
+  </si>
+  <si>
+    <t>FederalAgencySF428__c</t>
+  </si>
+  <si>
+    <t>FederalGrantIdentifyingNumberSF428__c</t>
+  </si>
+  <si>
+    <t>RecipientOrganizationNameSF428__c</t>
+  </si>
+  <si>
+    <t>Street1SF428__c</t>
+  </si>
+  <si>
+    <t>Street2SF428__c</t>
+  </si>
+  <si>
+    <t>CitySF428__c</t>
+  </si>
+  <si>
+    <t>CountySF428__c</t>
+  </si>
+  <si>
+    <t>StateSf428__c</t>
+  </si>
+  <si>
+    <t>ProvinceSF428__c</t>
+  </si>
+  <si>
+    <t>CountrySF428__c</t>
+  </si>
+  <si>
+    <t>ZipPostalCodeSF428__c</t>
+  </si>
+  <si>
+    <t>RecipientAccountNumberSF428__c</t>
+  </si>
+  <si>
+    <t>AnnualReportSF428A__c</t>
+  </si>
+  <si>
+    <t>FinalReportSF428B__c</t>
+  </si>
+  <si>
+    <t>DispositionReportRequestSF428C__c</t>
+  </si>
+  <si>
+    <t>SupplementalSheet__c</t>
+  </si>
+  <si>
+    <t>Prefix__c</t>
+  </si>
+  <si>
+    <t>FirstNameSF428__c</t>
+  </si>
+  <si>
+    <t>MiddleNameSF428__c</t>
+  </si>
+  <si>
+    <t>LastNameSF428__c</t>
+  </si>
+  <si>
+    <t>Suffix__c</t>
+  </si>
+  <si>
+    <t>TitleSF429__c</t>
+  </si>
+  <si>
+    <t>SubmittedBySF428__c</t>
+  </si>
+  <si>
+    <t>DateReportSubmittedSF428__c</t>
+  </si>
+  <si>
+    <t>AgencyCommentsSF428__c</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Identification__c</t>
+  </si>
+  <si>
+    <t>AcquisitionDate__c</t>
+  </si>
+  <si>
+    <t>FederalAgencyandOrganizationalSF429__c</t>
+  </si>
+  <si>
+    <t>Date__c</t>
   </si>
 </sst>
 </file>
@@ -1867,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>308</v>
+        <v>271</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1878,7 +1920,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -2551,10 +2593,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>316</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>317</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2562,7 +2604,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>312</v>
+        <v>275</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2573,7 +2615,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>276</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2584,7 +2626,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>277</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2595,7 +2637,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>315</v>
+        <v>278</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2606,7 +2648,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>318</v>
+        <v>281</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2617,7 +2659,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2628,7 +2670,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>320</v>
+        <v>283</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2639,7 +2681,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>321</v>
+        <v>284</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2650,7 +2692,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>322</v>
+        <v>285</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2661,10 +2703,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>323</v>
+        <v>286</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2672,7 +2714,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>324</v>
+        <v>287</v>
       </c>
       <c r="C12" s="10">
         <v>9999.99</v>
@@ -2683,7 +2725,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>325</v>
+        <v>288</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -2694,7 +2736,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>326</v>
+        <v>289</v>
       </c>
       <c r="C14" s="10">
         <v>9999.99</v>
@@ -2705,7 +2747,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>327</v>
+        <v>290</v>
       </c>
       <c r="C15" s="10">
         <v>1000</v>
@@ -2716,7 +2758,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>328</v>
+        <v>291</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>5</v>
@@ -2727,10 +2769,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>329</v>
+        <v>292</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2738,10 +2780,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>330</v>
+        <v>293</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2749,10 +2791,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2760,7 +2802,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>332</v>
+        <v>295</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>5</v>
@@ -2771,7 +2813,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>333</v>
+        <v>296</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>5</v>
@@ -2782,10 +2824,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>334</v>
+        <v>297</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2793,7 +2835,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>335</v>
+        <v>298</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2804,10 +2846,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>336</v>
+        <v>299</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2815,7 +2857,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>337</v>
+        <v>300</v>
       </c>
       <c r="C25">
         <v>8967045891</v>
@@ -2826,10 +2868,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>338</v>
+        <v>301</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2837,10 +2879,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>339</v>
+        <v>302</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2981,10 +3023,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2992,7 +3034,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -3003,7 +3045,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -3014,7 +3056,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -3025,7 +3067,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -3036,7 +3078,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>281</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -3047,7 +3089,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -3058,7 +3100,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -3069,7 +3111,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>284</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -3080,7 +3122,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>285</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -3091,7 +3133,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>291</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>5</v>
@@ -3102,10 +3144,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>293</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3113,10 +3155,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>294</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3124,7 +3166,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>295</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -3135,7 +3177,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>296</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -3146,10 +3188,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>297</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3157,7 +3199,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>298</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3168,10 +3210,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>299</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3179,7 +3221,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>300</v>
       </c>
       <c r="C19">
         <v>8967045891</v>
@@ -3190,10 +3232,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>301</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3201,10 +3243,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3237,10 +3279,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3251,7 +3293,7 @@
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3259,10 +3301,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3270,10 +3312,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3281,7 +3323,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -3292,7 +3334,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -3303,7 +3345,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3314,10 +3356,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3325,7 +3367,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3336,10 +3378,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3347,10 +3389,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3358,10 +3400,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3369,10 +3411,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3380,10 +3422,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3391,10 +3433,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3402,10 +3444,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3413,10 +3455,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3424,7 +3466,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3435,10 +3477,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3446,10 +3488,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3457,10 +3499,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3468,10 +3510,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3479,10 +3521,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3490,10 +3532,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3501,10 +3543,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3512,7 +3554,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="C27">
         <v>2122342342</v>
@@ -3523,10 +3565,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3534,7 +3576,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3560,10 +3602,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3571,10 +3613,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>352</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3582,10 +3624,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>326</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3593,7 +3635,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>353</v>
       </c>
       <c r="C4" s="11">
         <v>50</v>
@@ -3622,10 +3664,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3633,7 +3675,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="C2">
         <v>64789390</v>
@@ -3644,7 +3686,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>151</v>
+        <v>336</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3655,7 +3697,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>152</v>
+        <v>337</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3666,7 +3708,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>153</v>
+        <v>338</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3691,10 +3733,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3702,10 +3744,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>154</v>
+        <v>303</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3713,10 +3755,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>155</v>
+        <v>304</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3724,10 +3766,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>157</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3735,10 +3777,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>158</v>
+        <v>305</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3746,7 +3788,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>112</v>
+        <v>306</v>
       </c>
       <c r="C6" s="3">
         <v>25</v>
@@ -3757,10 +3799,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3768,7 +3810,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>160</v>
+        <v>308</v>
       </c>
       <c r="C8" s="13">
         <v>9999.99</v>
@@ -3779,10 +3821,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>161</v>
+        <v>309</v>
       </c>
       <c r="C9" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3805,10 +3847,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3816,7 +3858,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -3827,7 +3869,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>310</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3838,7 +3880,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>311</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3849,7 +3891,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3860,7 +3902,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>313</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -3871,10 +3913,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>170</v>
+        <v>317</v>
       </c>
       <c r="C7" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3882,7 +3924,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>314</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -3893,7 +3935,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -3904,7 +3946,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>315</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -3915,7 +3957,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -3926,10 +3968,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>286</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3937,7 +3979,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>318</v>
       </c>
       <c r="C13">
         <v>85</v>
@@ -3948,7 +3990,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>288</v>
       </c>
       <c r="C14">
         <v>85</v>
@@ -3959,7 +4001,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>289</v>
       </c>
       <c r="C15">
         <v>9999.99</v>
@@ -3970,7 +4012,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>290</v>
       </c>
       <c r="C16">
         <v>9999.99</v>
@@ -3981,10 +4023,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>292</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3992,10 +4034,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>293</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4003,10 +4045,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>294</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4014,7 +4056,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>295</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -4025,7 +4067,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>296</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -4036,10 +4078,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>297</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4047,7 +4089,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>298</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -4058,10 +4100,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>299</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4069,7 +4111,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>316</v>
       </c>
       <c r="C25">
         <v>9867589302</v>
@@ -4080,10 +4122,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>301</v>
       </c>
       <c r="C26" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4091,10 +4133,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="C27" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4117,10 +4159,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4128,7 +4170,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -4139,7 +4181,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>310</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -4150,7 +4192,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>311</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4161,7 +4203,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4172,7 +4214,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>313</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -4183,7 +4225,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>314</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -4194,7 +4236,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -4205,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>172</v>
+        <v>315</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -4216,7 +4258,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -4227,10 +4269,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>292</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4238,10 +4280,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>293</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4249,10 +4291,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>294</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4260,7 +4302,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>295</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4271,7 +4313,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>296</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4282,10 +4324,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>297</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4293,7 +4335,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>298</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -4304,10 +4346,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>299</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4315,7 +4357,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>316</v>
       </c>
       <c r="C19">
         <v>9867589302</v>
@@ -4326,10 +4368,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>301</v>
       </c>
       <c r="C20" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4337,10 +4379,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="C21" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4363,10 +4405,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4374,10 +4416,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>324</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4385,7 +4427,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>325</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4396,10 +4438,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>326</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4407,7 +4449,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>327</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4418,10 +4460,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>328</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4429,10 +4471,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>329</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4440,10 +4482,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>330</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4451,10 +4493,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>331</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4462,10 +4504,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>332</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4473,10 +4515,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>333</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4484,10 +4526,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>334</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4495,7 +4537,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>335</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4506,7 +4548,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>151</v>
+        <v>336</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4517,7 +4559,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>152</v>
+        <v>337</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4528,7 +4570,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>338</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -4539,7 +4581,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>180</v>
+        <v>339</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
@@ -4550,10 +4592,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>323</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4561,10 +4603,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>340</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4572,10 +4614,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4583,10 +4625,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
+        <v>342</v>
       </c>
       <c r="C21" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4594,10 +4636,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>343</v>
       </c>
       <c r="C22" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4605,10 +4647,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>137</v>
+        <v>344</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4616,10 +4658,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>139</v>
+        <v>345</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4627,10 +4669,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>346</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4638,7 +4680,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>316</v>
       </c>
       <c r="C26">
         <v>2122342342</v>
@@ -4649,10 +4691,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4660,7 +4702,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>182</v>
+        <v>347</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4671,10 +4713,10 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>183</v>
+        <v>348</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -4697,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4708,10 +4750,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>324</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4719,7 +4761,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>325</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4730,10 +4772,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>326</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4741,7 +4783,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>327</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4752,10 +4794,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>328</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4763,10 +4805,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>329</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4774,10 +4816,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>330</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4785,10 +4827,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>331</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4796,10 +4838,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>332</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4807,10 +4849,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>333</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4818,10 +4860,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>334</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4829,7 +4871,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>335</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4840,7 +4882,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>339</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
@@ -4851,10 +4893,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>323</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4862,10 +4904,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>340</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4873,10 +4915,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4884,10 +4926,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>133</v>
+        <v>342</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4895,10 +4937,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>343</v>
       </c>
       <c r="C19" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4906,10 +4948,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>137</v>
+        <v>344</v>
       </c>
       <c r="C20" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4917,10 +4959,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>139</v>
+        <v>345</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4928,10 +4970,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>141</v>
+        <v>346</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4939,7 +4981,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>142</v>
+        <v>316</v>
       </c>
       <c r="C23">
         <v>2122342342</v>
@@ -4950,10 +4992,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4961,7 +5003,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>182</v>
+        <v>347</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -4972,10 +5014,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>183</v>
+        <v>348</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -5067,10 +5109,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5078,7 +5120,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -5089,10 +5131,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5100,7 +5142,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5111,10 +5153,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5122,10 +5164,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5133,10 +5175,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5144,10 +5186,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5155,10 +5197,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5166,10 +5208,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5177,10 +5219,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5188,7 +5230,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -5199,7 +5241,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -5210,7 +5252,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -5221,7 +5263,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -5232,10 +5274,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5243,10 +5285,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5254,10 +5296,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5265,10 +5307,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5276,10 +5318,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5287,10 +5329,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C22" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5298,10 +5340,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5309,10 +5351,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5320,7 +5362,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="C25">
         <v>2122342342</v>
@@ -5331,10 +5373,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5342,7 +5384,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5353,10 +5395,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -5378,10 +5420,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5389,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>184</v>
+        <v>319</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -5400,10 +5442,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>185</v>
+        <v>320</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5411,10 +5453,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>187</v>
+        <v>321</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5422,7 +5464,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>188</v>
+        <v>322</v>
       </c>
       <c r="C5">
         <v>1111</v>
@@ -5433,10 +5475,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>181</v>
+        <v>323</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -5458,10 +5500,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5469,10 +5511,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>189</v>
+        <v>349</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5480,10 +5522,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>157</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5491,7 +5533,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>190</v>
+        <v>350</v>
       </c>
       <c r="C4">
         <v>76578</v>
@@ -5502,7 +5544,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>191</v>
+        <v>351</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -5513,7 +5555,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>160</v>
+        <v>308</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -5549,10 +5591,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5560,7 +5602,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5571,10 +5613,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5582,7 +5624,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5593,10 +5635,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5604,10 +5646,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5615,10 +5657,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5626,10 +5668,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5637,10 +5679,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5648,10 +5690,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5659,10 +5701,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5670,10 +5712,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5681,10 +5723,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5692,10 +5734,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5703,10 +5745,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5714,10 +5756,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5725,10 +5767,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5736,7 +5778,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -5747,7 +5789,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="C20">
         <v>150</v>
@@ -5758,7 +5800,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
@@ -5769,7 +5811,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
@@ -5780,7 +5822,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -5791,10 +5833,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5802,7 +5844,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -5813,10 +5855,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5824,10 +5866,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5835,10 +5877,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5846,10 +5888,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5857,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5868,10 +5910,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="C31" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5879,10 +5921,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5890,7 +5932,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C33" s="15">
         <v>2122342342</v>
@@ -5901,10 +5943,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5912,7 +5954,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5923,7 +5965,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -5959,10 +6001,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5970,7 +6012,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5981,10 +6023,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5992,7 +6034,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -6003,10 +6045,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6014,10 +6056,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6025,10 +6067,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6036,10 +6078,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6047,10 +6089,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6058,10 +6100,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6069,10 +6111,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6080,10 +6122,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6091,10 +6133,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6102,10 +6144,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6113,10 +6155,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6124,10 +6166,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6135,10 +6177,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6146,7 +6188,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -6157,10 +6199,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6168,10 +6210,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6179,10 +6221,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6190,10 +6232,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6201,10 +6243,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6212,10 +6254,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="C25" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6223,10 +6265,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6234,7 +6276,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C27" s="15">
         <v>2122342342</v>
@@ -6245,10 +6287,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6256,7 +6298,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6292,7 +6334,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6303,7 +6345,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -6314,7 +6356,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -6325,10 +6367,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6336,10 +6378,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6347,7 +6389,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C7">
         <v>123</v>
@@ -6358,10 +6400,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6369,10 +6411,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6380,10 +6422,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6391,10 +6433,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6402,10 +6444,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6413,10 +6455,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6424,10 +6466,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6435,7 +6477,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="C15">
         <v>1234</v>
@@ -6446,7 +6488,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="C16">
         <v>48</v>
@@ -6457,7 +6499,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="C17">
         <v>35</v>
@@ -6468,7 +6510,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -6479,10 +6521,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6490,7 +6532,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -6501,7 +6543,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6512,10 +6554,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6523,7 +6565,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -6534,7 +6576,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C24">
         <v>789</v>
@@ -6545,7 +6587,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -6556,7 +6598,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="C26">
         <v>456</v>
@@ -6567,7 +6609,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -6578,10 +6620,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6589,7 +6631,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="C29" t="s">
         <v>51</v>
@@ -6600,7 +6642,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="C30" t="s">
         <v>51</v>
@@ -6611,7 +6653,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="C31" t="s">
         <v>51</v>
@@ -6622,7 +6664,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -6633,10 +6675,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6644,7 +6686,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="C34" t="s">
         <v>45</v>
@@ -6655,10 +6697,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6666,10 +6708,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6677,7 +6719,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="C37">
         <v>10000</v>
@@ -6688,7 +6730,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="C38">
         <v>8000</v>
@@ -6699,7 +6741,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="C39">
         <v>6000</v>
@@ -6710,7 +6752,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -6721,7 +6763,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="C41">
         <v>300</v>
@@ -6732,7 +6774,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -6743,10 +6785,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +6821,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6790,7 +6832,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -6801,10 +6843,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6812,10 +6854,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6823,10 +6865,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6834,10 +6876,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6845,10 +6887,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6856,10 +6898,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6867,7 +6909,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C10" s="12">
         <v>1234</v>
@@ -6878,7 +6920,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="C11">
         <v>-8</v>
@@ -6889,7 +6931,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="C12">
         <v>-300</v>
@@ -6900,7 +6942,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="C13">
         <v>-200</v>
@@ -6911,7 +6953,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -6922,7 +6964,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C15">
         <v>-818</v>
@@ -6933,7 +6975,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="C16">
         <v>-8</v>
@@ -6944,7 +6986,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="C17">
         <v>-767</v>
@@ -6955,7 +6997,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -6966,7 +7008,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>45</v>
@@ -6977,7 +7019,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -6988,7 +7030,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -6999,7 +7041,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -7010,10 +7052,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7021,7 +7063,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="C24">
         <v>-1000</v>
@@ -7032,7 +7074,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="C25">
         <v>-700</v>
@@ -7043,7 +7085,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="C26">
         <v>-500</v>
@@ -7054,7 +7096,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="C27">
         <v>-300</v>
@@ -7065,7 +7107,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>245</v>
+        <v>208</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -7076,7 +7118,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="C29">
         <v>-150</v>
@@ -7087,7 +7129,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -7098,7 +7140,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="C31">
         <v>-40</v>
@@ -7145,10 +7187,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7156,7 +7198,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7167,10 +7209,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7178,10 +7220,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7189,10 +7231,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7200,10 +7242,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7211,10 +7253,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7222,10 +7264,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7233,10 +7275,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7244,7 +7286,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -7255,7 +7297,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -7266,7 +7308,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -7277,10 +7319,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7288,7 +7330,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -7299,7 +7341,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -7310,7 +7352,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -7321,10 +7363,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7332,7 +7374,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -7343,7 +7385,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -7354,10 +7396,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7365,7 +7407,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C23">
         <v>789</v>
@@ -7376,7 +7418,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="C24">
         <v>86</v>
@@ -7387,7 +7429,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="C25">
         <v>456</v>
@@ -7398,7 +7440,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="C26">
         <v>74</v>
@@ -7409,7 +7451,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
@@ -7420,7 +7462,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -7431,10 +7473,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7442,7 +7484,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -7453,10 +7495,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7486,7 +7528,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -7497,7 +7539,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -7508,7 +7550,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -7519,7 +7561,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -7530,7 +7572,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7541,7 +7583,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -7552,7 +7594,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -7563,10 +7605,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="C41" t="s">
-        <v>254</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7574,7 +7616,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>255</v>
+        <v>218</v>
       </c>
       <c r="C42">
         <v>400</v>
@@ -7585,7 +7627,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>256</v>
+        <v>219</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7596,7 +7638,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>257</v>
+        <v>220</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -7607,10 +7649,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -7655,7 +7697,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -7666,10 +7708,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7677,10 +7719,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7688,10 +7730,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7699,10 +7741,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7710,10 +7752,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7721,10 +7763,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7732,10 +7774,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -7779,10 +7821,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7790,7 +7832,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7801,10 +7843,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7812,10 +7854,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7823,10 +7865,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7834,10 +7876,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7845,10 +7887,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7856,10 +7898,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7867,7 +7909,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C11" s="12">
         <v>1234</v>
@@ -7878,7 +7920,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -7889,7 +7931,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="C13">
         <v>-466</v>
@@ -7900,7 +7942,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="C14">
         <v>-500</v>
@@ -7911,7 +7953,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="C15">
         <v>-400</v>
@@ -7922,7 +7964,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C16">
         <v>-789</v>
@@ -7933,7 +7975,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="C17">
         <v>-200</v>
@@ -7944,7 +7986,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="C18">
         <v>-456</v>
@@ -7955,7 +7997,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="C19">
         <v>-74</v>
@@ -7966,7 +8008,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -7977,7 +8019,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -7988,7 +8030,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="C22">
         <v>-400</v>
@@ -7999,7 +8041,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="C23">
         <v>-200</v>
@@ -8010,7 +8052,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="C24">
         <v>-100</v>
@@ -8021,7 +8063,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="C25">
         <v>-200</v>
@@ -8032,7 +8074,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="C26">
         <v>-50</v>
@@ -8043,7 +8085,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>255</v>
+        <v>218</v>
       </c>
       <c r="C27">
         <v>-400</v>
@@ -8054,7 +8096,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>270</v>
+        <v>233</v>
       </c>
       <c r="C28">
         <v>-200</v>
@@ -8065,7 +8107,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>256</v>
+        <v>219</v>
       </c>
       <c r="C29">
         <v>-100</v>
@@ -8076,7 +8118,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>257</v>
+        <v>220</v>
       </c>
       <c r="C30">
         <v>-200</v>
@@ -8087,7 +8129,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>271</v>
+        <v>234</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -8183,7 +8225,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8194,10 +8236,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="C3" t="s">
-        <v>261</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8205,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -8216,10 +8258,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8227,10 +8269,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8238,10 +8280,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8249,10 +8291,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8260,10 +8302,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8271,10 +8313,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8282,10 +8324,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8293,7 +8335,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -8304,7 +8346,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -8315,7 +8357,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -8326,7 +8368,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="C15">
         <v>500</v>
@@ -8337,10 +8379,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8348,7 +8390,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="C17">
         <v>1000</v>
@@ -8359,7 +8401,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="C18">
         <v>700</v>
@@ -8370,10 +8412,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8381,10 +8423,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>262</v>
+        <v>225</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8392,7 +8434,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>264</v>
+        <v>227</v>
       </c>
       <c r="C21">
         <v>1234</v>
@@ -8403,10 +8445,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="C22" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8414,10 +8456,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8425,10 +8467,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8436,7 +8478,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C25">
         <v>300</v>
@@ -8447,7 +8489,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="C26">
         <v>85</v>
@@ -8458,7 +8500,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -8469,7 +8511,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="C28">
         <v>76</v>
@@ -8480,7 +8522,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>45</v>
@@ -8491,7 +8533,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>45</v>
@@ -8502,10 +8544,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="C31" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8513,7 +8555,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>45</v>
@@ -8524,10 +8566,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8535,7 +8577,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>267</v>
+        <v>230</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>26</v>
@@ -8546,7 +8588,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>26</v>
@@ -8557,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>26</v>
@@ -8593,7 +8635,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8604,7 +8646,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -8615,10 +8657,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8626,10 +8668,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8637,10 +8679,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8648,10 +8690,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8659,10 +8701,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8670,10 +8712,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8681,10 +8723,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -8717,7 +8759,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="C2" s="3">
         <v>1234</v>
@@ -8728,7 +8770,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3">
         <v>123</v>
@@ -8739,10 +8781,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8750,10 +8792,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8761,10 +8803,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8772,10 +8814,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8783,10 +8825,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8794,10 +8836,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8805,7 +8847,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C10" s="15">
         <v>12345</v>
@@ -8816,7 +8858,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="C11" s="3">
         <v>-500</v>
@@ -8827,7 +8869,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="C12" s="3">
         <v>-1000</v>
@@ -8838,7 +8880,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="C13" s="3">
         <v>-700</v>
@@ -8849,7 +8891,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C14" s="3">
         <v>-300</v>
@@ -8860,7 +8902,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="C15" s="3">
         <v>-85</v>
@@ -8871,7 +8913,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="C16" s="3">
         <v>-200</v>
@@ -8882,7 +8924,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="C17" s="3">
         <v>-76</v>
@@ -8893,7 +8935,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>45</v>
@@ -8904,7 +8946,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>45</v>
@@ -8915,10 +8957,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8926,10 +8968,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>267</v>
+        <v>230</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8937,10 +8979,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8948,10 +8990,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -8974,7 +9016,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8985,10 +9027,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>272</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8996,10 +9038,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>288</v>
+        <v>251</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9007,10 +9049,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9018,7 +9060,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="C5" s="3">
         <v>1234</v>
@@ -9029,7 +9071,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>289</v>
+        <v>252</v>
       </c>
       <c r="C6" s="3">
         <v>8967589</v>
@@ -9040,7 +9082,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>291</v>
+        <v>254</v>
       </c>
       <c r="C7" s="3">
         <v>34567</v>
@@ -9051,7 +9093,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="C8" s="3">
         <v>50</v>
@@ -9062,7 +9104,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="C9" s="3">
         <v>100</v>
@@ -9073,10 +9115,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9084,7 +9126,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
@@ -9095,10 +9137,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9106,10 +9148,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9117,10 +9159,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9128,10 +9170,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9139,10 +9181,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9150,10 +9192,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9161,10 +9203,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>292</v>
+        <v>255</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>275</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9172,7 +9214,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="C19" s="3">
         <v>123</v>
@@ -9183,10 +9225,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9194,10 +9236,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>295</v>
+        <v>258</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9205,10 +9247,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>296</v>
+        <v>259</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9216,10 +9258,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9227,10 +9269,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9238,10 +9280,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9249,10 +9291,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9260,10 +9302,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9271,10 +9313,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>302</v>
+        <v>265</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>279</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9282,7 +9324,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="C29" s="3">
         <v>75</v>
@@ -9293,7 +9335,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>304</v>
+        <v>267</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
@@ -9304,7 +9346,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>305</v>
+        <v>268</v>
       </c>
       <c r="C31" s="3">
         <v>85</v>
@@ -9315,7 +9357,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="C32" s="3">
         <v>55</v>
@@ -9326,7 +9368,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>5</v>
@@ -9337,10 +9379,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9348,7 +9390,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -9359,10 +9401,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9370,10 +9412,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9381,10 +9423,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9392,10 +9434,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>282</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9403,10 +9445,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9414,10 +9456,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9425,7 +9467,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="C42" s="3">
         <v>9869875890</v>
@@ -9436,10 +9478,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>307</v>
+        <v>270</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9447,7 +9489,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C44" s="3">
         <v>20</v>
@@ -9458,10 +9500,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9469,10 +9511,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9480,10 +9522,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>285</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9491,10 +9533,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9502,10 +9544,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>286</v>
+        <v>249</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9513,7 +9555,7 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C50" s="3">
         <v>9869875890</v>
@@ -9538,7 +9580,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9549,10 +9591,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>272</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9560,10 +9602,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>288</v>
+        <v>251</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9571,10 +9613,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9582,7 +9624,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="C5" s="3">
         <v>50</v>
@@ -9593,7 +9635,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="C6" s="3">
         <v>100</v>
@@ -9604,10 +9646,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9615,7 +9657,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C8" s="3">
         <v>123</v>
@@ -9626,10 +9668,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9637,10 +9679,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9648,10 +9690,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9659,10 +9701,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9670,10 +9712,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9681,7 +9723,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3">
         <v>12345</v>
@@ -9692,10 +9734,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>292</v>
+        <v>255</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>275</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9703,7 +9745,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="C16" s="3">
         <v>123</v>
@@ -9714,10 +9756,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9725,10 +9767,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>295</v>
+        <v>258</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9736,10 +9778,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>296</v>
+        <v>259</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9747,10 +9789,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9758,10 +9800,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9769,7 +9811,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="C22" s="3">
         <v>12345</v>
@@ -9780,10 +9822,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9791,10 +9833,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9802,10 +9844,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>302</v>
+        <v>265</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>279</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9813,7 +9855,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="C26" s="3">
         <v>-75</v>
@@ -9824,7 +9866,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>304</v>
+        <v>267</v>
       </c>
       <c r="C27" s="3">
         <v>-65</v>
@@ -9835,7 +9877,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>305</v>
+        <v>268</v>
       </c>
       <c r="C28" s="3">
         <v>-85</v>
@@ -9846,7 +9888,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="C29" s="3">
         <v>-55</v>
@@ -9857,10 +9899,10 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9868,7 +9910,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -9879,10 +9921,10 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>307</v>
+        <v>270</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9890,7 +9932,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C33" s="3">
         <v>20</v>
@@ -10179,7 +10221,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>310</v>
+        <v>273</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>42</v>
@@ -10190,7 +10232,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>311</v>
+        <v>274</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>41</v>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6561DB-EB7B-4F5A-A1F8-54680C334475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799A7C7F-BA7F-49DE-9F9B-D63FCA5B6AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="11" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="13" activeTab="18" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="309">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -279,9 +279,6 @@
     <t>Construction</t>
   </si>
   <si>
-    <t>fieldInternalOrganization__c</t>
-  </si>
-  <si>
     <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
   </si>
   <si>
@@ -306,18 +303,6 @@
     <t>fieldFrequency__c</t>
   </si>
   <si>
-    <t>fieldGoverningOrganizationReportDate__c</t>
-  </si>
-  <si>
-    <t>fieldBoardInformation__c</t>
-  </si>
-  <si>
-    <t>fieldCalReportingStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldCalReportingEndDate__c</t>
-  </si>
-  <si>
     <t>fieldFederalGrantIdentifyingNumbe__c</t>
   </si>
   <si>
@@ -1012,6 +997,15 @@
   </si>
   <si>
     <t>BoardInformation__c</t>
+  </si>
+  <si>
+    <t>CalReportingStartDate__c</t>
+  </si>
+  <si>
+    <t>CalReportingEndDate__c</t>
+  </si>
+  <si>
+    <t>InternalOrganization__c</t>
   </si>
 </sst>
 </file>
@@ -1435,11 +1429,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1506,7 +1500,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1572,7 +1566,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>32</v>
@@ -1583,7 +1577,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>33</v>
@@ -1597,7 +1591,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1663,7 +1657,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>34</v>
@@ -1674,7 +1668,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>36</v>
@@ -1706,10 +1700,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="158" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1773,7 +1767,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1784,7 +1778,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -1798,10 +1792,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C922EE-7D55-45ED-84C0-E643E295F423}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1853,7 +1847,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>75</v>
+        <v>304</v>
       </c>
       <c r="C5" s="3">
         <v>-2</v>
@@ -1864,7 +1858,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>76</v>
+        <v>305</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>20</v>
@@ -1878,10 +1872,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1922,7 +1916,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>75</v>
+        <v>304</v>
       </c>
       <c r="C4" s="3">
         <v>-2</v>
@@ -1933,7 +1927,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>76</v>
+        <v>305</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>20</v>
@@ -1947,10 +1941,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1972,7 +1966,7 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2023,11 +2017,11 @@
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" t="s">
         <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2035,10 +2029,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
         <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2046,10 +2040,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2060,9 +2054,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2220,10 +2214,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2245,7 +2239,7 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2297,10 +2291,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" t="s">
         <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2308,10 +2302,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
         <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2319,10 +2313,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2333,10 +2327,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2358,7 +2352,7 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2410,10 +2404,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" t="s">
         <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2421,10 +2415,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
         <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2432,10 +2426,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2446,10 +2440,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5CE5DD-3172-4B5D-9DF0-D4E246B7968A}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2468,7 +2462,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2479,7 +2473,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2490,7 +2484,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2501,7 +2495,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2512,7 +2506,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2523,7 +2517,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2534,7 +2528,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2545,7 +2539,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2556,7 +2550,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2567,10 +2561,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2578,7 +2572,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C12" s="10">
         <v>9999.99</v>
@@ -2589,7 +2583,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -2600,7 +2594,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C14" s="10">
         <v>9999.99</v>
@@ -2611,7 +2605,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C15" s="10">
         <v>1000</v>
@@ -2622,7 +2616,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>5</v>
@@ -2633,10 +2627,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2644,10 +2638,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2655,10 +2649,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2666,7 +2660,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>5</v>
@@ -2677,7 +2671,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>5</v>
@@ -2688,10 +2682,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2699,7 +2693,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2710,10 +2704,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2721,7 +2715,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C25">
         <v>8967045891</v>
@@ -2732,10 +2726,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2743,10 +2737,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2758,10 +2752,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2840,9 +2834,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB2637BC-983B-4C46-AEC7-148BA71B263A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2862,7 +2856,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2876,10 +2870,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2898,7 +2892,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2909,7 +2903,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2920,7 +2914,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2931,7 +2925,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2942,7 +2936,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2953,7 +2947,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2964,7 +2958,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2975,7 +2969,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2986,7 +2980,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2997,7 +2991,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>5</v>
@@ -3008,10 +3002,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3019,10 +3013,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3030,7 +3024,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -3041,7 +3035,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -3052,10 +3046,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3063,7 +3057,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3074,10 +3068,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3085,7 +3079,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C19">
         <v>8967045891</v>
@@ -3096,10 +3090,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3107,10 +3101,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3121,7 +3115,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
@@ -3143,10 +3137,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3154,10 +3148,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3165,10 +3159,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3176,10 +3170,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3187,7 +3181,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -3198,7 +3192,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -3209,7 +3203,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3220,10 +3214,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3231,7 +3225,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3242,10 +3236,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3253,10 +3247,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3264,10 +3258,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3275,10 +3269,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3286,10 +3280,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3297,10 +3291,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3308,10 +3302,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3319,10 +3313,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3330,7 +3324,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3341,10 +3335,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3352,10 +3346,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3363,10 +3357,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3374,10 +3368,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3385,10 +3379,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3396,10 +3390,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3407,10 +3401,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3418,7 +3412,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C27">
         <v>2122342342</v>
@@ -3429,10 +3423,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3440,7 +3434,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3455,9 +3449,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785359D0-8BDB-4028-AD4B-2C0A4BB56435}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3477,10 +3471,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3488,10 +3482,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3499,7 +3493,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C4" s="11">
         <v>50</v>
@@ -3517,7 +3511,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B546E08-B445-4CFC-AE7C-A360990A58B3}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
@@ -3539,7 +3533,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>64789390</v>
@@ -3550,7 +3544,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3561,7 +3555,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3572,7 +3566,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3586,10 +3580,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08315C1-DA1D-48F4-A0A8-4BB13DC3E452}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="125.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="125.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3608,10 +3602,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3619,10 +3613,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3630,10 +3624,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3641,10 +3635,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" t="s">
         <v>159</v>
-      </c>
-      <c r="C5" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3652,7 +3646,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C6" s="3">
         <v>25</v>
@@ -3663,10 +3657,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3674,7 +3668,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C8" s="13">
         <v>9999.99</v>
@@ -3685,10 +3679,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -3700,10 +3694,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048DF57C-BB9A-45F0-8668-498DC1298DA0}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3722,7 +3716,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -3733,7 +3727,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3744,7 +3738,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3755,7 +3749,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3766,7 +3760,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -3777,10 +3771,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3788,7 +3782,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -3799,7 +3793,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -3810,7 +3804,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -3821,7 +3815,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -3832,10 +3826,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3843,7 +3837,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C13">
         <v>85</v>
@@ -3854,7 +3848,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C14">
         <v>85</v>
@@ -3865,7 +3859,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C15">
         <v>9999.99</v>
@@ -3876,7 +3870,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C16">
         <v>9999.99</v>
@@ -3887,10 +3881,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3898,10 +3892,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3909,10 +3903,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3920,7 +3914,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -3931,7 +3925,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -3942,10 +3936,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3953,7 +3947,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3964,10 +3958,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3975,7 +3969,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C25">
         <v>9867589302</v>
@@ -3986,10 +3980,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3997,10 +3991,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -4012,10 +4006,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8693D5-27C5-4228-92A0-224F98BEF54A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4034,7 +4028,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -4045,7 +4039,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -4056,7 +4050,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4067,7 +4061,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4078,7 +4072,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -4089,7 +4083,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -4100,7 +4094,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -4111,7 +4105,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -4122,7 +4116,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -4133,10 +4127,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4144,10 +4138,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4155,10 +4149,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4166,7 +4160,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4177,7 +4171,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4188,10 +4182,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4199,7 +4193,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -4210,10 +4204,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4221,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C19">
         <v>9867589302</v>
@@ -4232,10 +4226,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4243,10 +4237,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -4258,10 +4252,10 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702E2C7F-ACEF-451E-A257-8D7A1D64246B}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4280,10 +4274,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4291,7 +4285,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4302,10 +4296,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4313,7 +4307,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4324,10 +4318,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4335,10 +4329,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4346,10 +4340,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4357,10 +4351,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4368,10 +4362,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4379,10 +4373,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4390,10 +4384,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4401,7 +4395,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4412,7 +4406,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4423,7 +4417,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4434,7 +4428,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -4445,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
@@ -4456,10 +4450,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4467,10 +4461,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4478,10 +4472,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4489,10 +4483,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4500,10 +4494,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4511,10 +4505,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4522,10 +4516,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4533,10 +4527,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4544,7 +4538,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C26">
         <v>2122342342</v>
@@ -4555,10 +4549,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4566,7 +4560,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4577,10 +4571,10 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -4592,10 +4586,10 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18586F6-6D9E-4DD3-97F2-036CA4FFCAFA}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4614,10 +4608,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4625,7 +4619,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4636,10 +4630,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4647,7 +4641,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4658,10 +4652,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4669,10 +4663,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4680,10 +4674,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4691,10 +4685,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4702,10 +4696,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4713,10 +4707,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4724,10 +4718,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4735,7 +4729,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4746,7 +4740,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
@@ -4757,10 +4751,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4768,10 +4762,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4779,10 +4773,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4790,10 +4784,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4801,10 +4795,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4812,10 +4806,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4823,10 +4817,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4834,10 +4828,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4845,7 +4839,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C23">
         <v>2122342342</v>
@@ -4856,10 +4850,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4867,7 +4861,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -4878,10 +4872,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -4892,11 +4886,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4951,10 +4945,10 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4973,10 +4967,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4984,7 +4978,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4995,10 +4989,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5006,7 +5000,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5017,10 +5011,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5028,10 +5022,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5039,10 +5033,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5050,10 +5044,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5061,10 +5055,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5072,10 +5066,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5083,10 +5077,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5094,7 +5088,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -5105,7 +5099,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -5116,7 +5110,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -5127,7 +5121,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -5138,10 +5132,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5149,10 +5143,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5160,10 +5154,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5171,10 +5165,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5182,10 +5176,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C21" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5193,10 +5187,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5204,10 +5198,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5215,10 +5209,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5226,7 +5220,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C25">
         <v>2122342342</v>
@@ -5237,10 +5231,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5248,7 +5242,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5259,10 +5253,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -5273,9 +5267,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5295,7 +5289,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -5306,10 +5300,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5317,10 +5311,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>188</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5328,7 +5322,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C5">
         <v>1111</v>
@@ -5339,10 +5333,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -5353,10 +5347,10 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5DAE-E2BF-47B3-A1C9-7C4F12E126E5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5375,10 +5369,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5386,10 +5380,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5397,7 +5391,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C4">
         <v>76578</v>
@@ -5408,7 +5402,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -5419,7 +5413,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -5433,10 +5427,10 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF0C752-B8E1-4378-AC7E-8304285A9B90}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5455,10 +5449,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5466,7 +5460,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5477,10 +5471,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5488,7 +5482,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5499,10 +5493,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5510,10 +5504,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5521,10 +5515,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5532,10 +5526,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5543,10 +5537,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5554,10 +5548,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5565,10 +5559,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5576,10 +5570,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5587,10 +5581,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5598,10 +5592,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5609,10 +5603,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5620,10 +5614,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5631,10 +5625,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5642,7 +5636,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -5653,7 +5647,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C20">
         <v>150</v>
@@ -5664,7 +5658,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
@@ -5675,7 +5669,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
@@ -5686,7 +5680,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -5697,10 +5691,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5708,7 +5702,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -5719,10 +5713,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5730,10 +5724,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5741,10 +5735,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5752,10 +5746,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5763,10 +5757,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5774,10 +5768,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5785,10 +5779,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5796,7 +5790,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C33" s="15">
         <v>2122342342</v>
@@ -5807,10 +5801,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5818,7 +5812,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5829,7 +5823,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -5843,10 +5837,10 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E20211-1D84-48FF-8A84-AC0AE11DA487}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5865,10 +5859,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5876,7 +5870,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5887,10 +5881,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5898,7 +5892,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5909,10 +5903,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5920,10 +5914,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5931,10 +5925,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5942,10 +5936,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5953,10 +5947,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5964,10 +5958,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5975,10 +5969,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5986,10 +5980,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5997,10 +5991,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6008,10 +6002,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6019,10 +6013,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6030,10 +6024,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6041,10 +6035,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6052,7 +6046,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -6063,10 +6057,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6074,10 +6068,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6085,10 +6079,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6096,10 +6090,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6107,10 +6101,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6118,10 +6112,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6129,10 +6123,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6140,7 +6134,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C27" s="15">
         <v>2122342342</v>
@@ -6151,10 +6145,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6162,7 +6156,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6176,10 +6170,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDEAA85-D896-403F-9A59-1E6EC90F5CC2}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="44.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6198,7 +6192,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6209,7 +6203,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -6220,7 +6214,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -6231,10 +6225,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6242,10 +6236,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6253,7 +6247,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C7">
         <v>123</v>
@@ -6264,10 +6258,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6275,10 +6269,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" t="s">
         <v>118</v>
-      </c>
-      <c r="C9" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6286,10 +6280,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6297,10 +6291,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6308,10 +6302,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6319,10 +6313,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6330,10 +6324,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6341,7 +6335,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C15">
         <v>1234</v>
@@ -6352,7 +6346,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C16">
         <v>48</v>
@@ -6363,7 +6357,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C17">
         <v>35</v>
@@ -6374,7 +6368,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -6385,10 +6379,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6396,7 +6390,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -6407,7 +6401,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6418,10 +6412,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6429,7 +6423,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -6440,7 +6434,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C24">
         <v>789</v>
@@ -6451,7 +6445,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -6462,7 +6456,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C26">
         <v>456</v>
@@ -6473,7 +6467,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -6484,10 +6478,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6495,7 +6489,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C29" t="s">
         <v>51</v>
@@ -6506,7 +6500,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C30" t="s">
         <v>51</v>
@@ -6517,7 +6511,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C31" t="s">
         <v>51</v>
@@ -6528,7 +6522,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -6539,10 +6533,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6550,7 +6544,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C34" t="s">
         <v>45</v>
@@ -6561,10 +6555,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6572,10 +6566,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6583,7 +6577,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C37">
         <v>10000</v>
@@ -6594,7 +6588,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C38">
         <v>8000</v>
@@ -6605,7 +6599,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C39">
         <v>6000</v>
@@ -6616,7 +6610,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -6627,7 +6621,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C41">
         <v>300</v>
@@ -6638,7 +6632,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -6649,10 +6643,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -6663,10 +6657,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3C73BB-4FB2-4E8F-8651-A6AF93AAD260}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6685,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6696,7 +6690,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -6707,10 +6701,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6718,10 +6712,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" t="s">
         <v>118</v>
-      </c>
-      <c r="C5" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6729,10 +6723,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6740,10 +6734,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6751,10 +6745,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6762,10 +6756,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6773,7 +6767,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C10" s="12">
         <v>1234</v>
@@ -6784,7 +6778,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C11">
         <v>-8</v>
@@ -6795,7 +6789,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C12">
         <v>-300</v>
@@ -6806,7 +6800,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C13">
         <v>-200</v>
@@ -6817,7 +6811,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -6828,7 +6822,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C15">
         <v>-818</v>
@@ -6839,7 +6833,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C16">
         <v>-8</v>
@@ -6850,7 +6844,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C17">
         <v>-767</v>
@@ -6861,7 +6855,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -6872,7 +6866,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>45</v>
@@ -6883,7 +6877,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -6894,7 +6888,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -6905,7 +6899,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -6916,10 +6910,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6927,7 +6921,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C24">
         <v>-1000</v>
@@ -6938,7 +6932,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C25">
         <v>-700</v>
@@ -6949,7 +6943,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C26">
         <v>-500</v>
@@ -6960,7 +6954,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C27">
         <v>-300</v>
@@ -6971,7 +6965,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -6982,7 +6976,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C29">
         <v>-150</v>
@@ -6993,7 +6987,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -7004,7 +6998,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C31">
         <v>-40</v>
@@ -7018,10 +7012,10 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7695C766-C8BF-4FC6-94BA-EF5703D41976}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7040,7 +7034,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7051,10 +7045,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7062,7 +7056,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7073,10 +7067,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7084,10 +7078,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" t="s">
         <v>118</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7095,10 +7089,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7106,10 +7100,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7117,10 +7111,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7128,10 +7122,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7139,10 +7133,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7150,7 +7144,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -7161,7 +7155,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -7172,7 +7166,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -7183,10 +7177,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7194,7 +7188,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -7205,7 +7199,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -7216,7 +7210,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -7227,10 +7221,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7238,7 +7232,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -7249,7 +7243,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -7260,10 +7254,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7271,7 +7265,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C23">
         <v>789</v>
@@ -7282,7 +7276,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C24">
         <v>86</v>
@@ -7293,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C25">
         <v>456</v>
@@ -7304,7 +7298,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C26">
         <v>74</v>
@@ -7315,7 +7309,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
@@ -7326,7 +7320,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -7337,10 +7331,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7348,7 +7342,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -7359,10 +7353,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7370,7 +7364,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -7381,7 +7375,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -7392,7 +7386,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -7403,7 +7397,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -7414,7 +7408,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -7425,7 +7419,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -7436,7 +7430,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7447,7 +7441,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -7458,7 +7452,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -7469,10 +7463,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C41" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7480,7 +7474,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C42">
         <v>400</v>
@@ -7491,7 +7485,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7502,7 +7496,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -7513,10 +7507,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -7528,10 +7522,10 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89650214-A8DD-44FC-9DFA-301D63E80C53}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7550,7 +7544,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7561,7 +7555,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -7572,10 +7566,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7583,10 +7577,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" t="s">
         <v>118</v>
-      </c>
-      <c r="C5" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7594,10 +7588,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7605,10 +7599,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7616,10 +7610,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7627,10 +7621,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7638,10 +7632,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -7652,10 +7646,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE9724B-3165-4EC7-A43C-010FD17B4AF6}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7674,7 +7668,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7685,10 +7679,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7696,7 +7690,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7707,10 +7701,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7718,10 +7712,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" t="s">
         <v>118</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7729,10 +7723,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7740,10 +7734,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7751,10 +7745,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7762,10 +7756,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7773,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C11" s="12">
         <v>1234</v>
@@ -7784,7 +7778,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -7795,7 +7789,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C13">
         <v>-466</v>
@@ -7806,7 +7800,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C14">
         <v>-500</v>
@@ -7817,7 +7811,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C15">
         <v>-400</v>
@@ -7828,7 +7822,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C16">
         <v>-789</v>
@@ -7839,7 +7833,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C17">
         <v>-200</v>
@@ -7850,7 +7844,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C18">
         <v>-456</v>
@@ -7861,7 +7855,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C19">
         <v>-74</v>
@@ -7872,7 +7866,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -7883,7 +7877,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -7894,7 +7888,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C22">
         <v>-400</v>
@@ -7905,7 +7899,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C23">
         <v>-200</v>
@@ -7916,7 +7910,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C24">
         <v>-100</v>
@@ -7927,7 +7921,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C25">
         <v>-200</v>
@@ -7938,7 +7932,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C26">
         <v>-50</v>
@@ -7949,7 +7943,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C27">
         <v>-400</v>
@@ -7960,7 +7954,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C28">
         <v>-200</v>
@@ -7971,7 +7965,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C29">
         <v>-100</v>
@@ -7982,7 +7976,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C30">
         <v>-200</v>
@@ -7993,7 +7987,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -8008,11 +8002,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8067,10 +8061,10 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8089,7 +8083,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8100,10 +8094,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8111,7 +8105,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -8122,10 +8116,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8133,10 +8127,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" t="s">
         <v>118</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8144,10 +8138,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8155,10 +8149,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8166,10 +8160,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8177,10 +8171,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8188,10 +8182,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8199,7 +8193,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -8210,7 +8204,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -8221,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -8232,7 +8226,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C15">
         <v>500</v>
@@ -8243,10 +8237,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8254,7 +8248,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C17">
         <v>1000</v>
@@ -8265,7 +8259,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C18">
         <v>700</v>
@@ -8276,10 +8270,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8287,10 +8281,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8298,7 +8292,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C21">
         <v>1234</v>
@@ -8309,10 +8303,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C22" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8320,10 +8314,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8331,10 +8325,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8342,7 +8336,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C25">
         <v>300</v>
@@ -8353,7 +8347,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C26">
         <v>85</v>
@@ -8364,7 +8358,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -8375,7 +8369,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C28">
         <v>76</v>
@@ -8386,7 +8380,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>45</v>
@@ -8397,7 +8391,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>45</v>
@@ -8408,10 +8402,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C31" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8419,7 +8413,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>45</v>
@@ -8430,10 +8424,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8441,7 +8435,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>26</v>
@@ -8452,7 +8446,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>26</v>
@@ -8463,7 +8457,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>26</v>
@@ -8477,10 +8471,10 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87CE4365-F4A6-44A6-8070-7113DA611997}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8499,7 +8493,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8510,7 +8504,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -8521,10 +8515,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8532,10 +8526,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" t="s">
         <v>118</v>
-      </c>
-      <c r="C5" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8543,10 +8537,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8554,10 +8548,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8565,10 +8559,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8576,10 +8570,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8587,10 +8581,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -8601,10 +8595,10 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8623,7 +8617,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C2" s="3">
         <v>1234</v>
@@ -8634,7 +8628,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C3" s="3">
         <v>123</v>
@@ -8645,10 +8639,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8656,10 +8650,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8667,10 +8661,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8678,10 +8672,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8689,10 +8683,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8700,10 +8694,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8711,7 +8705,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C10" s="15">
         <v>12345</v>
@@ -8722,7 +8716,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C11" s="3">
         <v>-500</v>
@@ -8733,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C12" s="3">
         <v>-1000</v>
@@ -8744,7 +8738,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C13" s="3">
         <v>-700</v>
@@ -8755,7 +8749,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C14" s="3">
         <v>-300</v>
@@ -8766,7 +8760,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C15" s="3">
         <v>-85</v>
@@ -8777,7 +8771,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C16" s="3">
         <v>-200</v>
@@ -8788,7 +8782,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C17" s="3">
         <v>-76</v>
@@ -8799,7 +8793,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>45</v>
@@ -8810,7 +8804,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>45</v>
@@ -8821,10 +8815,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8832,10 +8826,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8843,10 +8837,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8854,10 +8848,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -8869,10 +8863,10 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B75E61-DAA5-4C75-9938-082F14D489D1}">
   <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="40.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.08984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8880,7 +8874,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8891,10 +8885,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8902,10 +8896,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8913,10 +8907,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8924,7 +8918,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C5" s="3">
         <v>1234</v>
@@ -8935,7 +8929,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C6" s="3">
         <v>8967589</v>
@@ -8946,7 +8940,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C7" s="3">
         <v>34567</v>
@@ -8957,7 +8951,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C8" s="3">
         <v>50</v>
@@ -8968,7 +8962,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C9" s="3">
         <v>100</v>
@@ -8979,10 +8973,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8990,7 +8984,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
@@ -9001,10 +8995,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9012,10 +9006,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9023,10 +9017,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9034,10 +9028,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9045,10 +9039,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9056,10 +9050,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9067,10 +9061,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9078,7 +9072,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C19" s="3">
         <v>123</v>
@@ -9089,10 +9083,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9100,10 +9094,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9111,10 +9105,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9122,10 +9116,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9133,10 +9127,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9144,10 +9138,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9155,10 +9149,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9166,10 +9160,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9177,10 +9171,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9188,7 +9182,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C29" s="3">
         <v>75</v>
@@ -9199,7 +9193,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
@@ -9210,7 +9204,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C31" s="3">
         <v>85</v>
@@ -9221,7 +9215,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C32" s="3">
         <v>55</v>
@@ -9232,7 +9226,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>5</v>
@@ -9243,10 +9237,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9254,7 +9248,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -9265,10 +9259,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9276,10 +9270,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9287,10 +9281,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9298,10 +9292,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9309,10 +9303,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9320,10 +9314,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9331,7 +9325,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C42" s="3">
         <v>9869875890</v>
@@ -9342,10 +9336,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9353,7 +9347,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C44" s="3">
         <v>20</v>
@@ -9364,10 +9358,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9375,10 +9369,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9386,10 +9380,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9397,10 +9391,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9408,10 +9402,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9419,7 +9413,7 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C50" s="3">
         <v>9869875890</v>
@@ -9433,10 +9427,10 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F13134-7D58-41D3-85C8-A2B7688C4794}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9444,7 +9438,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9455,10 +9449,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9466,10 +9460,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9477,10 +9471,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9488,7 +9482,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C5" s="3">
         <v>50</v>
@@ -9499,7 +9493,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C6" s="3">
         <v>100</v>
@@ -9510,10 +9504,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9521,7 +9515,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C8" s="3">
         <v>123</v>
@@ -9532,10 +9526,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9543,10 +9537,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9554,10 +9548,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9565,10 +9559,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9576,10 +9570,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9587,7 +9581,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C14" s="3">
         <v>12345</v>
@@ -9598,10 +9592,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9609,7 +9603,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C16" s="3">
         <v>123</v>
@@ -9620,10 +9614,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9631,10 +9625,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9642,10 +9636,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9653,10 +9647,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9664,10 +9658,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9675,7 +9669,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C22" s="3">
         <v>12345</v>
@@ -9686,10 +9680,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9697,10 +9691,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9708,10 +9702,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9719,7 +9713,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C26" s="3">
         <v>-75</v>
@@ -9730,7 +9724,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C27" s="3">
         <v>-65</v>
@@ -9741,7 +9735,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C28" s="3">
         <v>-85</v>
@@ -9752,7 +9746,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C29" s="3">
         <v>-55</v>
@@ -9763,10 +9757,10 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9774,7 +9768,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -9785,10 +9779,10 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9796,7 +9790,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C33" s="3">
         <v>20</v>
@@ -9810,11 +9804,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9869,9 +9863,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9927,7 +9921,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -9960,7 +9954,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>30</v>
@@ -9988,23 +9982,23 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15">
+    <row r="6" spans="1:3" ht="16">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15">
+    <row r="7" spans="1:3" ht="16">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>29</v>
@@ -10019,7 +10013,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -10080,23 +10074,23 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15">
+    <row r="6" spans="1:3" ht="16">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15">
+    <row r="7" spans="1:3" ht="16">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>41</v>
@@ -10110,7 +10104,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -10165,7 +10159,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>37</v>
@@ -10176,7 +10170,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>38</v>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB208F1D-0131-47FD-A8A7-2FADFC42E67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9CA75D-3E16-4FFD-B021-75A6D77675CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="21" activeTab="23" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="21" activeTab="21" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="356">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -342,9 +342,6 @@
     <t>John Mathews</t>
   </si>
   <si>
-    <t>fieldAcquisitionDateSF428A__c</t>
-  </si>
-  <si>
     <t>fieldTelephone2__c</t>
   </si>
   <si>
@@ -357,15 +354,6 @@
     <t>fieldFederalAgencySF428__c</t>
   </si>
   <si>
-    <t>fieldReportType__c</t>
-  </si>
-  <si>
-    <t>fieldBasisOfAccounting__c</t>
-  </si>
-  <si>
-    <t>fieldAcquiredDate__c</t>
-  </si>
-  <si>
     <t>fieldAORDateSubmitted__c</t>
   </si>
   <si>
@@ -1141,6 +1129,24 @@
   </si>
   <si>
     <t>Date__c</t>
+  </si>
+  <si>
+    <t>ReportType__c</t>
+  </si>
+  <si>
+    <t>BasisOfAccounting__c</t>
+  </si>
+  <si>
+    <t>AORDateSubmitted__c</t>
+  </si>
+  <si>
+    <t>Remark__c</t>
+  </si>
+  <si>
+    <t>AcknowledgementSF428__c</t>
+  </si>
+  <si>
+    <t>SubmittedOn__c</t>
   </si>
 </sst>
 </file>
@@ -1909,7 +1915,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1920,7 +1926,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -2593,10 +2599,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2604,7 +2610,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2615,7 +2621,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2626,7 +2632,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2637,7 +2643,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2648,7 +2654,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2659,7 +2665,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2670,7 +2676,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2681,7 +2687,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2692,7 +2698,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2703,7 +2709,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C11" t="s">
         <v>81</v>
@@ -2714,7 +2720,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C12" s="10">
         <v>9999.99</v>
@@ -2725,7 +2731,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -2736,7 +2742,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C14" s="10">
         <v>9999.99</v>
@@ -2747,7 +2753,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C15" s="10">
         <v>1000</v>
@@ -2758,7 +2764,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>5</v>
@@ -2769,7 +2775,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
         <v>84</v>
@@ -2780,7 +2786,7 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C18" t="s">
         <v>85</v>
@@ -2791,7 +2797,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C19" t="s">
         <v>85</v>
@@ -2802,7 +2808,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>5</v>
@@ -2813,7 +2819,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>5</v>
@@ -2824,7 +2830,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C22" t="s">
         <v>86</v>
@@ -2835,7 +2841,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2846,7 +2852,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C24" t="s">
         <v>86</v>
@@ -2857,7 +2863,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C25">
         <v>8967045891</v>
@@ -2868,7 +2874,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C26" t="s">
         <v>84</v>
@@ -2879,10 +2885,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3023,10 +3029,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3034,7 +3040,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -3045,7 +3051,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -3056,7 +3062,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -3067,7 +3073,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -3078,7 +3084,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -3089,7 +3095,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -3100,7 +3106,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -3111,7 +3117,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -3122,7 +3128,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -3133,7 +3139,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>5</v>
@@ -3144,7 +3150,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C12" t="s">
         <v>85</v>
@@ -3155,7 +3161,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C13" t="s">
         <v>85</v>
@@ -3166,7 +3172,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -3177,7 +3183,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -3188,7 +3194,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C16" t="s">
         <v>86</v>
@@ -3199,7 +3205,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3210,7 +3216,7 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C18" t="s">
         <v>86</v>
@@ -3221,7 +3227,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C19">
         <v>8967045891</v>
@@ -3232,7 +3238,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C20" t="s">
         <v>84</v>
@@ -3243,10 +3249,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3268,10 +3274,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3279,10 +3285,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3290,10 +3296,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>271</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3301,10 +3307,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>350</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3312,10 +3318,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>351</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3323,7 +3329,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>302</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -3334,7 +3340,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>294</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -3345,7 +3351,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>352</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3356,10 +3362,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>322</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3367,7 +3373,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>323</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3378,10 +3384,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>324</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3389,10 +3395,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>325</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3400,10 +3406,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" t="s">
         <v>100</v>
-      </c>
-      <c r="C13" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3411,10 +3417,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>327</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3422,10 +3428,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>328</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3433,10 +3439,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>329</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3444,10 +3450,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>330</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3455,7 +3461,7 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>353</v>
       </c>
       <c r="C18" t="s">
         <v>84</v>
@@ -3466,7 +3472,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>354</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3477,10 +3483,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>336</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3488,10 +3494,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>337</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3499,10 +3505,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>338</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3510,10 +3516,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>339</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3521,10 +3527,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>340</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3532,10 +3538,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>341</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3543,7 +3549,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>342</v>
       </c>
       <c r="C26" t="s">
         <v>86</v>
@@ -3554,7 +3560,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>312</v>
       </c>
       <c r="C27">
         <v>2122342342</v>
@@ -3565,10 +3571,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
+        <v>298</v>
+      </c>
+      <c r="C28" t="s">
         <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3576,7 +3582,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>355</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3602,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3613,10 +3619,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3624,10 +3630,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3635,7 +3641,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C4" s="11">
         <v>50</v>
@@ -3664,10 +3670,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3675,7 +3681,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C2">
         <v>64789390</v>
@@ -3686,7 +3692,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3697,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3708,7 +3714,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3733,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3744,10 +3750,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3755,10 +3761,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3769,7 +3775,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3777,10 +3783,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3788,7 +3794,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C6" s="3">
         <v>25</v>
@@ -3799,10 +3805,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3810,7 +3816,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C8" s="13">
         <v>9999.99</v>
@@ -3821,10 +3827,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -3847,10 +3853,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3858,7 +3864,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -3869,7 +3875,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3880,7 +3886,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3891,7 +3897,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3902,7 +3908,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -3913,10 +3919,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3924,7 +3930,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -3935,7 +3941,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -3946,7 +3952,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -3957,7 +3963,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -3968,7 +3974,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C12" t="s">
         <v>81</v>
@@ -3979,7 +3985,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C13">
         <v>85</v>
@@ -3990,7 +3996,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C14">
         <v>85</v>
@@ -4001,7 +4007,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C15">
         <v>9999.99</v>
@@ -4012,7 +4018,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C16">
         <v>9999.99</v>
@@ -4023,7 +4029,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
         <v>84</v>
@@ -4034,7 +4040,7 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C18" t="s">
         <v>85</v>
@@ -4045,7 +4051,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C19" t="s">
         <v>85</v>
@@ -4056,7 +4062,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -4067,7 +4073,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -4078,7 +4084,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C22" t="s">
         <v>84</v>
@@ -4089,7 +4095,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -4100,10 +4106,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4111,7 +4117,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C25">
         <v>9867589302</v>
@@ -4122,10 +4128,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C26" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4133,10 +4139,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C27" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -4159,10 +4165,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4170,7 +4176,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -4181,7 +4187,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -4192,7 +4198,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4203,7 +4209,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4214,7 +4220,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -4225,7 +4231,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -4236,7 +4242,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -4247,7 +4253,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -4258,7 +4264,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -4269,7 +4275,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C11" t="s">
         <v>84</v>
@@ -4280,7 +4286,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C12" t="s">
         <v>85</v>
@@ -4291,7 +4297,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C13" t="s">
         <v>85</v>
@@ -4302,7 +4308,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4313,7 +4319,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4324,7 +4330,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C16" t="s">
         <v>84</v>
@@ -4335,7 +4341,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -4346,10 +4352,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4357,7 +4363,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C19">
         <v>9867589302</v>
@@ -4368,10 +4374,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4379,10 +4385,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -4405,10 +4411,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4416,10 +4422,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4427,7 +4433,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4438,10 +4444,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4449,7 +4455,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4460,10 +4466,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4471,10 +4477,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4482,10 +4488,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4493,10 +4499,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4504,10 +4510,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4515,10 +4521,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4526,10 +4532,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4537,7 +4543,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4548,7 +4554,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4559,7 +4565,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4570,7 +4576,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -4581,7 +4587,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
@@ -4592,7 +4598,7 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C18" t="s">
         <v>84</v>
@@ -4603,10 +4609,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4614,10 +4620,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4625,10 +4631,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4636,10 +4642,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4647,10 +4653,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4658,10 +4664,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4669,7 +4675,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C25" t="s">
         <v>86</v>
@@ -4680,7 +4686,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C26">
         <v>2122342342</v>
@@ -4691,10 +4697,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4702,7 +4708,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4713,7 +4719,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C29" t="s">
         <v>84</v>
@@ -4739,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4750,10 +4756,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4761,7 +4767,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4772,10 +4778,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4783,7 +4789,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4794,10 +4800,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4805,10 +4811,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4816,10 +4822,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4827,10 +4833,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4838,10 +4844,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4849,10 +4855,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4860,10 +4866,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4871,7 +4877,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4882,7 +4888,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
@@ -4893,7 +4899,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C15" t="s">
         <v>84</v>
@@ -4904,10 +4910,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4915,10 +4921,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4926,10 +4932,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4937,10 +4943,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4948,10 +4954,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4959,10 +4965,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4970,7 +4976,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C22" t="s">
         <v>86</v>
@@ -4981,7 +4987,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C23">
         <v>2122342342</v>
@@ -4992,10 +4998,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5003,7 +5009,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -5014,7 +5020,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C26" t="s">
         <v>84</v>
@@ -5109,10 +5115,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5120,7 +5126,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -5131,10 +5137,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5142,7 +5148,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5153,10 +5159,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5164,10 +5170,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5175,10 +5181,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" t="s">
         <v>100</v>
-      </c>
-      <c r="C8" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5186,10 +5192,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5197,10 +5203,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5208,10 +5214,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5219,10 +5225,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5230,7 +5236,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -5241,7 +5247,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -5252,7 +5258,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -5263,7 +5269,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -5274,7 +5280,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C17" t="s">
         <v>84</v>
@@ -5285,10 +5291,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5296,10 +5302,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5307,10 +5313,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5318,10 +5324,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5329,10 +5335,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5340,10 +5346,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5351,7 +5357,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
         <v>86</v>
@@ -5362,7 +5368,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C25">
         <v>2122342342</v>
@@ -5373,10 +5379,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
         <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5384,7 +5390,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5395,7 +5401,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C28" t="s">
         <v>84</v>
@@ -5420,10 +5426,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5431,7 +5437,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -5442,10 +5448,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5453,10 +5459,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5464,7 +5470,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C5">
         <v>1111</v>
@@ -5475,7 +5481,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C6" t="s">
         <v>84</v>
@@ -5500,10 +5506,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5511,7 +5517,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C2" t="s">
         <v>84</v>
@@ -5525,7 +5531,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5533,7 +5539,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C4">
         <v>76578</v>
@@ -5544,7 +5550,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -5555,7 +5561,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -5591,10 +5597,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5602,7 +5608,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5613,10 +5619,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5624,7 +5630,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5635,10 +5641,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5646,10 +5652,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5657,10 +5663,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>100</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5668,10 +5674,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5679,10 +5685,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5690,10 +5696,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5701,10 +5707,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5712,10 +5718,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5723,10 +5729,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5734,10 +5740,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5745,10 +5751,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5756,10 +5762,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5767,10 +5773,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5778,7 +5784,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -5789,7 +5795,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C20">
         <v>150</v>
@@ -5800,7 +5806,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
@@ -5811,7 +5817,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
@@ -5822,7 +5828,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -5833,10 +5839,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5844,7 +5850,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -5855,10 +5861,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5866,10 +5872,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5877,10 +5883,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5888,10 +5894,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5899,10 +5905,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5910,10 +5916,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5921,7 +5927,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
         <v>86</v>
@@ -5932,7 +5938,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C33" s="15">
         <v>2122342342</v>
@@ -5943,10 +5949,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5954,7 +5960,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5965,7 +5971,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -6001,10 +6007,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6012,7 +6018,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -6023,10 +6029,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6034,7 +6040,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -6045,10 +6051,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6056,10 +6062,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6067,10 +6073,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>100</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6078,10 +6084,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6089,10 +6095,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6100,10 +6106,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6111,10 +6117,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6122,10 +6128,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6133,10 +6139,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6144,10 +6150,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6155,10 +6161,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6166,10 +6172,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6177,10 +6183,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6188,7 +6194,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -6199,10 +6205,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6210,10 +6216,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6221,10 +6227,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6232,10 +6238,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6243,10 +6249,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6254,10 +6260,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6265,7 +6271,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
         <v>86</v>
@@ -6276,7 +6282,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" s="15">
         <v>2122342342</v>
@@ -6287,10 +6293,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6298,7 +6304,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6334,7 +6340,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6345,7 +6351,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -6356,7 +6362,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -6367,10 +6373,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6378,7 +6384,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
         <v>84</v>
@@ -6389,7 +6395,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C7">
         <v>123</v>
@@ -6400,10 +6406,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6411,10 +6417,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6422,10 +6428,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6433,10 +6439,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6444,10 +6450,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6455,10 +6461,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6466,10 +6472,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6477,7 +6483,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C15">
         <v>1234</v>
@@ -6488,7 +6494,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C16">
         <v>48</v>
@@ -6499,7 +6505,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C17">
         <v>35</v>
@@ -6510,7 +6516,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -6521,10 +6527,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6532,7 +6538,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -6543,7 +6549,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6554,10 +6560,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6565,7 +6571,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -6587,7 +6593,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -6598,7 +6604,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C26">
         <v>456</v>
@@ -6609,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -6620,10 +6626,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6631,7 +6637,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
         <v>51</v>
@@ -6642,7 +6648,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C30" t="s">
         <v>51</v>
@@ -6653,7 +6659,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C31" t="s">
         <v>51</v>
@@ -6664,7 +6670,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -6675,7 +6681,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C33" t="s">
         <v>84</v>
@@ -6686,7 +6692,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C34" t="s">
         <v>45</v>
@@ -6697,7 +6703,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C35" t="s">
         <v>84</v>
@@ -6708,10 +6714,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6719,7 +6725,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C37">
         <v>10000</v>
@@ -6730,7 +6736,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C38">
         <v>8000</v>
@@ -6741,7 +6747,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C39">
         <v>6000</v>
@@ -6752,7 +6758,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -6763,7 +6769,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C41">
         <v>300</v>
@@ -6774,7 +6780,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -6785,7 +6791,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C43" t="s">
         <v>84</v>
@@ -6821,7 +6827,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6832,7 +6838,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -6843,10 +6849,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6854,10 +6860,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6865,10 +6871,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6876,10 +6882,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6887,10 +6893,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6898,10 +6904,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6909,7 +6915,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" s="12">
         <v>1234</v>
@@ -6920,7 +6926,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C11">
         <v>-8</v>
@@ -6931,7 +6937,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C12">
         <v>-300</v>
@@ -6942,7 +6948,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C13">
         <v>-200</v>
@@ -6953,7 +6959,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -6975,7 +6981,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C16">
         <v>-8</v>
@@ -6986,7 +6992,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C17">
         <v>-767</v>
@@ -6997,7 +7003,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -7008,7 +7014,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>45</v>
@@ -7019,7 +7025,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -7030,7 +7036,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -7041,7 +7047,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -7052,10 +7058,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7063,7 +7069,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C24">
         <v>-1000</v>
@@ -7074,7 +7080,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C25">
         <v>-700</v>
@@ -7085,7 +7091,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C26">
         <v>-500</v>
@@ -7096,7 +7102,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C27">
         <v>-300</v>
@@ -7107,7 +7113,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -7118,7 +7124,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C29">
         <v>-150</v>
@@ -7129,7 +7135,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -7140,7 +7146,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C31">
         <v>-40</v>
@@ -7187,7 +7193,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
         <v>84</v>
@@ -7198,7 +7204,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7209,10 +7215,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7220,10 +7226,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7231,10 +7237,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7242,10 +7248,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7253,10 +7259,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7264,10 +7270,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7275,10 +7281,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7286,7 +7292,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -7297,7 +7303,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -7308,7 +7314,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -7319,7 +7325,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C15" t="s">
         <v>84</v>
@@ -7330,7 +7336,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -7341,7 +7347,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -7352,7 +7358,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -7363,10 +7369,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7374,7 +7380,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -7385,7 +7391,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -7396,10 +7402,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7418,7 +7424,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C24">
         <v>86</v>
@@ -7429,7 +7435,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C25">
         <v>456</v>
@@ -7440,7 +7446,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C26">
         <v>74</v>
@@ -7451,7 +7457,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
@@ -7462,7 +7468,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -7473,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C29" t="s">
         <v>84</v>
@@ -7484,7 +7490,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -7495,7 +7501,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C31" t="s">
         <v>84</v>
@@ -7528,7 +7534,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -7539,7 +7545,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -7550,7 +7556,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -7561,7 +7567,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -7572,7 +7578,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7583,7 +7589,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -7594,7 +7600,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -7605,10 +7611,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C41" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7616,7 +7622,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C42">
         <v>400</v>
@@ -7627,7 +7633,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7638,7 +7644,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -7697,7 +7703,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -7708,10 +7714,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7719,10 +7725,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7730,10 +7736,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7741,10 +7747,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7752,10 +7758,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7763,10 +7769,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7774,10 +7780,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -7821,7 +7827,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
         <v>84</v>
@@ -7832,7 +7838,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7843,10 +7849,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7854,10 +7860,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7865,10 +7871,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7876,10 +7882,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7887,10 +7893,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7898,10 +7904,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7909,7 +7915,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C11" s="12">
         <v>1234</v>
@@ -7920,7 +7926,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -7931,7 +7937,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C13">
         <v>-466</v>
@@ -7942,7 +7948,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C14">
         <v>-500</v>
@@ -7953,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C15">
         <v>-400</v>
@@ -7975,7 +7981,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C17">
         <v>-200</v>
@@ -7986,7 +7992,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C18">
         <v>-456</v>
@@ -7997,7 +8003,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C19">
         <v>-74</v>
@@ -8008,7 +8014,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -8019,7 +8025,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -8030,7 +8036,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C22">
         <v>-400</v>
@@ -8041,7 +8047,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C23">
         <v>-200</v>
@@ -8052,7 +8058,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C24">
         <v>-100</v>
@@ -8063,7 +8069,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C25">
         <v>-200</v>
@@ -8074,7 +8080,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C26">
         <v>-50</v>
@@ -8085,7 +8091,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C27">
         <v>-400</v>
@@ -8096,7 +8102,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C28">
         <v>-200</v>
@@ -8107,7 +8113,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C29">
         <v>-100</v>
@@ -8118,7 +8124,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C30">
         <v>-200</v>
@@ -8129,7 +8135,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -8225,7 +8231,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8236,10 +8242,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8247,7 +8253,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -8258,10 +8264,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8269,10 +8275,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8280,10 +8286,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8291,10 +8297,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8302,10 +8308,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8313,10 +8319,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8324,10 +8330,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8335,7 +8341,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -8346,7 +8352,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -8357,7 +8363,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -8368,7 +8374,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C15">
         <v>500</v>
@@ -8379,10 +8385,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8390,7 +8396,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C17">
         <v>1000</v>
@@ -8401,7 +8407,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C18">
         <v>700</v>
@@ -8412,10 +8418,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8423,10 +8429,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8434,7 +8440,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C21">
         <v>1234</v>
@@ -8445,10 +8451,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C22" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8456,7 +8462,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C23" t="s">
         <v>84</v>
@@ -8467,7 +8473,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C24" t="s">
         <v>84</v>
@@ -8489,7 +8495,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C26">
         <v>85</v>
@@ -8500,7 +8506,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -8511,7 +8517,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C28">
         <v>76</v>
@@ -8522,7 +8528,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>45</v>
@@ -8533,7 +8539,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>45</v>
@@ -8544,10 +8550,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C31" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8555,7 +8561,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>45</v>
@@ -8569,7 +8575,7 @@
         <v>83</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8577,7 +8583,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>26</v>
@@ -8588,7 +8594,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>26</v>
@@ -8599,7 +8605,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>26</v>
@@ -8635,7 +8641,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8646,7 +8652,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -8657,10 +8663,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8668,10 +8674,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8679,10 +8685,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8690,10 +8696,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8701,10 +8707,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8712,10 +8718,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8723,10 +8729,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -8759,7 +8765,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C2" s="3">
         <v>1234</v>
@@ -8770,7 +8776,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C3" s="3">
         <v>123</v>
@@ -8781,10 +8787,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8792,10 +8798,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8803,10 +8809,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8814,10 +8820,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8825,10 +8831,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8836,10 +8842,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8847,7 +8853,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" s="15">
         <v>12345</v>
@@ -8858,7 +8864,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C11" s="3">
         <v>-500</v>
@@ -8869,7 +8875,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C12" s="3">
         <v>-1000</v>
@@ -8880,7 +8886,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C13" s="3">
         <v>-700</v>
@@ -8902,7 +8908,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C15" s="3">
         <v>-85</v>
@@ -8913,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C16" s="3">
         <v>-200</v>
@@ -8924,7 +8930,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C17" s="3">
         <v>-76</v>
@@ -8935,7 +8941,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>45</v>
@@ -8946,7 +8952,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>45</v>
@@ -8957,10 +8963,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8968,10 +8974,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8979,10 +8985,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8990,10 +8996,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -9016,7 +9022,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9027,10 +9033,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9038,10 +9044,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9049,10 +9055,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9060,7 +9066,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C5" s="3">
         <v>1234</v>
@@ -9071,7 +9077,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C6" s="3">
         <v>8967589</v>
@@ -9082,7 +9088,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C7" s="3">
         <v>34567</v>
@@ -9093,7 +9099,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C8" s="3">
         <v>50</v>
@@ -9104,7 +9110,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C9" s="3">
         <v>100</v>
@@ -9115,10 +9121,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9126,7 +9132,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
@@ -9137,10 +9143,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9148,10 +9154,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9159,10 +9165,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9170,10 +9176,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9181,10 +9187,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9192,10 +9198,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9203,10 +9209,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9214,7 +9220,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C19" s="3">
         <v>123</v>
@@ -9225,10 +9231,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9236,10 +9242,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9247,10 +9253,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9258,10 +9264,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9269,10 +9275,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9280,10 +9286,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9291,10 +9297,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9302,10 +9308,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9313,10 +9319,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9324,7 +9330,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C29" s="3">
         <v>75</v>
@@ -9335,7 +9341,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
@@ -9346,7 +9352,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C31" s="3">
         <v>85</v>
@@ -9357,7 +9363,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C32" s="3">
         <v>55</v>
@@ -9368,7 +9374,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>5</v>
@@ -9379,10 +9385,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9390,7 +9396,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -9401,10 +9407,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9412,10 +9418,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9423,10 +9429,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9434,10 +9440,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9445,10 +9451,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9456,10 +9462,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9467,7 +9473,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C42" s="3">
         <v>9869875890</v>
@@ -9478,10 +9484,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9489,7 +9495,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C44" s="3">
         <v>20</v>
@@ -9500,10 +9506,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9511,10 +9517,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9522,10 +9528,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9533,10 +9539,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9544,10 +9550,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9555,7 +9561,7 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C50" s="3">
         <v>9869875890</v>
@@ -9580,7 +9586,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9591,10 +9597,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9602,10 +9608,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9613,10 +9619,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9624,7 +9630,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C5" s="3">
         <v>50</v>
@@ -9635,7 +9641,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C6" s="3">
         <v>100</v>
@@ -9646,10 +9652,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9657,7 +9663,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C8" s="3">
         <v>123</v>
@@ -9668,10 +9674,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9679,10 +9685,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9690,10 +9696,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9701,10 +9707,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9712,10 +9718,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9723,7 +9729,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3">
         <v>12345</v>
@@ -9734,10 +9740,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9745,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C16" s="3">
         <v>123</v>
@@ -9756,10 +9762,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9767,10 +9773,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9778,10 +9784,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9789,10 +9795,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9800,10 +9806,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9811,7 +9817,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C22" s="3">
         <v>12345</v>
@@ -9822,10 +9828,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9833,10 +9839,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9844,10 +9850,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9855,7 +9861,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C26" s="3">
         <v>-75</v>
@@ -9866,7 +9872,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C27" s="3">
         <v>-65</v>
@@ -9877,7 +9883,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C28" s="3">
         <v>-85</v>
@@ -9888,7 +9894,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C29" s="3">
         <v>-55</v>
@@ -9899,10 +9905,10 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9910,7 +9916,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -9921,10 +9927,10 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9932,7 +9938,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C33" s="3">
         <v>20</v>
@@ -10221,7 +10227,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>42</v>
@@ -10232,7 +10238,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>41</v>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799A7C7F-BA7F-49DE-9F9B-D63FCA5B6AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41A13B0-3CD7-47A2-B0D4-D444B9D245D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="13" activeTab="18" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="31" activeTab="34" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="347">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -309,105 +309,33 @@
     <t>fieldRequestFederalAgencyDispositionInstr__c</t>
   </si>
   <si>
-    <t>fieldOther__c</t>
-  </si>
-  <si>
-    <t>fieldRequestApprovalSF428C__c</t>
-  </si>
-  <si>
-    <t>fieldRequestApproval2SF428C__c</t>
-  </si>
-  <si>
-    <t>fieldRequestUnconditionalTransferSF428C__c</t>
-  </si>
-  <si>
-    <t>fieldRequestAcquiredEquipmentSF428C__c</t>
-  </si>
-  <si>
-    <t>fieldRetentionAcquiredEquipmentSF428C__c</t>
-  </si>
-  <si>
-    <t>fieldSaleAcquiredEquipmentSF428C__c</t>
-  </si>
-  <si>
-    <t>fieldSaleProceedsrEstimateofCurrentFai__c</t>
-  </si>
-  <si>
     <t>(i) Sale Proceeds OR</t>
   </si>
   <si>
-    <t>fieldSaleProceedsMarketValue__c</t>
-  </si>
-  <si>
-    <t>fieldPercentageofFederalParticipation__c</t>
-  </si>
-  <si>
     <t>fieldFederalShare__c</t>
   </si>
   <si>
-    <t>fieldSellingandHandlingAllowance__c</t>
-  </si>
-  <si>
-    <t>fieldReportLoss__c</t>
-  </si>
-  <si>
     <t>fieldComments__c</t>
   </si>
   <si>
     <t>Automation Test</t>
   </si>
   <si>
-    <t>fieldAgencyresponsetorequested__c</t>
-  </si>
-  <si>
     <t>(i) Recipient request approved</t>
   </si>
   <si>
-    <t>fieldAgencyresponse__c</t>
-  </si>
-  <si>
-    <t>fieldDisposeinaccordance__c</t>
-  </si>
-  <si>
-    <t>fieldDisposeinaccordancewithattached__c</t>
-  </si>
-  <si>
-    <t>fieldAORSignature__c</t>
-  </si>
-  <si>
     <t>John Mathews</t>
   </si>
   <si>
-    <t>fieldAcquisitionDateSF428A__c</t>
-  </si>
-  <si>
-    <t>fieldName428B__c</t>
-  </si>
-  <si>
     <t>fieldTelephone2__c</t>
   </si>
   <si>
-    <t>fieldTitle__c</t>
-  </si>
-  <si>
-    <t>fieldEmailAddress__c</t>
-  </si>
-  <si>
     <t>automation@yopmail.com</t>
   </si>
   <si>
     <t>fieldFederalAgencySF428__c</t>
   </si>
   <si>
-    <t>fieldReportType__c</t>
-  </si>
-  <si>
-    <t>fieldBasisOfAccounting__c</t>
-  </si>
-  <si>
-    <t>fieldAcquiredDate__c</t>
-  </si>
-  <si>
     <t>fieldAORDateSubmitted__c</t>
   </si>
   <si>
@@ -516,45 +444,9 @@
     <t>New York</t>
   </si>
   <si>
-    <t>fieldFederalAgencyandOrganizationalSF429__c</t>
-  </si>
-  <si>
-    <t>fieldDate__c</t>
-  </si>
-  <si>
-    <t>fieldAnnualReportSF428A__c</t>
-  </si>
-  <si>
-    <t>fieldFinalReportSF428B__c</t>
-  </si>
-  <si>
-    <t>fieldDispositionReportRequestSF428C__c</t>
-  </si>
-  <si>
-    <t>fieldFederalAwardNumber__c</t>
-  </si>
-  <si>
-    <t>fieldGPACQ__c</t>
-  </si>
-  <si>
     <t>ACQ</t>
   </si>
   <si>
-    <t>fieldDescription__c</t>
-  </si>
-  <si>
-    <t>fieldIdentificationNumber__c</t>
-  </si>
-  <si>
-    <t>fieldConditionCode__c</t>
-  </si>
-  <si>
-    <t>fieldAcquisitionCost__c</t>
-  </si>
-  <si>
-    <t>fieldDispositionRequest__c</t>
-  </si>
-  <si>
     <t>eulkelendwdrgyethmgfmewoi</t>
   </si>
   <si>
@@ -567,30 +459,15 @@
     <t>gefakzgrpvjjbdneasuz</t>
   </si>
   <si>
-    <t>fieldFederallyownedProperty__c</t>
-  </si>
-  <si>
-    <t>fieldAcquiredEquipment__c</t>
-  </si>
-  <si>
-    <t>fieldResidualUnusedSupplies__c</t>
-  </si>
-  <si>
     <t>fieldRequestTransfertoAward__c</t>
   </si>
   <si>
     <t>fieldFederalAwardIdentifier__c</t>
   </si>
   <si>
-    <t>fieldRequestFederalAgency__c</t>
-  </si>
-  <si>
     <t>fieldAcknowledgeEquipment__c</t>
   </si>
   <si>
-    <t>fieldTotalAmount__c</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
@@ -606,66 +483,21 @@
     <t>Health</t>
   </si>
   <si>
-    <t>fieldRecipientAccountNumberSF428__c</t>
-  </si>
-  <si>
     <t>fieldSupplementalSheet__c</t>
   </si>
   <si>
     <t>fieldCommentsSF428__c</t>
   </si>
   <si>
-    <t>fieldDateReportSubmittedSF428__c</t>
-  </si>
-  <si>
-    <t>fieldAgencyCommentsSF428__c</t>
-  </si>
-  <si>
     <t>fieldFederalGrantSF428A__c</t>
   </si>
   <si>
-    <t>fieldReportTypePiclikist__c</t>
-  </si>
-  <si>
     <t>(a) Individual (Reporting Federally-owned property for one award)</t>
   </si>
   <si>
-    <t>fieldReportAsOf__c</t>
-  </si>
-  <si>
-    <t>fieldSEP30__c</t>
-  </si>
-  <si>
-    <t>fieldName</t>
-  </si>
-  <si>
-    <t>fieldIdentification__c</t>
-  </si>
-  <si>
-    <t>fieldAcquisitionDate__c</t>
-  </si>
-  <si>
     <t>30 SEP</t>
   </si>
   <si>
-    <t>fieldFederalGrantIdentifyingNumberSF429__c</t>
-  </si>
-  <si>
-    <t>fieldRecipientOrganizationNameSF429__c</t>
-  </si>
-  <si>
-    <t>fieldReportEndDate__c</t>
-  </si>
-  <si>
-    <t>fieldAttachmentA__c</t>
-  </si>
-  <si>
-    <t>fieldAttachmentB__c</t>
-  </si>
-  <si>
-    <t>fieldAttachmentC__c</t>
-  </si>
-  <si>
     <t>Automation test</t>
   </si>
   <si>
@@ -681,15 +513,9 @@
     <t>fieldTypeorPrintedLastName__c</t>
   </si>
   <si>
-    <t>fieldTypeorPrintedSuffix__c</t>
-  </si>
-  <si>
     <t>fieldTypeorPrintedTitle__c</t>
   </si>
   <si>
-    <t>fieldEmailAddress2__c</t>
-  </si>
-  <si>
     <t>fieldPeriodStartDate__c</t>
   </si>
   <si>
@@ -1006,6 +832,294 @@
   </si>
   <si>
     <t>InternalOrganization__c</t>
+  </si>
+  <si>
+    <t>FederalGrantIdentifyingNumbe__c</t>
+  </si>
+  <si>
+    <t>RequestFederalAgencyDispositionInstr__c</t>
+  </si>
+  <si>
+    <t>Other__c</t>
+  </si>
+  <si>
+    <t>RequestApprovalSF428C__c</t>
+  </si>
+  <si>
+    <t>RequestApproval2SF428C__c</t>
+  </si>
+  <si>
+    <t>RequestUnconditionalTransferSF428C__c</t>
+  </si>
+  <si>
+    <t>RequestAcquiredEquipmentSF428C__c</t>
+  </si>
+  <si>
+    <t>RetentionAcquiredEquipmentSF428C__c</t>
+  </si>
+  <si>
+    <t>SaleAcquiredEquipmentSF428C__c</t>
+  </si>
+  <si>
+    <t>SaleProceedsrEstimateofCurrentFai__c</t>
+  </si>
+  <si>
+    <t>SaleProceedsMarketValue__c</t>
+  </si>
+  <si>
+    <t>PercentageofFederalParticipation__c</t>
+  </si>
+  <si>
+    <t>FederalShare__c</t>
+  </si>
+  <si>
+    <t>SellingandHandlingAllowance__c</t>
+  </si>
+  <si>
+    <t>ReportLoss__c</t>
+  </si>
+  <si>
+    <t>Comments__c</t>
+  </si>
+  <si>
+    <t>Agencyresponsetorequested__c</t>
+  </si>
+  <si>
+    <t>Agencyresponse__c</t>
+  </si>
+  <si>
+    <t>Disposeinaccordance__c</t>
+  </si>
+  <si>
+    <t>Disposeinaccordancewithattached__c</t>
+  </si>
+  <si>
+    <t>AORSignature__c</t>
+  </si>
+  <si>
+    <t>AcquisitionDateSF428A__c</t>
+  </si>
+  <si>
+    <t>Name428B__c</t>
+  </si>
+  <si>
+    <t>Telephone2__c</t>
+  </si>
+  <si>
+    <t>Title__c</t>
+  </si>
+  <si>
+    <t>EmailAddress__c</t>
+  </si>
+  <si>
+    <t>FederalAgencySF428__c</t>
+  </si>
+  <si>
+    <t>ReportType__c</t>
+  </si>
+  <si>
+    <t>BasisOfAccounting__c</t>
+  </si>
+  <si>
+    <t>AcquiredDate__c</t>
+  </si>
+  <si>
+    <t>AORDateSubmitted__c</t>
+  </si>
+  <si>
+    <t>RecipientOrganizationNameSF428__c</t>
+  </si>
+  <si>
+    <t>Street1SF428__c</t>
+  </si>
+  <si>
+    <t>Street2SF428__c</t>
+  </si>
+  <si>
+    <t>CitySF428__c</t>
+  </si>
+  <si>
+    <t>CountySF428__c</t>
+  </si>
+  <si>
+    <t>StateSf428__c</t>
+  </si>
+  <si>
+    <t>ProvinceSF428__c</t>
+  </si>
+  <si>
+    <t>CountrySF428__c</t>
+  </si>
+  <si>
+    <t>ZipPostalCodeSF428__c</t>
+  </si>
+  <si>
+    <t>Remark__c</t>
+  </si>
+  <si>
+    <t>AcknowledgementSF428__c</t>
+  </si>
+  <si>
+    <t>Prefix__c</t>
+  </si>
+  <si>
+    <t>FirstNameSF428__c</t>
+  </si>
+  <si>
+    <t>MiddleNameSF428__c</t>
+  </si>
+  <si>
+    <t>LastNameSF428__c</t>
+  </si>
+  <si>
+    <t>Suffix__c</t>
+  </si>
+  <si>
+    <t>TitleSF429__c</t>
+  </si>
+  <si>
+    <t>SubmittedBySF428__c</t>
+  </si>
+  <si>
+    <t>Telephone__c</t>
+  </si>
+  <si>
+    <t>SubmittedOn__c</t>
+  </si>
+  <si>
+    <t>FederalAgencyandOrganizationalSF429__c</t>
+  </si>
+  <si>
+    <t>Date__c</t>
+  </si>
+  <si>
+    <t>AnnualReportSF428A__c</t>
+  </si>
+  <si>
+    <t>FinalReportSF428B__c</t>
+  </si>
+  <si>
+    <t>DispositionReportRequestSF428C__c</t>
+  </si>
+  <si>
+    <t>FederalAwardNumber__c</t>
+  </si>
+  <si>
+    <t>GPACQ__c</t>
+  </si>
+  <si>
+    <t>IdentificationNumber__c</t>
+  </si>
+  <si>
+    <t>ConditionCode__c</t>
+  </si>
+  <si>
+    <t>AcquisitionCost__c</t>
+  </si>
+  <si>
+    <t>DispositionRequest__c</t>
+  </si>
+  <si>
+    <t>FederallyownedProperty__c</t>
+  </si>
+  <si>
+    <t>AcquiredEquipment__c</t>
+  </si>
+  <si>
+    <t>ResidualUnusedSupplies__c</t>
+  </si>
+  <si>
+    <t>RequestTransfertoAward__c</t>
+  </si>
+  <si>
+    <t>FederalAwardIdentifier__c</t>
+  </si>
+  <si>
+    <t>RequestFederalAgency__c</t>
+  </si>
+  <si>
+    <t>AcknowledgeEquipment__c</t>
+  </si>
+  <si>
+    <t>TotalAmount__c</t>
+  </si>
+  <si>
+    <t>FederalGrantIdentifyingNumberSF428__c</t>
+  </si>
+  <si>
+    <t>RecipientAccountNumberSF428__c</t>
+  </si>
+  <si>
+    <t>SupplementalSheet__c</t>
+  </si>
+  <si>
+    <t>CommentsSF428__c</t>
+  </si>
+  <si>
+    <t>DateReportSubmittedSF428__c</t>
+  </si>
+  <si>
+    <t>AgencyCommentsSF428__c</t>
+  </si>
+  <si>
+    <t>FederalGrantSF428A__c</t>
+  </si>
+  <si>
+    <t>ReportTypePiclikist__c</t>
+  </si>
+  <si>
+    <t>ReportAsOf__c</t>
+  </si>
+  <si>
+    <t>SEP30__c</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Identification__c</t>
+  </si>
+  <si>
+    <t>AcquisitionDate__c</t>
+  </si>
+  <si>
+    <t>FederalGrantIdentifyingNumberSF429__c</t>
+  </si>
+  <si>
+    <t>RecipientOrganizationNameSF429__c</t>
+  </si>
+  <si>
+    <t>ReportEndDate__c</t>
+  </si>
+  <si>
+    <t>AttachmentA__c</t>
+  </si>
+  <si>
+    <t>AttachmentB__c</t>
+  </si>
+  <si>
+    <t>AttachmentC__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedPrefix__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedFirstName__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedMiddleName__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedLastName__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedSuffix__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedTitle__c</t>
+  </si>
+  <si>
+    <t>EmailAddress2__c</t>
   </si>
 </sst>
 </file>
@@ -1015,7 +1129,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00;[Red]0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1066,6 +1180,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF454545"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1087,7 +1207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1114,6 +1234,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1566,7 +1687,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>32</v>
@@ -1577,7 +1698,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>33</v>
@@ -1657,7 +1778,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>34</v>
@@ -1668,7 +1789,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>36</v>
@@ -1767,7 +1888,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>304</v>
+        <v>246</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1778,7 +1899,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>305</v>
+        <v>247</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -1847,7 +1968,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>304</v>
+        <v>246</v>
       </c>
       <c r="C5" s="3">
         <v>-2</v>
@@ -1858,7 +1979,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>305</v>
+        <v>247</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>20</v>
@@ -1916,7 +2037,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>304</v>
+        <v>246</v>
       </c>
       <c r="C4" s="3">
         <v>-2</v>
@@ -1927,7 +2048,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>305</v>
+        <v>247</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>20</v>
@@ -2018,7 +2139,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>250</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
@@ -2291,7 +2412,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>308</v>
+        <v>250</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
@@ -2404,7 +2525,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>308</v>
+        <v>250</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
@@ -2462,7 +2583,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2473,7 +2594,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2484,7 +2605,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2495,7 +2616,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>254</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2506,7 +2627,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>255</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2517,7 +2638,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2528,7 +2649,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2539,7 +2660,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>258</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2550,7 +2671,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2561,10 +2682,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>260</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2572,7 +2693,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>261</v>
       </c>
       <c r="C12" s="10">
         <v>9999.99</v>
@@ -2583,7 +2704,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>262</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -2594,7 +2715,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>263</v>
       </c>
       <c r="C14" s="10">
         <v>9999.99</v>
@@ -2605,7 +2726,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="C15" s="10">
         <v>1000</v>
@@ -2616,7 +2737,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>265</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>5</v>
@@ -2627,10 +2748,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>266</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2638,10 +2759,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>267</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2649,10 +2770,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>268</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2660,7 +2781,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>269</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>5</v>
@@ -2671,7 +2792,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>270</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>5</v>
@@ -2682,10 +2803,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>271</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2693,7 +2814,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>272</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2704,10 +2825,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>273</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2715,7 +2836,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="C25">
         <v>8967045891</v>
@@ -2726,10 +2847,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2737,10 +2858,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2856,7 +2977,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2892,7 +3013,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2903,7 +3024,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2914,7 +3035,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2925,7 +3046,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>254</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2936,7 +3057,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>255</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2947,7 +3068,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2958,7 +3079,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2969,7 +3090,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>258</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2980,7 +3101,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2991,7 +3112,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>265</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>5</v>
@@ -3002,10 +3123,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>267</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3013,10 +3134,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>268</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3024,7 +3145,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>269</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -3035,7 +3156,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>270</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -3046,10 +3167,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>271</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3057,7 +3178,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>272</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3068,10 +3189,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>273</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3079,7 +3200,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="C19">
         <v>8967045891</v>
@@ -3090,10 +3211,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3101,10 +3222,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3137,10 +3258,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>277</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3148,10 +3269,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3159,10 +3280,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>278</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3170,10 +3291,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>279</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3181,7 +3302,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>280</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -3192,7 +3313,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>272</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -3203,7 +3324,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>281</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3214,10 +3335,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>282</v>
       </c>
       <c r="C9" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3225,7 +3346,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3236,10 +3357,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3247,10 +3368,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="C12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3258,10 +3379,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3269,10 +3390,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3280,10 +3401,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3291,10 +3412,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>289</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3302,10 +3423,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>290</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3313,10 +3434,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>291</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3324,7 +3445,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>292</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3335,10 +3456,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>125</v>
+        <v>293</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3346,10 +3467,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3357,10 +3478,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>295</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3368,10 +3489,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>131</v>
+        <v>296</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3379,10 +3500,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3390,10 +3511,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>298</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3401,10 +3522,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>299</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3412,7 +3533,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="C27">
         <v>2122342342</v>
@@ -3423,10 +3544,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3434,7 +3555,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
+        <v>301</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3471,10 +3592,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>302</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3482,10 +3603,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>282</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3493,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>303</v>
       </c>
       <c r="C4" s="11">
         <v>50</v>
@@ -3533,7 +3654,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="C2">
         <v>64789390</v>
@@ -3544,7 +3665,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>147</v>
+        <v>304</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3555,7 +3676,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>148</v>
+        <v>305</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3566,7 +3687,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>149</v>
+        <v>306</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3602,10 +3723,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>150</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3613,10 +3734,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>151</v>
+        <v>308</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3624,10 +3745,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3635,10 +3756,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>154</v>
+        <v>309</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3646,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>108</v>
+        <v>280</v>
       </c>
       <c r="C6" s="3">
         <v>25</v>
@@ -3657,10 +3778,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3668,7 +3789,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>156</v>
+        <v>311</v>
       </c>
       <c r="C8" s="13">
         <v>9999.99</v>
@@ -3679,10 +3800,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>157</v>
+        <v>312</v>
       </c>
       <c r="C9" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3716,7 +3837,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -3727,7 +3848,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>313</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3738,7 +3859,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>314</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3749,7 +3870,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>315</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3760,7 +3881,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>316</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -3771,10 +3892,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>317</v>
       </c>
       <c r="C7" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3782,7 +3903,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>318</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -3793,7 +3914,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -3804,7 +3925,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>168</v>
+        <v>319</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -3815,7 +3936,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -3826,10 +3947,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>260</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3837,7 +3958,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>320</v>
       </c>
       <c r="C13">
         <v>85</v>
@@ -3848,7 +3969,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>262</v>
       </c>
       <c r="C14">
         <v>85</v>
@@ -3859,7 +3980,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>263</v>
       </c>
       <c r="C15">
         <v>9999.99</v>
@@ -3870,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="C16">
         <v>9999.99</v>
@@ -3881,10 +4002,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>266</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3892,10 +4013,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>267</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3903,10 +4024,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>268</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3914,7 +4035,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>269</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -3925,7 +4046,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>270</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -3936,10 +4057,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>271</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3947,7 +4068,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>272</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3958,10 +4079,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>273</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3969,7 +4090,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="C25">
         <v>9867589302</v>
@@ -3980,10 +4101,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="C26" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3991,10 +4112,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="C27" t="s">
-        <v>171</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -4028,7 +4149,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -4039,7 +4160,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>313</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -4050,7 +4171,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>314</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4061,7 +4182,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>315</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4072,7 +4193,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>316</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -4083,7 +4204,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>318</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -4094,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -4105,7 +4226,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>319</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -4116,7 +4237,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -4127,10 +4248,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>266</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4138,10 +4259,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>267</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4149,10 +4270,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>268</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4160,7 +4281,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>269</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4171,7 +4292,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>270</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4182,10 +4303,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>271</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4193,7 +4314,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>272</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -4204,10 +4325,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>273</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4215,7 +4336,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="C19">
         <v>9867589302</v>
@@ -4226,10 +4347,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="C20" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4237,10 +4358,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="C21" t="s">
-        <v>171</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -4274,10 +4395,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>277</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4285,7 +4406,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>321</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4296,10 +4417,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>282</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4307,7 +4428,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4318,10 +4439,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4329,10 +4450,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4340,10 +4461,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4351,10 +4472,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4362,10 +4483,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4373,10 +4494,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>289</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4384,10 +4505,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>290</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4395,7 +4516,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>322</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4406,7 +4527,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>304</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4417,7 +4538,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>305</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4428,7 +4549,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>306</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -4439,7 +4560,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>176</v>
+        <v>323</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
@@ -4450,10 +4571,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>177</v>
+        <v>324</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4461,10 +4582,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>125</v>
+        <v>293</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4472,10 +4593,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4483,10 +4604,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>295</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4494,10 +4615,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>296</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4505,10 +4626,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4516,10 +4637,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>298</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4527,10 +4648,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>137</v>
+        <v>299</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4538,7 +4659,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="C26">
         <v>2122342342</v>
@@ -4549,10 +4670,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4560,7 +4681,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>178</v>
+        <v>325</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4571,10 +4692,10 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>179</v>
+        <v>326</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4608,10 +4729,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>277</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4619,7 +4740,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>321</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4630,10 +4751,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>282</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4641,7 +4762,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4652,10 +4773,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4663,10 +4784,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4674,10 +4795,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4685,10 +4806,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4696,10 +4817,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4707,10 +4828,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>289</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4718,10 +4839,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>290</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4729,7 +4850,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>322</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4740,7 +4861,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>176</v>
+        <v>323</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
@@ -4751,10 +4872,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>324</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4762,10 +4883,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>125</v>
+        <v>293</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4773,10 +4894,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4784,10 +4905,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>295</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4795,10 +4916,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>296</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4806,10 +4927,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4817,10 +4938,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
+        <v>298</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4828,10 +4949,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>137</v>
+        <v>299</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4839,7 +4960,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="C23">
         <v>2122342342</v>
@@ -4850,10 +4971,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4861,7 +4982,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>178</v>
+        <v>325</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -4872,10 +4993,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>179</v>
+        <v>326</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4967,10 +5088,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>277</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4978,7 +5099,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>321</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4989,10 +5110,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>282</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5000,7 +5121,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5011,10 +5132,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5022,10 +5143,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5033,10 +5154,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5044,10 +5165,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5055,10 +5176,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5066,10 +5187,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>289</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5077,10 +5198,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>290</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5088,7 +5209,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>322</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -5099,7 +5220,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>304</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -5110,7 +5231,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>305</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -5121,7 +5242,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>306</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -5132,10 +5253,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>177</v>
+        <v>324</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5143,10 +5264,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>293</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5154,10 +5275,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5165,10 +5286,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>295</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5176,10 +5297,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>131</v>
+        <v>296</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5187,10 +5308,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5198,10 +5319,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>135</v>
+        <v>298</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5209,10 +5330,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>137</v>
+        <v>299</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5220,7 +5341,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="C25">
         <v>2122342342</v>
@@ -5231,10 +5352,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5242,7 +5363,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>178</v>
+        <v>325</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5253,10 +5374,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>179</v>
+        <v>326</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -5289,7 +5410,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>180</v>
+        <v>327</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -5300,10 +5421,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>181</v>
+        <v>328</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5311,10 +5432,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>183</v>
+        <v>329</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>188</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5322,7 +5443,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>184</v>
+        <v>330</v>
       </c>
       <c r="C5">
         <v>1111</v>
@@ -5333,10 +5454,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>177</v>
+        <v>324</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -5369,10 +5490,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>331</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5380,10 +5501,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5391,7 +5512,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>186</v>
+        <v>332</v>
       </c>
       <c r="C4">
         <v>76578</v>
@@ -5402,7 +5523,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>187</v>
+        <v>333</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -5413,7 +5534,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>156</v>
+        <v>311</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -5449,10 +5570,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>145</v>
+        <v>302</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>172</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5460,7 +5581,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>189</v>
+        <v>334</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5471,10 +5592,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>190</v>
+        <v>335</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5482,7 +5603,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5493,10 +5614,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5504,10 +5625,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5515,10 +5636,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5526,10 +5647,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5537,10 +5658,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5548,10 +5669,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>119</v>
+        <v>289</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5559,10 +5680,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>121</v>
+        <v>290</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5570,10 +5691,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>125</v>
+        <v>293</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5581,10 +5702,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5592,10 +5713,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>129</v>
+        <v>295</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5603,10 +5724,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>131</v>
+        <v>296</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5614,10 +5735,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5625,10 +5746,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5636,7 +5757,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -5647,7 +5768,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>191</v>
+        <v>336</v>
       </c>
       <c r="C20">
         <v>150</v>
@@ -5658,7 +5779,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
@@ -5669,7 +5790,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>193</v>
+        <v>338</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
@@ -5680,7 +5801,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>194</v>
+        <v>339</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -5691,10 +5812,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>177</v>
+        <v>324</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>195</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5702,7 +5823,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>124</v>
+        <v>292</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -5713,10 +5834,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>196</v>
+        <v>340</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5724,10 +5845,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>197</v>
+        <v>341</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5735,10 +5856,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>198</v>
+        <v>342</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5746,10 +5867,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>199</v>
+        <v>343</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5757,10 +5878,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>200</v>
+        <v>344</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5768,10 +5889,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>201</v>
+        <v>345</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5779,10 +5900,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>137</v>
+        <v>299</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5790,7 +5911,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="C33" s="15">
         <v>2122342342</v>
@@ -5801,10 +5922,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>202</v>
+        <v>346</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5812,7 +5933,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>178</v>
+        <v>325</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5823,7 +5944,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>177</v>
+        <v>324</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -5836,14 +5957,14 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E20211-1D84-48FF-8A84-AC0AE11DA487}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5854,169 +5975,170 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>145</v>
+        <v>302</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>131</v>
+      </c>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>189</v>
+        <v>334</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>190</v>
+        <v>335</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>119</v>
+        <v>289</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>121</v>
+        <v>290</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>125</v>
+        <v>293</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>129</v>
+        <v>295</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>131</v>
+        <v>296</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6024,10 +6146,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6035,10 +6157,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6046,7 +6168,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -6057,10 +6179,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>196</v>
+        <v>340</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6068,10 +6190,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>197</v>
+        <v>341</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6079,10 +6201,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>198</v>
+        <v>342</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6090,10 +6212,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>199</v>
+        <v>343</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6101,10 +6223,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>200</v>
+        <v>344</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6112,10 +6234,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>201</v>
+        <v>345</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6123,10 +6245,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>137</v>
+        <v>299</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6134,7 +6256,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="C27" s="15">
         <v>2122342342</v>
@@ -6145,10 +6267,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>202</v>
+        <v>346</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6156,7 +6278,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>178</v>
+        <v>325</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6192,7 +6314,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6203,7 +6325,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -6214,7 +6336,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -6225,10 +6347,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>205</v>
+        <v>147</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>206</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6236,10 +6358,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6247,7 +6369,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C7">
         <v>123</v>
@@ -6258,10 +6380,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6269,10 +6391,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6280,10 +6402,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6291,10 +6413,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6302,10 +6424,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6313,10 +6435,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6324,10 +6446,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6335,7 +6457,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>209</v>
+        <v>151</v>
       </c>
       <c r="C15">
         <v>1234</v>
@@ -6346,7 +6468,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="C16">
         <v>48</v>
@@ -6357,7 +6479,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="C17">
         <v>35</v>
@@ -6368,7 +6490,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -6379,10 +6501,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>213</v>
+        <v>155</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6390,7 +6512,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -6401,7 +6523,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6412,10 +6534,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>217</v>
+        <v>159</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>218</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6423,7 +6545,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -6434,7 +6556,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C24">
         <v>789</v>
@@ -6445,7 +6567,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>220</v>
+        <v>162</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -6456,7 +6578,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="C26">
         <v>456</v>
@@ -6467,7 +6589,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -6478,10 +6600,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>223</v>
+        <v>165</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>224</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6489,7 +6611,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
         <v>51</v>
@@ -6500,7 +6622,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="C30" t="s">
         <v>51</v>
@@ -6511,7 +6633,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="C31" t="s">
         <v>51</v>
@@ -6522,7 +6644,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -6533,10 +6655,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6544,7 +6666,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>229</v>
+        <v>171</v>
       </c>
       <c r="C34" t="s">
         <v>45</v>
@@ -6555,10 +6677,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6566,10 +6688,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>231</v>
+        <v>173</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6577,7 +6699,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="C37">
         <v>10000</v>
@@ -6588,7 +6710,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>234</v>
+        <v>176</v>
       </c>
       <c r="C38">
         <v>8000</v>
@@ -6599,7 +6721,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="C39">
         <v>6000</v>
@@ -6610,7 +6732,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>236</v>
+        <v>178</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -6621,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="C41">
         <v>300</v>
@@ -6632,7 +6754,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>238</v>
+        <v>180</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -6643,10 +6765,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -6679,7 +6801,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6690,7 +6812,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -6701,10 +6823,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6712,10 +6834,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6723,10 +6845,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6734,10 +6856,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6745,10 +6867,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6756,10 +6878,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6767,7 +6889,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C10" s="12">
         <v>1234</v>
@@ -6778,7 +6900,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="C11">
         <v>-8</v>
@@ -6789,7 +6911,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="C12">
         <v>-300</v>
@@ -6800,7 +6922,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="C13">
         <v>-200</v>
@@ -6811,7 +6933,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -6822,7 +6944,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C15">
         <v>-818</v>
@@ -6833,7 +6955,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>220</v>
+        <v>162</v>
       </c>
       <c r="C16">
         <v>-8</v>
@@ -6844,7 +6966,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="C17">
         <v>-767</v>
@@ -6855,7 +6977,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -6866,7 +6988,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>223</v>
+        <v>165</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>45</v>
@@ -6877,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -6888,7 +7010,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -6899,7 +7021,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>229</v>
+        <v>171</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -6910,10 +7032,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>231</v>
+        <v>173</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6921,7 +7043,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="C24">
         <v>-1000</v>
@@ -6932,7 +7054,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>234</v>
+        <v>176</v>
       </c>
       <c r="C25">
         <v>-700</v>
@@ -6943,7 +7065,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="C26">
         <v>-500</v>
@@ -6954,7 +7076,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>236</v>
+        <v>178</v>
       </c>
       <c r="C27">
         <v>-300</v>
@@ -6965,7 +7087,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>241</v>
+        <v>183</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -6976,7 +7098,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="C29">
         <v>-150</v>
@@ -6987,7 +7109,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>238</v>
+        <v>180</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -6998,7 +7120,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>239</v>
+        <v>181</v>
       </c>
       <c r="C31">
         <v>-40</v>
@@ -7045,10 +7167,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7056,7 +7178,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7067,10 +7189,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7078,10 +7200,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7089,10 +7211,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7100,10 +7222,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7111,10 +7233,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7122,10 +7244,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7133,10 +7255,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7144,7 +7266,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>209</v>
+        <v>151</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -7155,7 +7277,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -7166,7 +7288,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -7177,10 +7299,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>242</v>
+        <v>184</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7188,7 +7310,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -7199,7 +7321,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -7210,7 +7332,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -7221,10 +7343,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>254</v>
+        <v>196</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7232,7 +7354,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -7243,7 +7365,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -7254,10 +7376,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>218</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7265,7 +7387,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C23">
         <v>789</v>
@@ -7276,7 +7398,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>220</v>
+        <v>162</v>
       </c>
       <c r="C24">
         <v>86</v>
@@ -7287,7 +7409,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="C25">
         <v>456</v>
@@ -7298,7 +7420,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="C26">
         <v>74</v>
@@ -7309,7 +7431,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
@@ -7320,7 +7442,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -7331,10 +7453,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>243</v>
+        <v>185</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7342,7 +7464,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -7353,10 +7475,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7386,7 +7508,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -7397,7 +7519,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -7408,7 +7530,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -7419,7 +7541,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>245</v>
+        <v>187</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -7430,7 +7552,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>246</v>
+        <v>188</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7441,7 +7563,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>247</v>
+        <v>189</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -7452,7 +7574,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>248</v>
+        <v>190</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -7463,10 +7585,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>249</v>
+        <v>191</v>
       </c>
       <c r="C41" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7474,7 +7596,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="C42">
         <v>400</v>
@@ -7485,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>252</v>
+        <v>194</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7496,7 +7618,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -7507,10 +7629,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C45" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -7555,7 +7677,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -7566,10 +7688,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7577,10 +7699,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7588,10 +7710,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7599,10 +7721,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7610,10 +7732,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7621,10 +7743,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7632,10 +7754,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -7679,10 +7801,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7690,7 +7812,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7701,10 +7823,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7712,10 +7834,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7723,10 +7845,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7734,10 +7856,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7745,10 +7867,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7756,10 +7878,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7767,7 +7889,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C11" s="12">
         <v>1234</v>
@@ -7778,7 +7900,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -7789,7 +7911,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="C13">
         <v>-466</v>
@@ -7800,7 +7922,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="C14">
         <v>-500</v>
@@ -7811,7 +7933,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="C15">
         <v>-400</v>
@@ -7822,7 +7944,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C16">
         <v>-789</v>
@@ -7833,7 +7955,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>220</v>
+        <v>162</v>
       </c>
       <c r="C17">
         <v>-200</v>
@@ -7844,7 +7966,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="C18">
         <v>-456</v>
@@ -7855,7 +7977,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="C19">
         <v>-74</v>
@@ -7866,7 +7988,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -7877,7 +7999,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -7888,7 +8010,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>245</v>
+        <v>187</v>
       </c>
       <c r="C22">
         <v>-400</v>
@@ -7899,7 +8021,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>265</v>
+        <v>207</v>
       </c>
       <c r="C23">
         <v>-200</v>
@@ -7910,7 +8032,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>246</v>
+        <v>188</v>
       </c>
       <c r="C24">
         <v>-100</v>
@@ -7921,7 +8043,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>247</v>
+        <v>189</v>
       </c>
       <c r="C25">
         <v>-200</v>
@@ -7932,7 +8054,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>248</v>
+        <v>190</v>
       </c>
       <c r="C26">
         <v>-50</v>
@@ -7943,7 +8065,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="C27">
         <v>-400</v>
@@ -7954,7 +8076,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="C28">
         <v>-200</v>
@@ -7965,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>252</v>
+        <v>194</v>
       </c>
       <c r="C29">
         <v>-100</v>
@@ -7976,7 +8098,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="C30">
         <v>-200</v>
@@ -7987,7 +8109,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>267</v>
+        <v>209</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -8083,7 +8205,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8094,10 +8216,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>256</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
-        <v>257</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8105,7 +8227,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -8116,10 +8238,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8127,10 +8249,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8138,10 +8260,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8149,10 +8271,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8160,10 +8282,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8171,10 +8293,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8182,10 +8304,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8193,7 +8315,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>209</v>
+        <v>151</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -8204,7 +8326,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -8215,7 +8337,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -8226,7 +8348,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="C15">
         <v>500</v>
@@ -8237,10 +8359,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>254</v>
+        <v>196</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>218</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8248,7 +8370,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="C17">
         <v>1000</v>
@@ -8259,7 +8381,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="C18">
         <v>700</v>
@@ -8270,10 +8392,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>218</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8281,10 +8403,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>258</v>
+        <v>200</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>259</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8292,7 +8414,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>260</v>
+        <v>202</v>
       </c>
       <c r="C21">
         <v>1234</v>
@@ -8303,10 +8425,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>261</v>
+        <v>203</v>
       </c>
       <c r="C22" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8314,10 +8436,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>262</v>
+        <v>204</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8325,10 +8447,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8336,7 +8458,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C25">
         <v>300</v>
@@ -8347,7 +8469,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>220</v>
+        <v>162</v>
       </c>
       <c r="C26">
         <v>85</v>
@@ -8358,7 +8480,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -8369,7 +8491,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="C28">
         <v>76</v>
@@ -8380,7 +8502,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>229</v>
+        <v>171</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>45</v>
@@ -8391,7 +8513,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>45</v>
@@ -8402,10 +8524,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>243</v>
+        <v>185</v>
       </c>
       <c r="C31" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8413,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>45</v>
@@ -8424,10 +8546,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8435,7 +8557,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>263</v>
+        <v>205</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>26</v>
@@ -8446,7 +8568,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>264</v>
+        <v>206</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>26</v>
@@ -8457,7 +8579,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>26</v>
@@ -8493,7 +8615,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8504,7 +8626,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -8515,10 +8637,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8526,10 +8648,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8537,10 +8659,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8548,10 +8670,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8559,10 +8681,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8570,10 +8692,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8581,10 +8703,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -8617,7 +8739,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="C2" s="3">
         <v>1234</v>
@@ -8628,7 +8750,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3">
         <v>123</v>
@@ -8639,10 +8761,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8650,10 +8772,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8661,10 +8783,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8672,10 +8794,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8683,10 +8805,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8694,10 +8816,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8705,7 +8827,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C10" s="15">
         <v>12345</v>
@@ -8716,7 +8838,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="C11" s="3">
         <v>-500</v>
@@ -8727,7 +8849,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="C12" s="3">
         <v>-1000</v>
@@ -8738,7 +8860,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="C13" s="3">
         <v>-700</v>
@@ -8749,7 +8871,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C14" s="3">
         <v>-300</v>
@@ -8760,7 +8882,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>220</v>
+        <v>162</v>
       </c>
       <c r="C15" s="3">
         <v>-85</v>
@@ -8771,7 +8893,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="C16" s="3">
         <v>-200</v>
@@ -8782,7 +8904,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="C17" s="3">
         <v>-76</v>
@@ -8793,7 +8915,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>45</v>
@@ -8804,7 +8926,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>45</v>
@@ -8815,10 +8937,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>262</v>
+        <v>204</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8826,10 +8948,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>263</v>
+        <v>205</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8837,10 +8959,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>264</v>
+        <v>206</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8848,10 +8970,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -8874,7 +8996,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8885,10 +9007,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>283</v>
+        <v>225</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>268</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8896,10 +9018,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8907,10 +9029,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>269</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8918,7 +9040,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="C5" s="3">
         <v>1234</v>
@@ -8929,7 +9051,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>285</v>
+        <v>227</v>
       </c>
       <c r="C6" s="3">
         <v>8967589</v>
@@ -8940,7 +9062,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>287</v>
+        <v>229</v>
       </c>
       <c r="C7" s="3">
         <v>34567</v>
@@ -8951,7 +9073,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="C8" s="3">
         <v>50</v>
@@ -8962,7 +9084,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
       <c r="C9" s="3">
         <v>100</v>
@@ -8973,10 +9095,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8984,7 +9106,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
@@ -8995,10 +9117,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>270</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9006,10 +9128,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9017,10 +9139,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9028,10 +9150,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9039,10 +9161,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9050,10 +9172,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9061,10 +9183,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>288</v>
+        <v>230</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>271</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9072,7 +9194,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>289</v>
+        <v>231</v>
       </c>
       <c r="C19" s="3">
         <v>123</v>
@@ -9083,10 +9205,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>290</v>
+        <v>232</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>272</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9094,10 +9216,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>291</v>
+        <v>233</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9105,10 +9227,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>292</v>
+        <v>234</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9116,10 +9238,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>293</v>
+        <v>235</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9127,10 +9249,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>294</v>
+        <v>236</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9138,10 +9260,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9149,10 +9271,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>296</v>
+        <v>238</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>273</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9160,10 +9282,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>297</v>
+        <v>239</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>274</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9171,10 +9293,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>298</v>
+        <v>240</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9182,7 +9304,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>299</v>
+        <v>241</v>
       </c>
       <c r="C29" s="3">
         <v>75</v>
@@ -9193,7 +9315,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>300</v>
+        <v>242</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
@@ -9204,7 +9326,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>301</v>
+        <v>243</v>
       </c>
       <c r="C31" s="3">
         <v>85</v>
@@ -9215,7 +9337,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>302</v>
+        <v>244</v>
       </c>
       <c r="C32" s="3">
         <v>55</v>
@@ -9226,7 +9348,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>5</v>
@@ -9237,10 +9359,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>276</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9248,7 +9370,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -9259,10 +9381,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9270,10 +9392,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9281,10 +9403,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>277</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9292,10 +9414,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>278</v>
+        <v>220</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9303,10 +9425,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9314,10 +9436,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9325,7 +9447,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="C42" s="3">
         <v>9869875890</v>
@@ -9336,10 +9458,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>303</v>
+        <v>245</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>279</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9347,7 +9469,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="C44" s="3">
         <v>20</v>
@@ -9358,10 +9480,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>196</v>
+        <v>140</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9369,10 +9491,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>280</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9380,10 +9502,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>281</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9391,10 +9513,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>199</v>
+        <v>143</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>277</v>
+        <v>219</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9402,10 +9524,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>201</v>
+        <v>144</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>282</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9413,7 +9535,7 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="C50" s="3">
         <v>9869875890</v>
@@ -9438,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9449,10 +9571,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
+        <v>225</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>268</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9460,10 +9582,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9471,10 +9593,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>269</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9482,7 +9604,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="C5" s="3">
         <v>50</v>
@@ -9493,7 +9615,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
       <c r="C6" s="3">
         <v>100</v>
@@ -9504,10 +9626,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9515,7 +9637,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C8" s="3">
         <v>123</v>
@@ -9526,10 +9648,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>270</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9537,10 +9659,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9548,10 +9670,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9559,10 +9681,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9570,10 +9692,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9581,7 +9703,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C14" s="3">
         <v>12345</v>
@@ -9592,10 +9714,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>288</v>
+        <v>230</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>271</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9603,7 +9725,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>289</v>
+        <v>231</v>
       </c>
       <c r="C16" s="3">
         <v>123</v>
@@ -9614,10 +9736,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>290</v>
+        <v>232</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>272</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9625,10 +9747,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>291</v>
+        <v>233</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9636,10 +9758,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>292</v>
+        <v>234</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9647,10 +9769,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>293</v>
+        <v>235</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9658,10 +9780,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>294</v>
+        <v>236</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9669,7 +9791,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="C22" s="3">
         <v>12345</v>
@@ -9680,10 +9802,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>296</v>
+        <v>238</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>273</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9691,10 +9813,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>297</v>
+        <v>239</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>274</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9702,10 +9824,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>298</v>
+        <v>240</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9713,7 +9835,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>299</v>
+        <v>241</v>
       </c>
       <c r="C26" s="3">
         <v>-75</v>
@@ -9724,7 +9846,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>300</v>
+        <v>242</v>
       </c>
       <c r="C27" s="3">
         <v>-65</v>
@@ -9735,7 +9857,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>301</v>
+        <v>243</v>
       </c>
       <c r="C28" s="3">
         <v>-85</v>
@@ -9746,7 +9868,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>302</v>
+        <v>244</v>
       </c>
       <c r="C29" s="3">
         <v>-55</v>
@@ -9757,10 +9879,10 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>276</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9768,7 +9890,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -9779,10 +9901,10 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>303</v>
+        <v>245</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>279</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9790,7 +9912,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="C33" s="3">
         <v>20</v>
@@ -9987,7 +10109,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -9998,7 +10120,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>29</v>
@@ -10079,7 +10201,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>42</v>
@@ -10090,7 +10212,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>41</v>
@@ -10159,7 +10281,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>37</v>
@@ -10170,7 +10292,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>38</v>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41A13B0-3CD7-47A2-B0D4-D444B9D245D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DBBB0D-0604-4168-B4D0-383E680D1C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="31" activeTab="34" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="34" activeTab="34" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DBBB0D-0604-4168-B4D0-383E680D1C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F43C4A-B23B-4BDD-AD13-E01E84CC15AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="34" activeTab="34" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="35" activeTab="38" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="369">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -306,9 +306,6 @@
     <t>fieldFederalGrantIdentifyingNumbe__c</t>
   </si>
   <si>
-    <t>fieldRequestFederalAgencyDispositionInstr__c</t>
-  </si>
-  <si>
     <t>(i) Sale Proceeds OR</t>
   </si>
   <si>
@@ -459,15 +456,9 @@
     <t>gefakzgrpvjjbdneasuz</t>
   </si>
   <si>
-    <t>fieldRequestTransfertoAward__c</t>
-  </si>
-  <si>
     <t>fieldFederalAwardIdentifier__c</t>
   </si>
   <si>
-    <t>fieldAcknowledgeEquipment__c</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
@@ -477,18 +468,12 @@
     <t>Federal Agency and Organizational</t>
   </si>
   <si>
-    <t>fieldFederalGrantIdentifyingNumberSF428__c</t>
-  </si>
-  <si>
     <t>Health</t>
   </si>
   <si>
     <t>fieldSupplementalSheet__c</t>
   </si>
   <si>
-    <t>fieldCommentsSF428__c</t>
-  </si>
-  <si>
     <t>fieldFederalGrantSF428A__c</t>
   </si>
   <si>
@@ -522,9 +507,6 @@
     <t>fieldPeriodEndDate__c</t>
   </si>
   <si>
-    <t>fieldTypeOfFederalInterest__c</t>
-  </si>
-  <si>
     <t>Renovation</t>
   </si>
   <si>
@@ -546,9 +528,6 @@
     <t>fieldLandAcreageAmount__c</t>
   </si>
   <si>
-    <t>fieldUnits__c</t>
-  </si>
-  <si>
     <t>Acres</t>
   </si>
   <si>
@@ -558,15 +537,9 @@
     <t>fieldSquareFootageUsable__c</t>
   </si>
   <si>
-    <t>fieldUnit2__c</t>
-  </si>
-  <si>
     <t>Square Feet</t>
   </si>
   <si>
-    <t>fieldOwned__c</t>
-  </si>
-  <si>
     <t>fieldFederalSharePercentage__c</t>
   </si>
   <si>
@@ -576,9 +549,6 @@
     <t>fieldNonFederalShare__c</t>
   </si>
   <si>
-    <t>fieldHasaDeed__c</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -591,57 +561,18 @@
     <t>fieldNationalHistoricPreservation__c</t>
   </si>
   <si>
-    <t>fieldNHPADescription__c</t>
-  </si>
-  <si>
     <t>fieldSignificantChange__c</t>
   </si>
   <si>
-    <t>fieldSignificantChangeDescription__c</t>
-  </si>
-  <si>
-    <t>fieldRealPropertyDispositionStatus__c</t>
-  </si>
-  <si>
     <t>A. Sold</t>
   </si>
   <si>
-    <t>fieldFundsOwed__c</t>
-  </si>
-  <si>
-    <t>fieldNetProceeds__c</t>
-  </si>
-  <si>
-    <t>fieldFederalAgencyOwes__c</t>
-  </si>
-  <si>
-    <t>fieldAElectrickWh__c</t>
-  </si>
-  <si>
-    <t>fieldBPetroleumGal__c</t>
-  </si>
-  <si>
-    <t>fieldCNaturalGascuft__c</t>
-  </si>
-  <si>
-    <t>fieldDOther__c</t>
-  </si>
-  <si>
     <t>fieldOtherDescribe__c</t>
   </si>
   <si>
-    <t>fieldBtu__c</t>
-  </si>
-  <si>
-    <t>fieldSF429B__c</t>
-  </si>
-  <si>
     <t>fieldEnvironmentalDescription__c</t>
   </si>
   <si>
-    <t>fieldNoneoftheAbove__c</t>
-  </si>
-  <si>
     <t>fieldElectric429B__c</t>
   </si>
   <si>
@@ -654,9 +585,6 @@
     <t>fieldOther429B__c</t>
   </si>
   <si>
-    <t>fieldSpecify__c</t>
-  </si>
-  <si>
     <t>Test Gas</t>
   </si>
   <si>
@@ -1120,6 +1048,144 @@
   </si>
   <si>
     <t>EmailAddress2__c</t>
+  </si>
+  <si>
+    <t>PeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>PeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>TypeOfFederalInterest__c</t>
+  </si>
+  <si>
+    <t>DescriptionofRealProperty__c</t>
+  </si>
+  <si>
+    <t>ZoningInformation__c</t>
+  </si>
+  <si>
+    <t>GPSLocationLongitude__c</t>
+  </si>
+  <si>
+    <t>GPSLocationLatitude__c</t>
+  </si>
+  <si>
+    <t>LandAcreageAmount__c</t>
+  </si>
+  <si>
+    <t>Units__c</t>
+  </si>
+  <si>
+    <t>SquareFootageGross__c</t>
+  </si>
+  <si>
+    <t>SquareFootageUsable__c</t>
+  </si>
+  <si>
+    <t>Unit2__c</t>
+  </si>
+  <si>
+    <t>Owned__c</t>
+  </si>
+  <si>
+    <t>FederalSharePercentage__c</t>
+  </si>
+  <si>
+    <t>NonFederalShare__c</t>
+  </si>
+  <si>
+    <t>Non_FederalSharePercentage__c</t>
+  </si>
+  <si>
+    <t>HasaDeed__c</t>
+  </si>
+  <si>
+    <t>FederallyRequiredInsurance__c</t>
+  </si>
+  <si>
+    <t>EnvironmentalComplianceRequirements__c</t>
+  </si>
+  <si>
+    <t>NationalHistoricPreservation__c</t>
+  </si>
+  <si>
+    <t>NHPADescription__c</t>
+  </si>
+  <si>
+    <t>SignificantChange__c</t>
+  </si>
+  <si>
+    <t>SignificantChangeDescription__c</t>
+  </si>
+  <si>
+    <t>RealPropertyDispositionStatus__c</t>
+  </si>
+  <si>
+    <t>FundsOwed__c</t>
+  </si>
+  <si>
+    <t>NetProceeds__c</t>
+  </si>
+  <si>
+    <t>FederalAgencyOwes__c</t>
+  </si>
+  <si>
+    <t>AElectrickWh__c</t>
+  </si>
+  <si>
+    <t>BPetroleumGal__c</t>
+  </si>
+  <si>
+    <t>CNaturalGascuft__c</t>
+  </si>
+  <si>
+    <t>OtherDescribe__c</t>
+  </si>
+  <si>
+    <t>Btu__c</t>
+  </si>
+  <si>
+    <t>DOther__c</t>
+  </si>
+  <si>
+    <t>SF429B__c</t>
+  </si>
+  <si>
+    <t>Selectunits__c</t>
+  </si>
+  <si>
+    <t>Select_units__c</t>
+  </si>
+  <si>
+    <t>EnvironmentalDescription__c</t>
+  </si>
+  <si>
+    <t>NoneoftheAbove__c</t>
+  </si>
+  <si>
+    <t>Electric429B__c</t>
+  </si>
+  <si>
+    <t>Petroleum429B__c</t>
+  </si>
+  <si>
+    <t>NaturalGas429B__c</t>
+  </si>
+  <si>
+    <t>Other429B__c</t>
+  </si>
+  <si>
+    <t>Specify__c</t>
+  </si>
+  <si>
+    <t>Electric__c</t>
+  </si>
+  <si>
+    <t>Petroleum__c</t>
+  </si>
+  <si>
+    <t>NaturalGas__c</t>
   </si>
 </sst>
 </file>
@@ -1687,7 +1753,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>32</v>
@@ -1698,7 +1764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>33</v>
@@ -1778,7 +1844,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>34</v>
@@ -1789,7 +1855,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>36</v>
@@ -1888,7 +1954,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1899,7 +1965,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -1968,7 +2034,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="C5" s="3">
         <v>-2</v>
@@ -1979,7 +2045,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>20</v>
@@ -2037,7 +2103,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="C4" s="3">
         <v>-2</v>
@@ -2048,7 +2114,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>20</v>
@@ -2139,7 +2205,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
@@ -2412,7 +2478,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
@@ -2525,7 +2591,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
@@ -2583,7 +2649,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2594,7 +2660,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2605,7 +2671,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2616,7 +2682,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2627,7 +2693,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2638,7 +2704,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2649,7 +2715,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2660,7 +2726,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2671,7 +2737,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2682,10 +2748,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2693,7 +2759,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="C12" s="10">
         <v>9999.99</v>
@@ -2704,7 +2770,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -2715,7 +2781,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="C14" s="10">
         <v>9999.99</v>
@@ -2726,7 +2792,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="C15" s="10">
         <v>1000</v>
@@ -2737,7 +2803,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>5</v>
@@ -2748,10 +2814,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2759,10 +2825,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2770,10 +2836,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2781,7 +2847,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>5</v>
@@ -2792,7 +2858,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>5</v>
@@ -2803,10 +2869,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2814,7 +2880,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2825,10 +2891,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2836,7 +2902,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="C25">
         <v>8967045891</v>
@@ -2847,10 +2913,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2858,10 +2924,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2977,7 +3043,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -3013,7 +3079,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -3024,7 +3090,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -3035,7 +3101,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -3046,7 +3112,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -3057,7 +3123,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -3068,7 +3134,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -3079,7 +3145,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -3090,7 +3156,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -3101,7 +3167,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -3112,7 +3178,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>5</v>
@@ -3123,10 +3189,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3134,10 +3200,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3145,7 +3211,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -3156,7 +3222,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -3167,10 +3233,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3178,7 +3244,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3189,10 +3255,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3200,7 +3266,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="C19">
         <v>8967045891</v>
@@ -3211,10 +3277,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3222,10 +3288,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -3258,10 +3324,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3269,10 +3335,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3280,10 +3346,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3291,10 +3357,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3302,7 +3368,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -3313,7 +3379,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -3324,7 +3390,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3335,10 +3401,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3346,7 +3412,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3357,10 +3423,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3368,10 +3434,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3379,10 +3445,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3390,10 +3456,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3401,10 +3467,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3412,10 +3478,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3423,10 +3489,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3434,10 +3500,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3445,7 +3511,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3456,10 +3522,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3467,10 +3533,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3478,10 +3544,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3489,10 +3555,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3500,10 +3566,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3511,10 +3577,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3522,10 +3588,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3533,7 +3599,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C27">
         <v>2122342342</v>
@@ -3544,10 +3610,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3555,7 +3621,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3592,10 +3658,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3603,10 +3669,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3614,7 +3680,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="C4" s="11">
         <v>50</v>
@@ -3654,7 +3720,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C2">
         <v>64789390</v>
@@ -3665,7 +3731,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3676,7 +3742,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3687,7 +3753,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3723,10 +3789,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3734,10 +3800,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3748,7 +3814,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3756,10 +3822,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3767,7 +3833,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="C6" s="3">
         <v>25</v>
@@ -3778,10 +3844,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3789,7 +3855,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="C8" s="13">
         <v>9999.99</v>
@@ -3800,10 +3866,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3837,7 +3903,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -3848,7 +3914,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3859,7 +3925,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3870,7 +3936,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3881,7 +3947,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -3892,10 +3958,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3903,7 +3969,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -3914,7 +3980,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -3925,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -3936,7 +4002,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -3947,10 +4013,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3958,7 +4024,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="C13">
         <v>85</v>
@@ -3969,7 +4035,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="C14">
         <v>85</v>
@@ -3980,7 +4046,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="C15">
         <v>9999.99</v>
@@ -3991,7 +4057,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="C16">
         <v>9999.99</v>
@@ -4002,10 +4068,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4013,10 +4079,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4024,10 +4090,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4035,7 +4101,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -4046,7 +4112,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -4057,10 +4123,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4068,7 +4134,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -4079,10 +4145,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4090,7 +4156,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C25">
         <v>9867589302</v>
@@ -4101,10 +4167,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4112,10 +4178,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -4149,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -4160,7 +4226,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -4171,7 +4237,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4182,7 +4248,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4193,7 +4259,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -4204,7 +4270,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -4215,7 +4281,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -4226,7 +4292,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -4237,7 +4303,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -4248,10 +4314,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4259,10 +4325,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4270,10 +4336,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4281,7 +4347,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4292,7 +4358,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4303,10 +4369,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4314,7 +4380,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -4325,10 +4391,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4336,7 +4402,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C19">
         <v>9867589302</v>
@@ -4347,10 +4413,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4358,10 +4424,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -4395,10 +4461,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4406,7 +4472,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4417,10 +4483,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4428,7 +4494,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4439,10 +4505,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4450,10 +4516,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4461,10 +4527,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4472,10 +4538,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4483,10 +4549,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4494,10 +4560,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4505,10 +4571,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4516,7 +4582,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4527,7 +4593,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4538,7 +4604,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4549,7 +4615,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -4560,7 +4626,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
@@ -4571,10 +4637,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4582,10 +4648,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4593,10 +4659,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4604,10 +4670,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4615,10 +4681,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4626,10 +4692,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4637,10 +4703,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4648,10 +4714,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4659,7 +4725,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C26">
         <v>2122342342</v>
@@ -4670,10 +4736,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4681,7 +4747,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4692,10 +4758,10 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -4729,10 +4795,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4740,7 +4806,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4751,10 +4817,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4762,7 +4828,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4773,10 +4839,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4784,10 +4850,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4795,10 +4861,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4806,10 +4872,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4817,10 +4883,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4828,10 +4894,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4839,10 +4905,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4850,7 +4916,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4861,7 +4927,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
@@ -4872,10 +4938,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4883,10 +4949,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4894,10 +4960,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4905,10 +4971,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4916,10 +4982,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4927,10 +4993,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4938,10 +5004,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4949,10 +5015,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4960,7 +5026,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C23">
         <v>2122342342</v>
@@ -4971,10 +5037,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4982,7 +5048,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -4993,10 +5059,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -5088,10 +5154,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5099,7 +5165,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -5110,10 +5176,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5121,7 +5187,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5132,10 +5198,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5143,10 +5209,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5154,10 +5220,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5165,10 +5231,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5176,10 +5242,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5187,10 +5253,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5198,10 +5264,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5209,7 +5275,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -5220,7 +5286,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -5231,7 +5297,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -5242,7 +5308,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -5253,10 +5319,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5264,10 +5330,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5275,10 +5341,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5286,10 +5352,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5297,10 +5363,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5308,10 +5374,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5319,10 +5385,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5330,10 +5396,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5341,7 +5407,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C25">
         <v>2122342342</v>
@@ -5352,10 +5418,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5363,7 +5429,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5374,10 +5440,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -5410,7 +5476,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -5421,10 +5487,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5432,10 +5498,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5443,7 +5509,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="C5">
         <v>1111</v>
@@ -5454,10 +5520,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -5490,10 +5556,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5504,7 +5570,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5512,7 +5578,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="C4">
         <v>76578</v>
@@ -5523,7 +5589,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -5534,7 +5600,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -5570,10 +5636,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5581,7 +5647,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5592,10 +5658,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5603,7 +5669,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5614,10 +5680,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5625,10 +5691,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5636,10 +5702,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5647,10 +5713,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5658,10 +5724,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5669,10 +5735,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5680,10 +5746,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5691,10 +5757,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5702,10 +5768,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5713,10 +5779,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5724,10 +5790,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5735,10 +5801,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5746,10 +5812,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5757,7 +5823,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -5768,7 +5834,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="C20">
         <v>150</v>
@@ -5779,7 +5845,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
@@ -5790,7 +5856,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
@@ -5801,7 +5867,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -5812,10 +5878,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5823,7 +5889,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -5834,10 +5900,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5845,10 +5911,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5856,10 +5922,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5867,10 +5933,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5878,10 +5944,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5889,10 +5955,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5900,10 +5966,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5911,7 +5977,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="C33" s="15">
         <v>2122342342</v>
@@ -5922,10 +5988,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5933,7 +5999,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5944,7 +6010,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -5980,10 +6046,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E2" s="16"/>
     </row>
@@ -5992,7 +6058,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -6003,10 +6069,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6014,7 +6080,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -6025,10 +6091,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6036,10 +6102,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6047,10 +6113,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6058,10 +6124,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6069,10 +6135,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6080,10 +6146,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6091,10 +6157,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6102,10 +6168,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6113,10 +6179,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6124,10 +6190,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6135,10 +6201,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6146,10 +6212,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6157,10 +6223,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6168,7 +6234,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -6179,10 +6245,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6190,10 +6256,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6201,10 +6267,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6212,10 +6278,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6223,10 +6289,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6234,10 +6300,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6245,10 +6311,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6256,7 +6322,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="C27" s="15">
         <v>2122342342</v>
@@ -6267,10 +6333,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6278,7 +6344,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6314,7 +6380,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>132</v>
+        <v>297</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6325,7 +6391,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>145</v>
+        <v>323</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -6336,7 +6402,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>146</v>
+        <v>324</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -6347,10 +6413,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>147</v>
+        <v>325</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6358,10 +6424,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>149</v>
+        <v>326</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6369,7 +6435,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>87</v>
+        <v>259</v>
       </c>
       <c r="C7">
         <v>123</v>
@@ -6380,10 +6446,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>88</v>
+        <v>260</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6391,10 +6457,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>89</v>
+        <v>261</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6402,10 +6468,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>90</v>
+        <v>262</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6413,10 +6479,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6424,10 +6490,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>93</v>
+        <v>264</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6435,10 +6501,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6446,10 +6512,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>97</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6457,7 +6523,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>151</v>
+        <v>327</v>
       </c>
       <c r="C15">
         <v>1234</v>
@@ -6468,7 +6534,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>152</v>
+        <v>328</v>
       </c>
       <c r="C16">
         <v>48</v>
@@ -6479,7 +6545,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>153</v>
+        <v>329</v>
       </c>
       <c r="C17">
         <v>35</v>
@@ -6490,7 +6556,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>154</v>
+        <v>330</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -6501,10 +6567,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>155</v>
+        <v>331</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6512,7 +6578,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>157</v>
+        <v>332</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -6523,7 +6589,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>158</v>
+        <v>333</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6534,10 +6600,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>159</v>
+        <v>334</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6545,7 +6611,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>161</v>
+        <v>335</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -6556,7 +6622,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="C24">
         <v>789</v>
@@ -6567,7 +6633,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>162</v>
+        <v>336</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -6578,7 +6644,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>164</v>
+        <v>337</v>
       </c>
       <c r="C26">
         <v>456</v>
@@ -6589,7 +6655,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>163</v>
+        <v>338</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -6600,10 +6666,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>165</v>
+        <v>339</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6611,7 +6677,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>134</v>
+        <v>299</v>
       </c>
       <c r="C29" t="s">
         <v>51</v>
@@ -6622,7 +6688,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>167</v>
+        <v>340</v>
       </c>
       <c r="C30" t="s">
         <v>51</v>
@@ -6633,7 +6699,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>168</v>
+        <v>341</v>
       </c>
       <c r="C31" t="s">
         <v>51</v>
@@ -6644,7 +6710,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>169</v>
+        <v>342</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -6655,10 +6721,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>170</v>
+        <v>343</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6666,7 +6732,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>171</v>
+        <v>344</v>
       </c>
       <c r="C34" t="s">
         <v>45</v>
@@ -6677,10 +6743,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>172</v>
+        <v>345</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6688,10 +6754,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>173</v>
+        <v>346</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6699,7 +6765,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>175</v>
+        <v>347</v>
       </c>
       <c r="C37">
         <v>10000</v>
@@ -6710,7 +6776,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>176</v>
+        <v>348</v>
       </c>
       <c r="C38">
         <v>8000</v>
@@ -6721,7 +6787,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>177</v>
+        <v>349</v>
       </c>
       <c r="C39">
         <v>6000</v>
@@ -6732,7 +6798,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>178</v>
+        <v>350</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -6743,7 +6809,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>179</v>
+        <v>351</v>
       </c>
       <c r="C41">
         <v>300</v>
@@ -6754,7 +6820,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>180</v>
+        <v>352</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -6765,10 +6831,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -6801,7 +6867,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>132</v>
+        <v>297</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6812,7 +6878,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>87</v>
+        <v>259</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -6823,10 +6889,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>88</v>
+        <v>260</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6834,10 +6900,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>89</v>
+        <v>261</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6845,10 +6911,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>90</v>
+        <v>262</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6856,10 +6922,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6867,10 +6933,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>93</v>
+        <v>264</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6878,10 +6944,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6889,7 +6955,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>97</v>
+        <v>266</v>
       </c>
       <c r="C10" s="12">
         <v>1234</v>
@@ -6900,7 +6966,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>154</v>
+        <v>330</v>
       </c>
       <c r="C11">
         <v>-8</v>
@@ -6911,7 +6977,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>157</v>
+        <v>332</v>
       </c>
       <c r="C12">
         <v>-300</v>
@@ -6922,7 +6988,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>158</v>
+        <v>333</v>
       </c>
       <c r="C13">
         <v>-200</v>
@@ -6933,7 +6999,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>182</v>
+        <v>353</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -6944,7 +7010,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="C15">
         <v>-818</v>
@@ -6955,7 +7021,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>162</v>
+        <v>336</v>
       </c>
       <c r="C16">
         <v>-8</v>
@@ -6966,7 +7032,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>164</v>
+        <v>337</v>
       </c>
       <c r="C17">
         <v>-767</v>
@@ -6977,7 +7043,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>163</v>
+        <v>338</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -6988,7 +7054,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>165</v>
+        <v>339</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>45</v>
@@ -6999,7 +7065,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>168</v>
+        <v>341</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -7010,7 +7076,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>169</v>
+        <v>342</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -7021,7 +7087,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>171</v>
+        <v>344</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -7032,10 +7098,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>173</v>
+        <v>346</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7043,7 +7109,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>175</v>
+        <v>347</v>
       </c>
       <c r="C24">
         <v>-1000</v>
@@ -7054,7 +7120,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>176</v>
+        <v>348</v>
       </c>
       <c r="C25">
         <v>-700</v>
@@ -7065,7 +7131,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>177</v>
+        <v>349</v>
       </c>
       <c r="C26">
         <v>-500</v>
@@ -7076,7 +7142,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>178</v>
+        <v>350</v>
       </c>
       <c r="C27">
         <v>-300</v>
@@ -7087,7 +7153,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>183</v>
+        <v>354</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -7098,7 +7164,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>179</v>
+        <v>351</v>
       </c>
       <c r="C29">
         <v>-150</v>
@@ -7109,7 +7175,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>180</v>
+        <v>352</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -7120,7 +7186,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>181</v>
+        <v>355</v>
       </c>
       <c r="C31">
         <v>-40</v>
@@ -7156,7 +7222,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7167,10 +7233,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>149</v>
+        <v>326</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7178,7 +7244,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>87</v>
+        <v>259</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7189,10 +7255,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>88</v>
+        <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7200,10 +7266,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>89</v>
+        <v>261</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7211,10 +7277,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>90</v>
+        <v>262</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7222,10 +7288,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7233,10 +7299,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>93</v>
+        <v>264</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7244,10 +7310,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7255,10 +7321,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>97</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7266,7 +7332,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>151</v>
+        <v>327</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -7277,7 +7343,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>152</v>
+        <v>328</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -7288,7 +7354,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>153</v>
+        <v>329</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -7299,10 +7365,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>184</v>
+        <v>356</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7310,7 +7376,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>161</v>
+        <v>335</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -7321,7 +7387,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>85</v>
+        <v>257</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -7332,7 +7398,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>154</v>
+        <v>330</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -7343,10 +7409,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>196</v>
+        <v>357</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7354,7 +7420,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>157</v>
+        <v>332</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -7365,7 +7431,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>158</v>
+        <v>333</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -7376,10 +7442,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>197</v>
+        <v>358</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7387,7 +7453,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="C23">
         <v>789</v>
@@ -7398,7 +7464,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>162</v>
+        <v>336</v>
       </c>
       <c r="C24">
         <v>86</v>
@@ -7409,7 +7475,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>164</v>
+        <v>337</v>
       </c>
       <c r="C25">
         <v>456</v>
@@ -7420,7 +7486,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>163</v>
+        <v>338</v>
       </c>
       <c r="C26">
         <v>74</v>
@@ -7431,7 +7497,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>134</v>
+        <v>299</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
@@ -7442,7 +7508,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>168</v>
+        <v>341</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -7453,10 +7519,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>185</v>
+        <v>359</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7464,7 +7530,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>167</v>
+        <v>340</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -7475,10 +7541,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>170</v>
+        <v>343</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7486,7 +7552,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -7497,7 +7563,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -7508,7 +7574,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>128</v>
+        <v>295</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -7519,7 +7585,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>126</v>
+        <v>292</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -7530,7 +7596,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>186</v>
+        <v>360</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -7541,7 +7607,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>187</v>
+        <v>361</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -7552,7 +7618,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>188</v>
+        <v>362</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7563,7 +7629,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>189</v>
+        <v>363</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -7574,7 +7640,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>190</v>
+        <v>364</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -7585,10 +7651,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>191</v>
+        <v>365</v>
       </c>
       <c r="C41" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7596,7 +7662,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>193</v>
+        <v>366</v>
       </c>
       <c r="C42">
         <v>400</v>
@@ -7607,7 +7673,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>194</v>
+        <v>367</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7618,7 +7684,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>195</v>
+        <v>368</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -7629,10 +7695,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C45" t="s">
         <v>78</v>
-      </c>
-      <c r="C45" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -7666,7 +7732,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7677,7 +7743,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>87</v>
+        <v>259</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -7688,10 +7754,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>88</v>
+        <v>260</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7699,10 +7765,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>89</v>
+        <v>261</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7710,10 +7776,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>90</v>
+        <v>262</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7721,10 +7787,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7732,10 +7798,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>93</v>
+        <v>264</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7743,10 +7809,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7754,10 +7820,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>97</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -7801,10 +7867,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7812,7 +7878,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7823,10 +7889,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7834,10 +7900,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7845,10 +7911,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7856,10 +7922,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7867,10 +7933,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7878,10 +7944,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7889,7 +7955,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C11" s="12">
         <v>1234</v>
@@ -7900,7 +7966,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -7911,7 +7977,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C13">
         <v>-466</v>
@@ -7922,7 +7988,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C14">
         <v>-500</v>
@@ -7933,7 +7999,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C15">
         <v>-400</v>
@@ -7944,7 +8010,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16">
         <v>-789</v>
@@ -7955,7 +8021,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C17">
         <v>-200</v>
@@ -7966,7 +8032,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C18">
         <v>-456</v>
@@ -7977,7 +8043,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C19">
         <v>-74</v>
@@ -7988,7 +8054,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -7999,7 +8065,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -8010,7 +8076,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="C22">
         <v>-400</v>
@@ -8021,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="C23">
         <v>-200</v>
@@ -8032,7 +8098,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C24">
         <v>-100</v>
@@ -8043,7 +8109,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="C25">
         <v>-200</v>
@@ -8054,7 +8120,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="C26">
         <v>-50</v>
@@ -8065,7 +8131,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C27">
         <v>-400</v>
@@ -8076,7 +8142,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="C28">
         <v>-200</v>
@@ -8087,7 +8153,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="C29">
         <v>-100</v>
@@ -8098,7 +8164,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="C30">
         <v>-200</v>
@@ -8109,7 +8175,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -8205,7 +8271,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8216,10 +8282,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8227,7 +8293,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -8238,10 +8304,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8249,10 +8315,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8260,10 +8326,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8271,10 +8337,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8282,10 +8348,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8293,10 +8359,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8304,10 +8370,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>97</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8315,7 +8381,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -8326,7 +8392,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -8337,7 +8403,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -8348,7 +8414,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C15">
         <v>500</v>
@@ -8359,10 +8425,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8370,7 +8436,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C17">
         <v>1000</v>
@@ -8381,7 +8447,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C18">
         <v>700</v>
@@ -8392,10 +8458,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8403,10 +8469,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8414,7 +8480,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="C21">
         <v>1234</v>
@@ -8425,10 +8491,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="C22" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8436,10 +8502,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8447,10 +8513,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8458,7 +8524,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C25">
         <v>300</v>
@@ -8469,7 +8535,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C26">
         <v>85</v>
@@ -8480,7 +8546,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -8491,7 +8557,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C28">
         <v>76</v>
@@ -8502,7 +8568,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>45</v>
@@ -8513,7 +8579,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>45</v>
@@ -8524,10 +8590,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8535,7 +8601,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>45</v>
@@ -8546,10 +8612,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8557,7 +8623,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>26</v>
@@ -8568,7 +8634,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>26</v>
@@ -8579,7 +8645,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>26</v>
@@ -8615,7 +8681,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8626,7 +8692,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -8637,10 +8703,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8648,10 +8714,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8659,10 +8725,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8670,10 +8736,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8681,10 +8747,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8692,10 +8758,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8703,10 +8769,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>97</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -8739,7 +8805,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3">
         <v>1234</v>
@@ -8750,7 +8816,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3">
         <v>123</v>
@@ -8761,10 +8827,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8772,10 +8838,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8783,10 +8849,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8794,10 +8860,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>91</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8805,10 +8871,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8816,10 +8882,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>95</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8827,7 +8893,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="15">
         <v>12345</v>
@@ -8838,7 +8904,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C11" s="3">
         <v>-500</v>
@@ -8849,7 +8915,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C12" s="3">
         <v>-1000</v>
@@ -8860,7 +8926,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C13" s="3">
         <v>-700</v>
@@ -8871,7 +8937,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" s="3">
         <v>-300</v>
@@ -8882,7 +8948,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C15" s="3">
         <v>-85</v>
@@ -8893,7 +8959,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C16" s="3">
         <v>-200</v>
@@ -8904,7 +8970,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C17" s="3">
         <v>-76</v>
@@ -8915,7 +8981,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>45</v>
@@ -8926,7 +8992,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>45</v>
@@ -8937,10 +9003,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8948,10 +9014,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8959,10 +9025,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8970,10 +9036,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -8996,7 +9062,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9007,10 +9073,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9018,10 +9084,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9029,10 +9095,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9040,7 +9106,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" s="3">
         <v>1234</v>
@@ -9051,7 +9117,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="C6" s="3">
         <v>8967589</v>
@@ -9062,7 +9128,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="C7" s="3">
         <v>34567</v>
@@ -9073,7 +9139,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C8" s="3">
         <v>50</v>
@@ -9084,7 +9150,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C9" s="3">
         <v>100</v>
@@ -9095,10 +9161,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9106,7 +9172,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
@@ -9117,10 +9183,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9128,10 +9194,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9139,10 +9205,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9150,10 +9216,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9161,10 +9227,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9172,10 +9238,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9183,10 +9249,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9194,7 +9260,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="C19" s="3">
         <v>123</v>
@@ -9205,10 +9271,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9216,10 +9282,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9227,10 +9293,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9238,10 +9304,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9249,10 +9315,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9260,10 +9326,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9271,10 +9337,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9282,10 +9348,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9293,10 +9359,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9304,7 +9370,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="C29" s="3">
         <v>75</v>
@@ -9315,7 +9381,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
@@ -9326,7 +9392,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="C31" s="3">
         <v>85</v>
@@ -9337,7 +9403,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="C32" s="3">
         <v>55</v>
@@ -9348,7 +9414,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>5</v>
@@ -9359,10 +9425,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9370,7 +9436,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -9381,10 +9447,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9392,10 +9458,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9403,10 +9469,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9414,10 +9480,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9425,10 +9491,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9436,10 +9502,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9447,7 +9513,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C42" s="3">
         <v>9869875890</v>
@@ -9458,10 +9524,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9469,7 +9535,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C44" s="3">
         <v>20</v>
@@ -9480,10 +9546,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9491,10 +9557,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9502,10 +9568,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9513,10 +9579,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9524,10 +9590,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9535,7 +9601,7 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C50" s="3">
         <v>9869875890</v>
@@ -9560,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9571,10 +9637,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9582,10 +9648,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9593,10 +9659,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9604,7 +9670,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3">
         <v>50</v>
@@ -9615,7 +9681,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3">
         <v>100</v>
@@ -9626,10 +9692,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9637,7 +9703,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C8" s="3">
         <v>123</v>
@@ -9648,10 +9714,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9659,10 +9725,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9670,10 +9736,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9681,10 +9747,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9692,10 +9758,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9703,7 +9769,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C14" s="3">
         <v>12345</v>
@@ -9714,10 +9780,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9725,7 +9791,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="C16" s="3">
         <v>123</v>
@@ -9736,10 +9802,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9747,10 +9813,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9758,10 +9824,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9769,10 +9835,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9780,10 +9846,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9791,7 +9857,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="C22" s="3">
         <v>12345</v>
@@ -9802,10 +9868,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9813,10 +9879,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9824,10 +9890,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9835,7 +9901,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="C26" s="3">
         <v>-75</v>
@@ -9846,7 +9912,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="C27" s="3">
         <v>-65</v>
@@ -9857,7 +9923,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="C28" s="3">
         <v>-85</v>
@@ -9868,7 +9934,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="C29" s="3">
         <v>-55</v>
@@ -9879,10 +9945,10 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9890,7 +9956,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -9901,10 +9967,10 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9912,7 +9978,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C33" s="3">
         <v>20</v>
@@ -10109,7 +10175,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -10120,7 +10186,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>29</v>
@@ -10201,7 +10267,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>42</v>
@@ -10212,7 +10278,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>41</v>
@@ -10281,7 +10347,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>37</v>
@@ -10292,7 +10358,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>38</v>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F43C4A-B23B-4BDD-AD13-E01E84CC15AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3376FB6C-54E3-468A-BF9A-7A5CB1A6EC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="35" activeTab="38" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="40" activeTab="43" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="308">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -303,18 +303,9 @@
     <t>fieldFrequency__c</t>
   </si>
   <si>
-    <t>fieldFederalGrantIdentifyingNumbe__c</t>
-  </si>
-  <si>
     <t>(i) Sale Proceeds OR</t>
   </si>
   <si>
-    <t>fieldFederalShare__c</t>
-  </si>
-  <si>
-    <t>fieldComments__c</t>
-  </si>
-  <si>
     <t>Automation Test</t>
   </si>
   <si>
@@ -324,108 +315,36 @@
     <t>John Mathews</t>
   </si>
   <si>
-    <t>fieldTelephone2__c</t>
-  </si>
-  <si>
     <t>automation@yopmail.com</t>
   </si>
   <si>
-    <t>fieldFederalAgencySF428__c</t>
-  </si>
-  <si>
-    <t>fieldAORDateSubmitted__c</t>
-  </si>
-  <si>
-    <t>fieldRecipientOrganizationNameSF428__c</t>
-  </si>
-  <si>
-    <t>fieldStreet1SF428__c</t>
-  </si>
-  <si>
-    <t>fieldStreet2SF428__c</t>
-  </si>
-  <si>
-    <t>fieldCitySF428__c</t>
-  </si>
-  <si>
-    <t>fieldCountySF428__c</t>
-  </si>
-  <si>
-    <t>fieldStateSf428__c</t>
-  </si>
-  <si>
-    <t>NY: New York</t>
-  </si>
-  <si>
-    <t>fieldProvinceSF428__c</t>
-  </si>
-  <si>
     <t>NY</t>
   </si>
   <si>
-    <t>fieldCountrySF428__c</t>
-  </si>
-  <si>
     <t>USA: UNITED STATES</t>
   </si>
   <si>
-    <t>fieldZipPostalCodeSF428__c</t>
-  </si>
-  <si>
     <t>12345-1234</t>
   </si>
   <si>
-    <t>fieldRemark__c</t>
-  </si>
-  <si>
-    <t>fieldAcknowledgementSF428__c</t>
-  </si>
-  <si>
-    <t>fieldPrefix__c</t>
-  </si>
-  <si>
     <t>Mr.</t>
   </si>
   <si>
-    <t>fieldFirstNameSF428__c</t>
-  </si>
-  <si>
     <t>John</t>
   </si>
   <si>
-    <t>fieldMiddleNameSF428__c</t>
-  </si>
-  <si>
     <t>Andrew</t>
   </si>
   <si>
-    <t>fieldLastNameSF428__c</t>
-  </si>
-  <si>
     <t>Mathews</t>
   </si>
   <si>
-    <t>fieldSuffix__c</t>
-  </si>
-  <si>
     <t>Jr.</t>
   </si>
   <si>
-    <t>fieldTitleSF429__c</t>
-  </si>
-  <si>
     <t>Associate</t>
   </si>
   <si>
-    <t>fieldSubmittedBySF428__c</t>
-  </si>
-  <si>
-    <t>fieldTelephone__c</t>
-  </si>
-  <si>
-    <t>fieldSubmittedOn__c</t>
-  </si>
-  <si>
     <t>Automation Test Organization</t>
   </si>
   <si>
@@ -456,9 +375,6 @@
     <t>gefakzgrpvjjbdneasuz</t>
   </si>
   <si>
-    <t>fieldFederalAwardIdentifier__c</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
@@ -471,12 +387,6 @@
     <t>Health</t>
   </si>
   <si>
-    <t>fieldSupplementalSheet__c</t>
-  </si>
-  <si>
-    <t>fieldFederalGrantSF428A__c</t>
-  </si>
-  <si>
     <t>(a) Individual (Reporting Federally-owned property for one award)</t>
   </si>
   <si>
@@ -486,159 +396,33 @@
     <t>Automation test</t>
   </si>
   <si>
-    <t>fieldTypeorPrintedPrefix__c</t>
-  </si>
-  <si>
-    <t>fieldTypeorPrintedFirstName__c</t>
-  </si>
-  <si>
-    <t>fieldTypeorPrintedMiddleName__c</t>
-  </si>
-  <si>
-    <t>fieldTypeorPrintedLastName__c</t>
-  </si>
-  <si>
-    <t>fieldTypeorPrintedTitle__c</t>
-  </si>
-  <si>
-    <t>fieldPeriodStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldPeriodEndDate__c</t>
-  </si>
-  <si>
     <t>Renovation</t>
   </si>
   <si>
-    <t>fieldDescriptionofRealProperty__c</t>
-  </si>
-  <si>
     <t>Street1</t>
   </si>
   <si>
-    <t>fieldZoningInformation__c</t>
-  </si>
-  <si>
-    <t>fieldGPSLocationLongitude__c</t>
-  </si>
-  <si>
-    <t>fieldGPSLocationLatitude__c</t>
-  </si>
-  <si>
-    <t>fieldLandAcreageAmount__c</t>
-  </si>
-  <si>
     <t>Acres</t>
   </si>
   <si>
-    <t>fieldSquareFootageGross__c</t>
-  </si>
-  <si>
-    <t>fieldSquareFootageUsable__c</t>
-  </si>
-  <si>
     <t>Square Feet</t>
   </si>
   <si>
-    <t>fieldFederalSharePercentage__c</t>
-  </si>
-  <si>
-    <t>fieldNon_FederalSharePercentage__c</t>
-  </si>
-  <si>
-    <t>fieldNonFederalShare__c</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>fieldFederallyRequiredInsurance__c</t>
-  </si>
-  <si>
-    <t>fieldEnvironmentalComplianceRequirements__c</t>
-  </si>
-  <si>
-    <t>fieldNationalHistoricPreservation__c</t>
-  </si>
-  <si>
-    <t>fieldSignificantChange__c</t>
-  </si>
-  <si>
     <t>A. Sold</t>
   </si>
   <si>
-    <t>fieldOtherDescribe__c</t>
-  </si>
-  <si>
-    <t>fieldEnvironmentalDescription__c</t>
-  </si>
-  <si>
-    <t>fieldElectric429B__c</t>
-  </si>
-  <si>
-    <t>fieldPetroleum429B__c</t>
-  </si>
-  <si>
-    <t>fieldNaturalGas429B__c</t>
-  </si>
-  <si>
-    <t>fieldOther429B__c</t>
-  </si>
-  <si>
     <t>Test Gas</t>
   </si>
   <si>
-    <t>fieldElectric__c</t>
-  </si>
-  <si>
-    <t>fieldPetroleum__c</t>
-  </si>
-  <si>
-    <t>fieldNaturalGas__c</t>
-  </si>
-  <si>
-    <t>fieldSelectunits__c</t>
-  </si>
-  <si>
-    <t>fieldSelect_units__c</t>
-  </si>
-  <si>
-    <t>fieldDescription429C__c</t>
-  </si>
-  <si>
     <t>Autmation Test</t>
   </si>
   <si>
-    <t>fieldDispositionPreferenceSF429C__c</t>
-  </si>
-  <si>
     <t>A. Sell</t>
   </si>
   <si>
-    <t>fieldGrantNumber__c</t>
-  </si>
-  <si>
-    <t>fieldTitleSF428__c</t>
-  </si>
-  <si>
-    <t>fieldIntendedUse__c</t>
-  </si>
-  <si>
-    <t>fieldEncumberedParties__c</t>
-  </si>
-  <si>
-    <t>fieldRequestReasons__c</t>
-  </si>
-  <si>
-    <t>fieldor_Btu_429B__c</t>
-  </si>
-  <si>
-    <t>fieldorBtu__c</t>
-  </si>
-  <si>
-    <t>fieldOtherEnergy__c</t>
-  </si>
-  <si>
     <t>Final</t>
   </si>
   <si>
@@ -684,69 +468,9 @@
     <t>Junior</t>
   </si>
   <si>
-    <t>fieldTypeOfRequest__c</t>
-  </si>
-  <si>
-    <t>fieldBasisOfRequest__c</t>
-  </si>
-  <si>
-    <t>fieldPartialPaymentRequest__c</t>
-  </si>
-  <si>
     <t>FieldAPIName</t>
   </si>
   <si>
-    <t>fieldFinancialAssistance__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeOrganizationName__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeStreet1__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeStreet2__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeCity__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeCounty__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeState__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeProvince__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeZipCode__c</t>
-  </si>
-  <si>
-    <t>fieldPrograms__c</t>
-  </si>
-  <si>
-    <t>fieldFunctions__c</t>
-  </si>
-  <si>
-    <t>fieldActivities__c</t>
-  </si>
-  <si>
-    <t>fieldProgramPercentage__c</t>
-  </si>
-  <si>
-    <t>fieldFunctionPercentage__c</t>
-  </si>
-  <si>
-    <t>fieldActivityPercentage__c</t>
-  </si>
-  <si>
-    <t>fieldTotalPercentage271__c</t>
-  </si>
-  <si>
-    <t>fieldSignatureofAuthorized__c</t>
-  </si>
-  <si>
     <t>GoverningOrganizationReportDate__c</t>
   </si>
   <si>
@@ -1186,6 +910,99 @@
   </si>
   <si>
     <t>NaturalGas__c</t>
+  </si>
+  <si>
+    <t>or_Btu_429B__c</t>
+  </si>
+  <si>
+    <t>orBtu__c</t>
+  </si>
+  <si>
+    <t>OtherEnergy__c</t>
+  </si>
+  <si>
+    <t>Description429C__c</t>
+  </si>
+  <si>
+    <t>DispositionPreferenceSF429C__c</t>
+  </si>
+  <si>
+    <t>GrantNumber__c</t>
+  </si>
+  <si>
+    <t>TitleSF428__c</t>
+  </si>
+  <si>
+    <t>IntendedUse__c</t>
+  </si>
+  <si>
+    <t>EncumberedParties__c</t>
+  </si>
+  <si>
+    <t>RequestReasons__c</t>
+  </si>
+  <si>
+    <t>TypeOfRequest__c</t>
+  </si>
+  <si>
+    <t>BasisOfRequest__c</t>
+  </si>
+  <si>
+    <t>PartialPaymentRequest__c</t>
+  </si>
+  <si>
+    <t>FinancialAssistance__c</t>
+  </si>
+  <si>
+    <t>PayeeOrganizationName__c</t>
+  </si>
+  <si>
+    <t>PayeeStreet1__c</t>
+  </si>
+  <si>
+    <t>PayeeStreet2__c</t>
+  </si>
+  <si>
+    <t>PayeeCity__c</t>
+  </si>
+  <si>
+    <t>PayeeCounty__c</t>
+  </si>
+  <si>
+    <t>PayeeState__c</t>
+  </si>
+  <si>
+    <t>PayeeProvince__c</t>
+  </si>
+  <si>
+    <t>PayeeZipCode__c</t>
+  </si>
+  <si>
+    <t>Programs__c</t>
+  </si>
+  <si>
+    <t>Functions__c</t>
+  </si>
+  <si>
+    <t>Activities__c</t>
+  </si>
+  <si>
+    <t>ProgramPercentage__c</t>
+  </si>
+  <si>
+    <t>FunctionPercentage__c</t>
+  </si>
+  <si>
+    <t>ActivityPercentage__c</t>
+  </si>
+  <si>
+    <t>TotalPercentage271__c</t>
+  </si>
+  <si>
+    <t>SignatureofAuthorized__c</t>
+  </si>
+  <si>
+    <t>FL: Florida</t>
   </si>
 </sst>
 </file>
@@ -1753,7 +1570,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>32</v>
@@ -1764,7 +1581,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>33</v>
@@ -1844,7 +1661,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>34</v>
@@ -1855,7 +1672,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>36</v>
@@ -1954,7 +1771,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>222</v>
+        <v>130</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1965,7 +1782,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>223</v>
+        <v>131</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -2034,7 +1851,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>222</v>
+        <v>130</v>
       </c>
       <c r="C5" s="3">
         <v>-2</v>
@@ -2045,7 +1862,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>223</v>
+        <v>131</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>20</v>
@@ -2103,7 +1920,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>222</v>
+        <v>130</v>
       </c>
       <c r="C4" s="3">
         <v>-2</v>
@@ -2114,7 +1931,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>223</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>20</v>
@@ -2205,7 +2022,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
@@ -2478,7 +2295,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
@@ -2591,7 +2408,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
@@ -2649,7 +2466,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2660,7 +2477,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2671,7 +2488,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2682,7 +2499,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2693,7 +2510,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>139</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2704,7 +2521,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>232</v>
+        <v>140</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2715,7 +2532,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>141</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2726,7 +2543,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>234</v>
+        <v>142</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2737,7 +2554,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2748,10 +2565,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2759,7 +2576,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>237</v>
+        <v>145</v>
       </c>
       <c r="C12" s="10">
         <v>9999.99</v>
@@ -2770,7 +2587,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -2781,7 +2598,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>239</v>
+        <v>147</v>
       </c>
       <c r="C14" s="10">
         <v>9999.99</v>
@@ -2792,7 +2609,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>240</v>
+        <v>148</v>
       </c>
       <c r="C15" s="10">
         <v>1000</v>
@@ -2803,7 +2620,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>241</v>
+        <v>149</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>5</v>
@@ -2814,10 +2631,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>242</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2825,10 +2642,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>151</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2836,10 +2653,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>244</v>
+        <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2847,7 +2664,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>5</v>
@@ -2858,7 +2675,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>5</v>
@@ -2869,10 +2686,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>247</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2880,7 +2697,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2891,10 +2708,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>249</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2902,7 +2719,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>250</v>
+        <v>158</v>
       </c>
       <c r="C25">
         <v>8967045891</v>
@@ -2913,10 +2730,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>251</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2924,10 +2741,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3043,7 +2860,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -3079,7 +2896,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -3090,7 +2907,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -3101,7 +2918,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -3112,7 +2929,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -3123,7 +2940,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>139</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -3134,7 +2951,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>232</v>
+        <v>140</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -3145,7 +2962,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>141</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -3156,7 +2973,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>234</v>
+        <v>142</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -3167,7 +2984,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -3178,7 +2995,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>241</v>
+        <v>149</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>5</v>
@@ -3189,10 +3006,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3200,10 +3017,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3211,7 +3028,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -3222,7 +3039,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -3233,10 +3050,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>155</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3244,7 +3061,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3255,10 +3072,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>249</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3266,7 +3083,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>250</v>
+        <v>158</v>
       </c>
       <c r="C19">
         <v>8967045891</v>
@@ -3277,10 +3094,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>251</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3288,10 +3105,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3324,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3335,10 +3152,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3346,10 +3163,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>254</v>
+        <v>162</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3357,10 +3174,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>255</v>
+        <v>163</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3368,7 +3185,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -3379,7 +3196,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -3390,7 +3207,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>257</v>
+        <v>165</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3401,10 +3218,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3412,7 +3229,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>259</v>
+        <v>167</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3423,10 +3240,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3434,10 +3251,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3445,10 +3262,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3456,10 +3273,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3467,10 +3284,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3478,10 +3295,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3489,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3500,10 +3317,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>267</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3511,7 +3328,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>268</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3522,10 +3339,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>269</v>
+        <v>177</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3533,10 +3350,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>270</v>
+        <v>178</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3544,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>271</v>
+        <v>179</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3555,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>180</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3566,10 +3383,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3577,10 +3394,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>274</v>
+        <v>182</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3588,10 +3405,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>275</v>
+        <v>183</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3599,7 +3416,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="C27">
         <v>2122342342</v>
@@ -3610,10 +3427,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3621,7 +3438,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>277</v>
+        <v>185</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3658,10 +3475,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3669,10 +3486,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3680,7 +3497,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>279</v>
+        <v>187</v>
       </c>
       <c r="C4" s="11">
         <v>50</v>
@@ -3720,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>64789390</v>
@@ -3731,7 +3548,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>280</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3742,7 +3559,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>281</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3753,7 +3570,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>282</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3789,10 +3606,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>283</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3800,10 +3617,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>284</v>
+        <v>192</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3814,7 +3631,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3822,10 +3639,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>285</v>
+        <v>193</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3833,7 +3650,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="C6" s="3">
         <v>25</v>
@@ -3844,10 +3661,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>286</v>
+        <v>194</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3855,7 +3672,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>287</v>
+        <v>195</v>
       </c>
       <c r="C8" s="13">
         <v>9999.99</v>
@@ -3866,10 +3683,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>288</v>
+        <v>196</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3903,7 +3720,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -3914,7 +3731,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>197</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3925,7 +3742,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>290</v>
+        <v>198</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3936,7 +3753,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>199</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3947,7 +3764,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -3958,10 +3775,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>201</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3969,7 +3786,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>294</v>
+        <v>202</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -3980,7 +3797,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -3991,7 +3808,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>295</v>
+        <v>203</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -4002,7 +3819,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -4013,10 +3830,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4024,7 +3841,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>296</v>
+        <v>204</v>
       </c>
       <c r="C13">
         <v>85</v>
@@ -4035,7 +3852,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="C14">
         <v>85</v>
@@ -4046,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>239</v>
+        <v>147</v>
       </c>
       <c r="C15">
         <v>9999.99</v>
@@ -4057,7 +3874,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>240</v>
+        <v>148</v>
       </c>
       <c r="C16">
         <v>9999.99</v>
@@ -4068,10 +3885,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>242</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4079,10 +3896,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>151</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4090,10 +3907,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>244</v>
+        <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4101,7 +3918,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -4112,7 +3929,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -4123,10 +3940,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>247</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4134,7 +3951,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -4145,10 +3962,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>249</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4156,7 +3973,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="C25">
         <v>9867589302</v>
@@ -4167,10 +3984,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>251</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4178,10 +3995,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -4215,7 +4032,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -4226,7 +4043,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>197</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -4237,7 +4054,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>290</v>
+        <v>198</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4248,7 +4065,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>199</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4259,7 +4076,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -4270,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>294</v>
+        <v>202</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -4281,7 +4098,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -4292,7 +4109,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>295</v>
+        <v>203</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -4303,7 +4120,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -4314,10 +4131,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>242</v>
+        <v>150</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4325,10 +4142,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4336,10 +4153,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4347,7 +4164,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4358,7 +4175,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4369,10 +4186,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>155</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4380,7 +4197,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -4391,10 +4208,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>249</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4402,7 +4219,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="C19">
         <v>9867589302</v>
@@ -4413,10 +4230,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>251</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4424,10 +4241,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -4461,10 +4278,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4472,7 +4289,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>205</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4483,10 +4300,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4494,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>167</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4505,10 +4322,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4516,10 +4333,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4527,10 +4344,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4538,10 +4355,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4549,10 +4366,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4560,10 +4377,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4571,10 +4388,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4582,7 +4399,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>298</v>
+        <v>206</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4593,7 +4410,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>280</v>
+        <v>188</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4604,7 +4421,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>281</v>
+        <v>189</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4615,7 +4432,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>282</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -4626,7 +4443,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>299</v>
+        <v>207</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
@@ -4637,10 +4454,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>300</v>
+        <v>208</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4648,10 +4465,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>269</v>
+        <v>177</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4659,10 +4476,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>270</v>
+        <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4670,10 +4487,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>271</v>
+        <v>179</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4681,10 +4498,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>272</v>
+        <v>180</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4692,10 +4509,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4703,10 +4520,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>274</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4714,10 +4531,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>275</v>
+        <v>183</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4725,7 +4542,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="C26">
         <v>2122342342</v>
@@ -4736,10 +4553,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4747,7 +4564,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>301</v>
+        <v>209</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4758,10 +4575,10 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>302</v>
+        <v>210</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -4795,10 +4612,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4806,7 +4623,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>205</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4817,10 +4634,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4828,7 +4645,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>167</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4839,10 +4656,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4850,10 +4667,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4861,10 +4678,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4872,10 +4689,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4883,10 +4700,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4894,10 +4711,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4905,10 +4722,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4916,7 +4733,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>298</v>
+        <v>206</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4927,7 +4744,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>299</v>
+        <v>207</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
@@ -4938,10 +4755,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>300</v>
+        <v>208</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4949,10 +4766,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>269</v>
+        <v>177</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4960,10 +4777,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>270</v>
+        <v>178</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4971,10 +4788,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>271</v>
+        <v>179</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4982,10 +4799,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>272</v>
+        <v>180</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4993,10 +4810,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5004,10 +4821,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>274</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5015,10 +4832,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>275</v>
+        <v>183</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5026,7 +4843,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="C23">
         <v>2122342342</v>
@@ -5037,10 +4854,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5048,7 +4865,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>301</v>
+        <v>209</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -5059,10 +4876,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>302</v>
+        <v>210</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -5154,10 +4971,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5165,7 +4982,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>205</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -5176,10 +4993,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5187,7 +5004,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>167</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5198,10 +5015,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5209,10 +5026,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5220,10 +5037,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5231,10 +5048,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5242,10 +5059,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5253,10 +5070,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5264,10 +5081,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5275,7 +5092,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>298</v>
+        <v>206</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -5286,7 +5103,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>280</v>
+        <v>188</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -5297,7 +5114,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>281</v>
+        <v>189</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -5308,7 +5125,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>282</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -5319,10 +5136,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>300</v>
+        <v>208</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5330,10 +5147,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>269</v>
+        <v>177</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5341,10 +5158,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>270</v>
+        <v>178</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5352,10 +5169,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>271</v>
+        <v>179</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5363,10 +5180,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>272</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5374,10 +5191,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5385,10 +5202,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>274</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5396,10 +5213,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>275</v>
+        <v>183</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5407,7 +5224,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="C25">
         <v>2122342342</v>
@@ -5418,10 +5235,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5429,7 +5246,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>301</v>
+        <v>209</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5440,10 +5257,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>302</v>
+        <v>210</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -5476,7 +5293,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>303</v>
+        <v>211</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -5487,10 +5304,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>304</v>
+        <v>212</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5498,10 +5315,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>305</v>
+        <v>213</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5509,7 +5326,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>306</v>
+        <v>214</v>
       </c>
       <c r="C5">
         <v>1111</v>
@@ -5520,10 +5337,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>300</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -5556,10 +5373,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>307</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5570,7 +5387,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5578,7 +5395,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>308</v>
+        <v>216</v>
       </c>
       <c r="C4">
         <v>76578</v>
@@ -5589,7 +5406,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>309</v>
+        <v>217</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -5600,7 +5417,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>287</v>
+        <v>195</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -5636,10 +5453,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>278</v>
+        <v>186</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5647,7 +5464,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>310</v>
+        <v>218</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5658,10 +5475,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>311</v>
+        <v>219</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5669,7 +5486,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>259</v>
+        <v>167</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5680,10 +5497,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5691,10 +5508,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5702,10 +5519,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5713,10 +5530,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>91</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5724,10 +5541,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5735,10 +5552,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5746,10 +5563,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5757,10 +5574,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>269</v>
+        <v>177</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5768,10 +5585,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>270</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5779,10 +5596,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>271</v>
+        <v>179</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5790,10 +5607,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>272</v>
+        <v>180</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5801,10 +5618,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5812,10 +5629,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5823,7 +5640,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -5834,7 +5651,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>312</v>
+        <v>220</v>
       </c>
       <c r="C20">
         <v>150</v>
@@ -5845,7 +5662,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>313</v>
+        <v>221</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
@@ -5856,7 +5673,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>314</v>
+        <v>222</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
@@ -5867,7 +5684,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>315</v>
+        <v>223</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -5878,10 +5695,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>300</v>
+        <v>208</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5889,7 +5706,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>268</v>
+        <v>176</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -5900,10 +5717,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>316</v>
+        <v>224</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5911,10 +5728,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>317</v>
+        <v>225</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5922,10 +5739,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>318</v>
+        <v>226</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5933,10 +5750,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>319</v>
+        <v>227</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5944,10 +5761,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>320</v>
+        <v>228</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5955,10 +5772,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>321</v>
+        <v>229</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5966,10 +5783,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>275</v>
+        <v>183</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5977,7 +5794,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>250</v>
+        <v>158</v>
       </c>
       <c r="C33" s="15">
         <v>2122342342</v>
@@ -5988,10 +5805,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>322</v>
+        <v>230</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5999,7 +5816,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>301</v>
+        <v>209</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -6010,7 +5827,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>300</v>
+        <v>208</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -6046,10 +5863,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>278</v>
+        <v>186</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="E2" s="16"/>
     </row>
@@ -6058,7 +5875,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>310</v>
+        <v>218</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -6069,10 +5886,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>311</v>
+        <v>219</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6080,7 +5897,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>259</v>
+        <v>167</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -6091,10 +5908,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6102,10 +5919,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6113,10 +5930,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6124,10 +5941,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>91</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6135,10 +5952,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6146,10 +5963,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6157,10 +5974,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6168,10 +5985,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>269</v>
+        <v>177</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6179,10 +5996,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>270</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6190,10 +6007,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>271</v>
+        <v>179</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6201,10 +6018,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>272</v>
+        <v>180</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6212,10 +6029,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6223,10 +6040,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6234,7 +6051,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -6245,10 +6062,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>316</v>
+        <v>224</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6256,10 +6073,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>317</v>
+        <v>225</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6267,10 +6084,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>318</v>
+        <v>226</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6278,10 +6095,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>319</v>
+        <v>227</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6289,10 +6106,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>320</v>
+        <v>228</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6300,10 +6117,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>321</v>
+        <v>229</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6311,10 +6128,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>275</v>
+        <v>183</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6322,7 +6139,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>250</v>
+        <v>158</v>
       </c>
       <c r="C27" s="15">
         <v>2122342342</v>
@@ -6333,10 +6150,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>322</v>
+        <v>230</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6344,7 +6161,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>301</v>
+        <v>209</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6380,7 +6197,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>297</v>
+        <v>205</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6391,7 +6208,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>323</v>
+        <v>231</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -6402,7 +6219,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>324</v>
+        <v>232</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -6413,10 +6230,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>325</v>
+        <v>233</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6424,10 +6241,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>326</v>
+        <v>234</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6435,7 +6252,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>259</v>
+        <v>167</v>
       </c>
       <c r="C7">
         <v>123</v>
@@ -6446,10 +6263,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6457,10 +6274,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6468,10 +6285,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6479,10 +6296,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>91</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6490,10 +6307,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6501,10 +6318,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6512,10 +6329,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6523,7 +6340,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>327</v>
+        <v>235</v>
       </c>
       <c r="C15">
         <v>1234</v>
@@ -6534,7 +6351,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>328</v>
+        <v>236</v>
       </c>
       <c r="C16">
         <v>48</v>
@@ -6545,7 +6362,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>329</v>
+        <v>237</v>
       </c>
       <c r="C17">
         <v>35</v>
@@ -6556,7 +6373,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>330</v>
+        <v>238</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -6567,10 +6384,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>331</v>
+        <v>239</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6578,7 +6395,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>332</v>
+        <v>240</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -6589,7 +6406,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>333</v>
+        <v>241</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6600,10 +6417,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6611,7 +6428,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>335</v>
+        <v>243</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -6622,7 +6439,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>239</v>
+        <v>147</v>
       </c>
       <c r="C24">
         <v>789</v>
@@ -6633,7 +6450,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>336</v>
+        <v>244</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -6644,7 +6461,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>337</v>
+        <v>245</v>
       </c>
       <c r="C26">
         <v>456</v>
@@ -6655,7 +6472,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -6666,10 +6483,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>339</v>
+        <v>247</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6677,7 +6494,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>299</v>
+        <v>207</v>
       </c>
       <c r="C29" t="s">
         <v>51</v>
@@ -6688,7 +6505,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>340</v>
+        <v>248</v>
       </c>
       <c r="C30" t="s">
         <v>51</v>
@@ -6699,7 +6516,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>341</v>
+        <v>249</v>
       </c>
       <c r="C31" t="s">
         <v>51</v>
@@ -6710,7 +6527,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>342</v>
+        <v>250</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -6721,10 +6538,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>343</v>
+        <v>251</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6732,7 +6549,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>344</v>
+        <v>252</v>
       </c>
       <c r="C34" t="s">
         <v>45</v>
@@ -6743,10 +6560,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>345</v>
+        <v>253</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6754,10 +6571,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6765,7 +6582,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>347</v>
+        <v>255</v>
       </c>
       <c r="C37">
         <v>10000</v>
@@ -6776,7 +6593,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="C38">
         <v>8000</v>
@@ -6787,7 +6604,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>349</v>
+        <v>257</v>
       </c>
       <c r="C39">
         <v>6000</v>
@@ -6798,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>350</v>
+        <v>258</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -6809,7 +6626,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
       <c r="C41">
         <v>300</v>
@@ -6820,7 +6637,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>352</v>
+        <v>260</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -6831,10 +6648,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>300</v>
+        <v>208</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -6867,7 +6684,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>297</v>
+        <v>205</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6878,7 +6695,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>259</v>
+        <v>167</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -6889,10 +6706,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6900,10 +6717,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6911,10 +6728,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6922,10 +6739,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>91</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6933,10 +6750,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6944,10 +6761,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6955,7 +6772,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="C10" s="12">
         <v>1234</v>
@@ -6966,7 +6783,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>330</v>
+        <v>238</v>
       </c>
       <c r="C11">
         <v>-8</v>
@@ -6977,7 +6794,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>332</v>
+        <v>240</v>
       </c>
       <c r="C12">
         <v>-300</v>
@@ -6988,7 +6805,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>333</v>
+        <v>241</v>
       </c>
       <c r="C13">
         <v>-200</v>
@@ -6999,7 +6816,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>353</v>
+        <v>261</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -7010,7 +6827,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>239</v>
+        <v>147</v>
       </c>
       <c r="C15">
         <v>-818</v>
@@ -7021,7 +6838,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>336</v>
+        <v>244</v>
       </c>
       <c r="C16">
         <v>-8</v>
@@ -7032,7 +6849,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>337</v>
+        <v>245</v>
       </c>
       <c r="C17">
         <v>-767</v>
@@ -7043,7 +6860,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -7054,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>339</v>
+        <v>247</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>45</v>
@@ -7065,7 +6882,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>341</v>
+        <v>249</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -7076,7 +6893,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>342</v>
+        <v>250</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -7087,7 +6904,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>344</v>
+        <v>252</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -7098,10 +6915,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7109,7 +6926,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>347</v>
+        <v>255</v>
       </c>
       <c r="C24">
         <v>-1000</v>
@@ -7120,7 +6937,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="C25">
         <v>-700</v>
@@ -7131,7 +6948,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>349</v>
+        <v>257</v>
       </c>
       <c r="C26">
         <v>-500</v>
@@ -7142,7 +6959,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>350</v>
+        <v>258</v>
       </c>
       <c r="C27">
         <v>-300</v>
@@ -7153,7 +6970,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>354</v>
+        <v>262</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -7164,7 +6981,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
       <c r="C29">
         <v>-150</v>
@@ -7175,7 +6992,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>352</v>
+        <v>260</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -7186,7 +7003,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>355</v>
+        <v>263</v>
       </c>
       <c r="C31">
         <v>-40</v>
@@ -7222,7 +7039,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7233,10 +7050,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>326</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7244,7 +7061,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>259</v>
+        <v>167</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7255,10 +7072,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7266,10 +7083,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7277,10 +7094,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7288,10 +7105,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>91</v>
+        <v>171</v>
+      </c>
+      <c r="C8" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7299,10 +7116,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7310,10 +7127,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7321,10 +7138,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7332,7 +7149,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>327</v>
+        <v>235</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -7343,7 +7160,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>328</v>
+        <v>236</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -7354,7 +7171,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>329</v>
+        <v>237</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -7365,10 +7182,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>356</v>
+        <v>264</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7376,7 +7193,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>335</v>
+        <v>243</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -7387,7 +7204,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>257</v>
+        <v>165</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -7398,7 +7215,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>330</v>
+        <v>238</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -7409,10 +7226,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>357</v>
+        <v>265</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7420,7 +7237,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>332</v>
+        <v>240</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -7431,7 +7248,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>333</v>
+        <v>241</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -7442,10 +7259,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>358</v>
+        <v>266</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7453,7 +7270,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>239</v>
+        <v>147</v>
       </c>
       <c r="C23">
         <v>789</v>
@@ -7464,7 +7281,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>336</v>
+        <v>244</v>
       </c>
       <c r="C24">
         <v>86</v>
@@ -7475,7 +7292,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>337</v>
+        <v>245</v>
       </c>
       <c r="C25">
         <v>456</v>
@@ -7486,7 +7303,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="C26">
         <v>74</v>
@@ -7497,7 +7314,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>299</v>
+        <v>207</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
@@ -7508,7 +7325,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>341</v>
+        <v>249</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -7519,10 +7336,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>359</v>
+        <v>267</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7530,7 +7347,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>340</v>
+        <v>248</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -7541,10 +7358,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>343</v>
+        <v>251</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7552,7 +7369,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -7563,7 +7380,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -7574,7 +7391,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>295</v>
+        <v>203</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -7585,7 +7402,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>292</v>
+        <v>200</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -7596,7 +7413,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>360</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -7607,7 +7424,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>361</v>
+        <v>269</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -7618,7 +7435,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>362</v>
+        <v>270</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7629,7 +7446,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>363</v>
+        <v>271</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -7640,7 +7457,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>364</v>
+        <v>272</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -7651,10 +7468,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>365</v>
+        <v>273</v>
       </c>
       <c r="C41" t="s">
-        <v>168</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7662,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>366</v>
+        <v>274</v>
       </c>
       <c r="C42">
         <v>400</v>
@@ -7673,7 +7490,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>367</v>
+        <v>275</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7684,7 +7501,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>368</v>
+        <v>276</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -7695,10 +7512,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>242</v>
+        <v>150</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -7732,7 +7549,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7743,7 +7560,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>259</v>
+        <v>167</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -7754,10 +7571,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7765,10 +7582,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7776,10 +7593,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7787,10 +7604,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>91</v>
+        <v>171</v>
+      </c>
+      <c r="C7" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7798,10 +7615,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7809,10 +7626,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7820,10 +7637,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -7856,7 +7673,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7867,10 +7684,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7878,7 +7695,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7889,10 +7706,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7900,10 +7717,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7911,10 +7728,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7922,10 +7739,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>91</v>
+        <v>171</v>
+      </c>
+      <c r="C8" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7933,10 +7750,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" t="s">
         <v>92</v>
-      </c>
-      <c r="C9" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7944,10 +7761,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7955,7 +7772,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="C11" s="12">
         <v>1234</v>
@@ -7966,7 +7783,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>162</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -7977,7 +7794,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>148</v>
+        <v>238</v>
       </c>
       <c r="C13">
         <v>-466</v>
@@ -7988,7 +7805,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="C14">
         <v>-500</v>
@@ -7999,7 +7816,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="C15">
         <v>-400</v>
@@ -8010,7 +7827,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="C16">
         <v>-789</v>
@@ -8021,7 +7838,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>153</v>
+        <v>244</v>
       </c>
       <c r="C17">
         <v>-200</v>
@@ -8032,7 +7849,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>155</v>
+        <v>245</v>
       </c>
       <c r="C18">
         <v>-456</v>
@@ -8043,7 +7860,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="C19">
         <v>-74</v>
@@ -8054,7 +7871,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -8065,7 +7882,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>157</v>
+        <v>248</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -8076,7 +7893,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>164</v>
+        <v>269</v>
       </c>
       <c r="C22">
         <v>-400</v>
@@ -8087,7 +7904,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>183</v>
+        <v>277</v>
       </c>
       <c r="C23">
         <v>-200</v>
@@ -8098,7 +7915,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="C24">
         <v>-100</v>
@@ -8109,7 +7926,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="C25">
         <v>-200</v>
@@ -8120,7 +7937,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>167</v>
+        <v>272</v>
       </c>
       <c r="C26">
         <v>-50</v>
@@ -8131,7 +7948,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>169</v>
+        <v>274</v>
       </c>
       <c r="C27">
         <v>-400</v>
@@ -8142,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>184</v>
+        <v>278</v>
       </c>
       <c r="C28">
         <v>-200</v>
@@ -8153,7 +7970,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>170</v>
+        <v>275</v>
       </c>
       <c r="C29">
         <v>-100</v>
@@ -8164,7 +7981,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>171</v>
+        <v>276</v>
       </c>
       <c r="C30">
         <v>-200</v>
@@ -8175,7 +7992,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>185</v>
+        <v>279</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -8271,7 +8088,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8282,10 +8099,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>174</v>
+        <v>280</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8293,7 +8110,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -8304,10 +8121,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8315,10 +8132,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8326,10 +8143,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8337,10 +8154,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>91</v>
+        <v>171</v>
+      </c>
+      <c r="C8" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8348,10 +8165,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" t="s">
         <v>92</v>
-      </c>
-      <c r="C9" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8359,10 +8176,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8370,10 +8187,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8381,7 +8198,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -8392,7 +8209,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>146</v>
+        <v>236</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -8403,7 +8220,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>147</v>
+        <v>237</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -8414,7 +8231,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>148</v>
+        <v>238</v>
       </c>
       <c r="C15">
         <v>500</v>
@@ -8425,10 +8242,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>172</v>
+        <v>265</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8436,7 +8253,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="C17">
         <v>1000</v>
@@ -8447,7 +8264,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="C18">
         <v>700</v>
@@ -8458,10 +8275,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>173</v>
+        <v>266</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8469,10 +8286,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>176</v>
+        <v>281</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>177</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8480,7 +8297,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>178</v>
+        <v>282</v>
       </c>
       <c r="C21">
         <v>1234</v>
@@ -8491,10 +8308,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>179</v>
+        <v>283</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8502,10 +8319,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>180</v>
+        <v>284</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8513,10 +8330,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8524,7 +8341,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="C25">
         <v>300</v>
@@ -8535,7 +8352,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>153</v>
+        <v>244</v>
       </c>
       <c r="C26">
         <v>85</v>
@@ -8546,7 +8363,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>155</v>
+        <v>245</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -8557,7 +8374,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="C28">
         <v>76</v>
@@ -8568,7 +8385,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>160</v>
+        <v>252</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>45</v>
@@ -8579,7 +8396,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>130</v>
+        <v>207</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>45</v>
@@ -8590,10 +8407,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>163</v>
+        <v>267</v>
       </c>
       <c r="C31" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8601,7 +8418,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>159</v>
+        <v>250</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>45</v>
@@ -8612,10 +8429,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8623,7 +8440,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>181</v>
+        <v>285</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>26</v>
@@ -8634,7 +8451,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>182</v>
+        <v>286</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>26</v>
@@ -8645,7 +8462,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>26</v>
@@ -8681,7 +8498,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8692,7 +8509,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -8703,10 +8520,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8714,10 +8531,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8725,10 +8542,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8736,10 +8553,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>91</v>
+        <v>171</v>
+      </c>
+      <c r="C7" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8747,10 +8564,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" t="s">
         <v>92</v>
-      </c>
-      <c r="C8" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8758,10 +8575,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8769,10 +8586,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -8805,7 +8622,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="C2" s="3">
         <v>1234</v>
@@ -8816,7 +8633,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3">
         <v>123</v>
@@ -8827,10 +8644,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8838,10 +8655,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8849,10 +8666,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8860,10 +8677,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>91</v>
+        <v>171</v>
+      </c>
+      <c r="C7" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8871,10 +8688,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8882,10 +8699,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8893,7 +8710,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="C10" s="15">
         <v>12345</v>
@@ -8904,7 +8721,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>148</v>
+        <v>238</v>
       </c>
       <c r="C11" s="3">
         <v>-500</v>
@@ -8915,7 +8732,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="C12" s="3">
         <v>-1000</v>
@@ -8926,7 +8743,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="C13" s="3">
         <v>-700</v>
@@ -8937,7 +8754,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="C14" s="3">
         <v>-300</v>
@@ -8948,7 +8765,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>153</v>
+        <v>244</v>
       </c>
       <c r="C15" s="3">
         <v>-85</v>
@@ -8959,7 +8776,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>155</v>
+        <v>245</v>
       </c>
       <c r="C16" s="3">
         <v>-200</v>
@@ -8970,7 +8787,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="C17" s="3">
         <v>-76</v>
@@ -8981,7 +8798,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>130</v>
+        <v>207</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>45</v>
@@ -8992,7 +8809,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>159</v>
+        <v>250</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>45</v>
@@ -9003,10 +8820,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>180</v>
+        <v>284</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9014,10 +8831,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>181</v>
+        <v>285</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9025,10 +8842,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>182</v>
+        <v>286</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9036,10 +8853,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -9062,7 +8879,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9073,10 +8890,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>201</v>
+        <v>287</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>186</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9084,10 +8901,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>202</v>
+        <v>288</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9095,10 +8912,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>187</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9106,7 +8923,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="C5" s="3">
         <v>1234</v>
@@ -9117,7 +8934,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>203</v>
+        <v>289</v>
       </c>
       <c r="C6" s="3">
         <v>8967589</v>
@@ -9128,7 +8945,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>205</v>
+        <v>290</v>
       </c>
       <c r="C7" s="3">
         <v>34567</v>
@@ -9139,7 +8956,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="C8" s="3">
         <v>50</v>
@@ -9150,7 +8967,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="C9" s="3">
         <v>100</v>
@@ -9161,10 +8978,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9172,7 +8989,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
@@ -9183,10 +9000,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9194,10 +9011,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9205,10 +9022,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9216,10 +9033,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>91</v>
+        <v>171</v>
+      </c>
+      <c r="C15" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9227,10 +9044,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9238,10 +9055,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9249,10 +9066,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>206</v>
+        <v>291</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>189</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9260,7 +9077,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="C19" s="3">
         <v>123</v>
@@ -9271,10 +9088,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>208</v>
+        <v>293</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>190</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9282,10 +9099,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>209</v>
+        <v>294</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9293,10 +9110,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9304,10 +9121,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>91</v>
+        <v>296</v>
+      </c>
+      <c r="C23" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9315,10 +9132,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>212</v>
+        <v>297</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9326,10 +9143,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>213</v>
+        <v>298</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9337,10 +9154,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>214</v>
+        <v>299</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9348,10 +9165,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>215</v>
+        <v>300</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>192</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9359,10 +9176,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>216</v>
+        <v>301</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>193</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9370,7 +9187,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>217</v>
+        <v>302</v>
       </c>
       <c r="C29" s="3">
         <v>75</v>
@@ -9381,7 +9198,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>218</v>
+        <v>303</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
@@ -9392,7 +9209,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>219</v>
+        <v>304</v>
       </c>
       <c r="C31" s="3">
         <v>85</v>
@@ -9403,7 +9220,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="C32" s="3">
         <v>55</v>
@@ -9414,7 +9231,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>99</v>
+        <v>176</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>5</v>
@@ -9425,10 +9242,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>194</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9436,7 +9253,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -9447,10 +9264,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>100</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9458,10 +9275,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9469,10 +9286,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>195</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9480,10 +9297,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>196</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9491,10 +9308,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9502,10 +9319,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9513,7 +9330,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="C42" s="3">
         <v>9869875890</v>
@@ -9524,10 +9341,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>221</v>
+        <v>306</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>197</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9535,7 +9352,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="C44" s="3">
         <v>20</v>
@@ -9546,10 +9363,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9557,10 +9374,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>136</v>
+        <v>225</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>198</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9568,10 +9385,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9579,10 +9396,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>138</v>
+        <v>227</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>195</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9590,10 +9407,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>139</v>
+        <v>229</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>200</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9601,7 +9418,7 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="C50" s="3">
         <v>9869875890</v>
@@ -9626,7 +9443,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9637,10 +9454,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>287</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>186</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9648,10 +9465,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>288</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9659,10 +9476,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>187</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9670,7 +9487,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="C5" s="3">
         <v>50</v>
@@ -9681,7 +9498,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="C6" s="3">
         <v>100</v>
@@ -9692,10 +9509,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9703,7 +9520,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="C8" s="3">
         <v>123</v>
@@ -9714,10 +9531,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9725,10 +9542,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9736,10 +9553,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9747,10 +9564,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>91</v>
+        <v>171</v>
+      </c>
+      <c r="C12" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9758,10 +9575,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9769,7 +9586,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="C14" s="3">
         <v>12345</v>
@@ -9780,10 +9597,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>206</v>
+        <v>291</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>189</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9791,7 +9608,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="C16" s="3">
         <v>123</v>
@@ -9802,10 +9619,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>208</v>
+        <v>293</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>190</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9813,10 +9630,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>209</v>
+        <v>294</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9824,10 +9641,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9835,10 +9652,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>211</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>91</v>
+        <v>296</v>
+      </c>
+      <c r="C20" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9846,10 +9663,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>212</v>
+        <v>297</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9857,7 +9674,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>213</v>
+        <v>298</v>
       </c>
       <c r="C22" s="3">
         <v>12345</v>
@@ -9868,10 +9685,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>214</v>
+        <v>299</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9879,10 +9696,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>215</v>
+        <v>300</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>192</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9890,10 +9707,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>216</v>
+        <v>301</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>193</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9901,7 +9718,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>217</v>
+        <v>302</v>
       </c>
       <c r="C26" s="3">
         <v>-75</v>
@@ -9912,7 +9729,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>218</v>
+        <v>303</v>
       </c>
       <c r="C27" s="3">
         <v>-65</v>
@@ -9923,7 +9740,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>219</v>
+        <v>304</v>
       </c>
       <c r="C28" s="3">
         <v>-85</v>
@@ -9934,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="C29" s="3">
         <v>-55</v>
@@ -9945,10 +9762,10 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>194</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9956,7 +9773,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -9967,10 +9784,10 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>221</v>
+        <v>306</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>197</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9978,7 +9795,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="C33" s="3">
         <v>20</v>
@@ -10175,7 +9992,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -10186,7 +10003,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>29</v>
@@ -10267,7 +10084,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>42</v>
@@ -10278,7 +10095,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>41</v>
@@ -10347,7 +10164,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>37</v>
@@ -10358,7 +10175,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>38</v>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9CA75D-3E16-4FFD-B021-75A6D77675CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3376FB6C-54E3-468A-BF9A-7A5CB1A6EC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="21" activeTab="21" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="40" activeTab="43" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="308">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -279,9 +279,6 @@
     <t>Construction</t>
   </si>
   <si>
-    <t>fieldInternalOrganization__c</t>
-  </si>
-  <si>
     <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
   </si>
   <si>
@@ -306,33 +303,9 @@
     <t>fieldFrequency__c</t>
   </si>
   <si>
-    <t>fieldGoverningOrganizationReportDate__c</t>
-  </si>
-  <si>
-    <t>fieldBoardInformation__c</t>
-  </si>
-  <si>
-    <t>fieldCalReportingStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldCalReportingEndDate__c</t>
-  </si>
-  <si>
-    <t>fieldFederalGrantIdentifyingNumbe__c</t>
-  </si>
-  <si>
-    <t>fieldRequestFederalAgencyDispositionInstr__c</t>
-  </si>
-  <si>
     <t>(i) Sale Proceeds OR</t>
   </si>
   <si>
-    <t>fieldFederalShare__c</t>
-  </si>
-  <si>
-    <t>fieldComments__c</t>
-  </si>
-  <si>
     <t>Automation Test</t>
   </si>
   <si>
@@ -342,111 +315,36 @@
     <t>John Mathews</t>
   </si>
   <si>
-    <t>fieldTelephone2__c</t>
-  </si>
-  <si>
-    <t>fieldEmailAddress__c</t>
-  </si>
-  <si>
     <t>automation@yopmail.com</t>
   </si>
   <si>
-    <t>fieldFederalAgencySF428__c</t>
-  </si>
-  <si>
-    <t>fieldAORDateSubmitted__c</t>
-  </si>
-  <si>
-    <t>fieldRecipientOrganizationNameSF428__c</t>
-  </si>
-  <si>
-    <t>fieldStreet1SF428__c</t>
-  </si>
-  <si>
-    <t>fieldStreet2SF428__c</t>
-  </si>
-  <si>
-    <t>fieldCitySF428__c</t>
-  </si>
-  <si>
-    <t>fieldCountySF428__c</t>
-  </si>
-  <si>
-    <t>fieldStateSf428__c</t>
-  </si>
-  <si>
-    <t>NY: New York</t>
-  </si>
-  <si>
-    <t>fieldProvinceSF428__c</t>
-  </si>
-  <si>
     <t>NY</t>
   </si>
   <si>
-    <t>fieldCountrySF428__c</t>
-  </si>
-  <si>
     <t>USA: UNITED STATES</t>
   </si>
   <si>
-    <t>fieldZipPostalCodeSF428__c</t>
-  </si>
-  <si>
     <t>12345-1234</t>
   </si>
   <si>
-    <t>fieldRemark__c</t>
-  </si>
-  <si>
-    <t>fieldAcknowledgementSF428__c</t>
-  </si>
-  <si>
-    <t>fieldPrefix__c</t>
-  </si>
-  <si>
     <t>Mr.</t>
   </si>
   <si>
-    <t>fieldFirstNameSF428__c</t>
-  </si>
-  <si>
     <t>John</t>
   </si>
   <si>
-    <t>fieldMiddleNameSF428__c</t>
-  </si>
-  <si>
     <t>Andrew</t>
   </si>
   <si>
-    <t>fieldLastNameSF428__c</t>
-  </si>
-  <si>
     <t>Mathews</t>
   </si>
   <si>
-    <t>fieldSuffix__c</t>
-  </si>
-  <si>
     <t>Jr.</t>
   </si>
   <si>
-    <t>fieldTitleSF429__c</t>
-  </si>
-  <si>
     <t>Associate</t>
   </si>
   <si>
-    <t>fieldSubmittedBySF428__c</t>
-  </si>
-  <si>
-    <t>fieldTelephone__c</t>
-  </si>
-  <si>
-    <t>fieldSubmittedOn__c</t>
-  </si>
-  <si>
     <t>Automation Test Organization</t>
   </si>
   <si>
@@ -462,18 +360,6 @@
     <t>New York</t>
   </si>
   <si>
-    <t>fieldFederalAgencyandOrganizationalSF429__c</t>
-  </si>
-  <si>
-    <t>fieldAnnualReportSF428A__c</t>
-  </si>
-  <si>
-    <t>fieldFinalReportSF428B__c</t>
-  </si>
-  <si>
-    <t>fieldDispositionReportRequestSF428C__c</t>
-  </si>
-  <si>
     <t>ACQ</t>
   </si>
   <si>
@@ -489,15 +375,6 @@
     <t>gefakzgrpvjjbdneasuz</t>
   </si>
   <si>
-    <t>fieldRequestTransfertoAward__c</t>
-  </si>
-  <si>
-    <t>fieldFederalAwardIdentifier__c</t>
-  </si>
-  <si>
-    <t>fieldAcknowledgeEquipment__c</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
@@ -507,273 +384,45 @@
     <t>Federal Agency and Organizational</t>
   </si>
   <si>
-    <t>fieldFederalGrantIdentifyingNumberSF428__c</t>
-  </si>
-  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>fieldRecipientAccountNumberSF428__c</t>
-  </si>
-  <si>
-    <t>fieldSupplementalSheet__c</t>
-  </si>
-  <si>
-    <t>fieldCommentsSF428__c</t>
-  </si>
-  <si>
-    <t>fieldDateReportSubmittedSF428__c</t>
-  </si>
-  <si>
-    <t>fieldAgencyCommentsSF428__c</t>
-  </si>
-  <si>
-    <t>fieldFederalGrantSF428A__c</t>
-  </si>
-  <si>
     <t>(a) Individual (Reporting Federally-owned property for one award)</t>
   </si>
   <si>
     <t>30 SEP</t>
   </si>
   <si>
-    <t>fieldFederalGrantIdentifyingNumberSF429__c</t>
-  </si>
-  <si>
-    <t>fieldRecipientOrganizationNameSF429__c</t>
-  </si>
-  <si>
-    <t>fieldReportEndDate__c</t>
-  </si>
-  <si>
-    <t>fieldAttachmentA__c</t>
-  </si>
-  <si>
-    <t>fieldAttachmentB__c</t>
-  </si>
-  <si>
-    <t>fieldAttachmentC__c</t>
-  </si>
-  <si>
     <t>Automation test</t>
   </si>
   <si>
-    <t>fieldTypeorPrintedPrefix__c</t>
-  </si>
-  <si>
-    <t>fieldTypeorPrintedFirstName__c</t>
-  </si>
-  <si>
-    <t>fieldTypeorPrintedMiddleName__c</t>
-  </si>
-  <si>
-    <t>fieldTypeorPrintedLastName__c</t>
-  </si>
-  <si>
-    <t>fieldTypeorPrintedSuffix__c</t>
-  </si>
-  <si>
-    <t>fieldTypeorPrintedTitle__c</t>
-  </si>
-  <si>
-    <t>fieldEmailAddress2__c</t>
-  </si>
-  <si>
-    <t>fieldPeriodStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldPeriodEndDate__c</t>
-  </si>
-  <si>
-    <t>fieldTypeOfFederalInterest__c</t>
-  </si>
-  <si>
     <t>Renovation</t>
   </si>
   <si>
-    <t>fieldDescriptionofRealProperty__c</t>
-  </si>
-  <si>
     <t>Street1</t>
   </si>
   <si>
-    <t>fieldZoningInformation__c</t>
-  </si>
-  <si>
-    <t>fieldGPSLocationLongitude__c</t>
-  </si>
-  <si>
-    <t>fieldGPSLocationLatitude__c</t>
-  </si>
-  <si>
-    <t>fieldLandAcreageAmount__c</t>
-  </si>
-  <si>
-    <t>fieldUnits__c</t>
-  </si>
-  <si>
     <t>Acres</t>
   </si>
   <si>
-    <t>fieldSquareFootageGross__c</t>
-  </si>
-  <si>
-    <t>fieldSquareFootageUsable__c</t>
-  </si>
-  <si>
-    <t>fieldUnit2__c</t>
-  </si>
-  <si>
     <t>Square Feet</t>
   </si>
   <si>
-    <t>fieldOwned__c</t>
-  </si>
-  <si>
-    <t>fieldFederalSharePercentage__c</t>
-  </si>
-  <si>
-    <t>fieldNon_FederalSharePercentage__c</t>
-  </si>
-  <si>
-    <t>fieldNonFederalShare__c</t>
-  </si>
-  <si>
-    <t>fieldHasaDeed__c</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>fieldFederallyRequiredInsurance__c</t>
-  </si>
-  <si>
-    <t>fieldEnvironmentalComplianceRequirements__c</t>
-  </si>
-  <si>
-    <t>fieldNationalHistoricPreservation__c</t>
-  </si>
-  <si>
-    <t>fieldNHPADescription__c</t>
-  </si>
-  <si>
-    <t>fieldSignificantChange__c</t>
-  </si>
-  <si>
-    <t>fieldSignificantChangeDescription__c</t>
-  </si>
-  <si>
-    <t>fieldRealPropertyDispositionStatus__c</t>
-  </si>
-  <si>
     <t>A. Sold</t>
   </si>
   <si>
-    <t>fieldFundsOwed__c</t>
-  </si>
-  <si>
-    <t>fieldNetProceeds__c</t>
-  </si>
-  <si>
-    <t>fieldFederalAgencyOwes__c</t>
-  </si>
-  <si>
-    <t>fieldAElectrickWh__c</t>
-  </si>
-  <si>
-    <t>fieldBPetroleumGal__c</t>
-  </si>
-  <si>
-    <t>fieldCNaturalGascuft__c</t>
-  </si>
-  <si>
-    <t>fieldDOther__c</t>
-  </si>
-  <si>
-    <t>fieldOtherDescribe__c</t>
-  </si>
-  <si>
-    <t>fieldBtu__c</t>
-  </si>
-  <si>
-    <t>fieldSF429B__c</t>
-  </si>
-  <si>
-    <t>fieldEnvironmentalDescription__c</t>
-  </si>
-  <si>
-    <t>fieldNoneoftheAbove__c</t>
-  </si>
-  <si>
-    <t>fieldElectric429B__c</t>
-  </si>
-  <si>
-    <t>fieldPetroleum429B__c</t>
-  </si>
-  <si>
-    <t>fieldNaturalGas429B__c</t>
-  </si>
-  <si>
-    <t>fieldOther429B__c</t>
-  </si>
-  <si>
-    <t>fieldSpecify__c</t>
-  </si>
-  <si>
     <t>Test Gas</t>
   </si>
   <si>
-    <t>fieldElectric__c</t>
-  </si>
-  <si>
-    <t>fieldPetroleum__c</t>
-  </si>
-  <si>
-    <t>fieldNaturalGas__c</t>
-  </si>
-  <si>
-    <t>fieldSelectunits__c</t>
-  </si>
-  <si>
-    <t>fieldSelect_units__c</t>
-  </si>
-  <si>
-    <t>fieldDescription429C__c</t>
-  </si>
-  <si>
     <t>Autmation Test</t>
   </si>
   <si>
-    <t>fieldDispositionPreferenceSF429C__c</t>
-  </si>
-  <si>
     <t>A. Sell</t>
   </si>
   <si>
-    <t>fieldGrantNumber__c</t>
-  </si>
-  <si>
-    <t>fieldTitleSF428__c</t>
-  </si>
-  <si>
-    <t>fieldIntendedUse__c</t>
-  </si>
-  <si>
-    <t>fieldEncumberedParties__c</t>
-  </si>
-  <si>
-    <t>fieldRequestReasons__c</t>
-  </si>
-  <si>
-    <t>fieldor_Btu_429B__c</t>
-  </si>
-  <si>
-    <t>fieldorBtu__c</t>
-  </si>
-  <si>
-    <t>fieldOtherEnergy__c</t>
-  </si>
-  <si>
     <t>Final</t>
   </si>
   <si>
@@ -819,69 +468,9 @@
     <t>Junior</t>
   </si>
   <si>
-    <t>fieldTypeOfRequest__c</t>
-  </si>
-  <si>
-    <t>fieldBasisOfRequest__c</t>
-  </si>
-  <si>
-    <t>fieldPartialPaymentRequest__c</t>
-  </si>
-  <si>
     <t>FieldAPIName</t>
   </si>
   <si>
-    <t>fieldFinancialAssistance__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeOrganizationName__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeStreet1__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeStreet2__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeCity__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeCounty__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeState__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeProvince__c</t>
-  </si>
-  <si>
-    <t>fieldPayeeZipCode__c</t>
-  </si>
-  <si>
-    <t>fieldPrograms__c</t>
-  </si>
-  <si>
-    <t>fieldFunctions__c</t>
-  </si>
-  <si>
-    <t>fieldActivities__c</t>
-  </si>
-  <si>
-    <t>fieldProgramPercentage__c</t>
-  </si>
-  <si>
-    <t>fieldFunctionPercentage__c</t>
-  </si>
-  <si>
-    <t>fieldActivityPercentage__c</t>
-  </si>
-  <si>
-    <t>fieldTotalPercentage271__c</t>
-  </si>
-  <si>
-    <t>fieldSignatureofAuthorized__c</t>
-  </si>
-  <si>
     <t>GoverningOrganizationReportDate__c</t>
   </si>
   <si>
@@ -894,6 +483,9 @@
     <t>CalReportingEndDate__c</t>
   </si>
   <si>
+    <t>InternalOrganization__c</t>
+  </si>
+  <si>
     <t>FederalGrantIdentifyingNumbe__c</t>
   </si>
   <si>
@@ -906,12 +498,6 @@
     <t>RequestApprovalSF428C__c</t>
   </si>
   <si>
-    <t xml:space="preserve"> API Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Value</t>
-  </si>
-  <si>
     <t>RequestApproval2SF428C__c</t>
   </si>
   <si>
@@ -978,6 +564,96 @@
     <t>EmailAddress__c</t>
   </si>
   <si>
+    <t>FederalAgencySF428__c</t>
+  </si>
+  <si>
+    <t>ReportType__c</t>
+  </si>
+  <si>
+    <t>BasisOfAccounting__c</t>
+  </si>
+  <si>
+    <t>AcquiredDate__c</t>
+  </si>
+  <si>
+    <t>AORDateSubmitted__c</t>
+  </si>
+  <si>
+    <t>RecipientOrganizationNameSF428__c</t>
+  </si>
+  <si>
+    <t>Street1SF428__c</t>
+  </si>
+  <si>
+    <t>Street2SF428__c</t>
+  </si>
+  <si>
+    <t>CitySF428__c</t>
+  </si>
+  <si>
+    <t>CountySF428__c</t>
+  </si>
+  <si>
+    <t>StateSf428__c</t>
+  </si>
+  <si>
+    <t>ProvinceSF428__c</t>
+  </si>
+  <si>
+    <t>CountrySF428__c</t>
+  </si>
+  <si>
+    <t>ZipPostalCodeSF428__c</t>
+  </si>
+  <si>
+    <t>Remark__c</t>
+  </si>
+  <si>
+    <t>AcknowledgementSF428__c</t>
+  </si>
+  <si>
+    <t>Prefix__c</t>
+  </si>
+  <si>
+    <t>FirstNameSF428__c</t>
+  </si>
+  <si>
+    <t>MiddleNameSF428__c</t>
+  </si>
+  <si>
+    <t>LastNameSF428__c</t>
+  </si>
+  <si>
+    <t>Suffix__c</t>
+  </si>
+  <si>
+    <t>TitleSF429__c</t>
+  </si>
+  <si>
+    <t>SubmittedBySF428__c</t>
+  </si>
+  <si>
+    <t>Telephone__c</t>
+  </si>
+  <si>
+    <t>SubmittedOn__c</t>
+  </si>
+  <si>
+    <t>FederalAgencyandOrganizationalSF429__c</t>
+  </si>
+  <si>
+    <t>Date__c</t>
+  </si>
+  <si>
+    <t>AnnualReportSF428A__c</t>
+  </si>
+  <si>
+    <t>FinalReportSF428B__c</t>
+  </si>
+  <si>
+    <t>DispositionReportRequestSF428C__c</t>
+  </si>
+  <si>
     <t>FederalAwardNumber__c</t>
   </si>
   <si>
@@ -987,9 +663,6 @@
     <t>IdentificationNumber__c</t>
   </si>
   <si>
-    <t>AcquiredDate__c</t>
-  </si>
-  <si>
     <t>ConditionCode__c</t>
   </si>
   <si>
@@ -1011,21 +684,36 @@
     <t>RequestTransfertoAward__c</t>
   </si>
   <si>
+    <t>FederalAwardIdentifier__c</t>
+  </si>
+  <si>
     <t>RequestFederalAgency__c</t>
   </si>
   <si>
     <t>AcknowledgeEquipment__c</t>
   </si>
   <si>
-    <t>Telephone__c</t>
-  </si>
-  <si>
-    <t>FederalAwardIdentifier__c</t>
-  </si>
-  <si>
     <t>TotalAmount__c</t>
   </si>
   <si>
+    <t>FederalGrantIdentifyingNumberSF428__c</t>
+  </si>
+  <si>
+    <t>RecipientAccountNumberSF428__c</t>
+  </si>
+  <si>
+    <t>SupplementalSheet__c</t>
+  </si>
+  <si>
+    <t>CommentsSF428__c</t>
+  </si>
+  <si>
+    <t>DateReportSubmittedSF428__c</t>
+  </si>
+  <si>
+    <t>AgencyCommentsSF428__c</t>
+  </si>
+  <si>
     <t>FederalGrantSF428A__c</t>
   </si>
   <si>
@@ -1038,84 +726,6 @@
     <t>SEP30__c</t>
   </si>
   <si>
-    <t>CommentsSF428__c</t>
-  </si>
-  <si>
-    <t>FederalAgencySF428__c</t>
-  </si>
-  <si>
-    <t>FederalGrantIdentifyingNumberSF428__c</t>
-  </si>
-  <si>
-    <t>RecipientOrganizationNameSF428__c</t>
-  </si>
-  <si>
-    <t>Street1SF428__c</t>
-  </si>
-  <si>
-    <t>Street2SF428__c</t>
-  </si>
-  <si>
-    <t>CitySF428__c</t>
-  </si>
-  <si>
-    <t>CountySF428__c</t>
-  </si>
-  <si>
-    <t>StateSf428__c</t>
-  </si>
-  <si>
-    <t>ProvinceSF428__c</t>
-  </si>
-  <si>
-    <t>CountrySF428__c</t>
-  </si>
-  <si>
-    <t>ZipPostalCodeSF428__c</t>
-  </si>
-  <si>
-    <t>RecipientAccountNumberSF428__c</t>
-  </si>
-  <si>
-    <t>AnnualReportSF428A__c</t>
-  </si>
-  <si>
-    <t>FinalReportSF428B__c</t>
-  </si>
-  <si>
-    <t>DispositionReportRequestSF428C__c</t>
-  </si>
-  <si>
-    <t>SupplementalSheet__c</t>
-  </si>
-  <si>
-    <t>Prefix__c</t>
-  </si>
-  <si>
-    <t>FirstNameSF428__c</t>
-  </si>
-  <si>
-    <t>MiddleNameSF428__c</t>
-  </si>
-  <si>
-    <t>LastNameSF428__c</t>
-  </si>
-  <si>
-    <t>Suffix__c</t>
-  </si>
-  <si>
-    <t>TitleSF429__c</t>
-  </si>
-  <si>
-    <t>SubmittedBySF428__c</t>
-  </si>
-  <si>
-    <t>DateReportSubmittedSF428__c</t>
-  </si>
-  <si>
-    <t>AgencyCommentsSF428__c</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -1125,28 +735,274 @@
     <t>AcquisitionDate__c</t>
   </si>
   <si>
-    <t>FederalAgencyandOrganizationalSF429__c</t>
-  </si>
-  <si>
-    <t>Date__c</t>
-  </si>
-  <si>
-    <t>ReportType__c</t>
-  </si>
-  <si>
-    <t>BasisOfAccounting__c</t>
-  </si>
-  <si>
-    <t>AORDateSubmitted__c</t>
-  </si>
-  <si>
-    <t>Remark__c</t>
-  </si>
-  <si>
-    <t>AcknowledgementSF428__c</t>
-  </si>
-  <si>
-    <t>SubmittedOn__c</t>
+    <t>FederalGrantIdentifyingNumberSF429__c</t>
+  </si>
+  <si>
+    <t>RecipientOrganizationNameSF429__c</t>
+  </si>
+  <si>
+    <t>ReportEndDate__c</t>
+  </si>
+  <si>
+    <t>AttachmentA__c</t>
+  </si>
+  <si>
+    <t>AttachmentB__c</t>
+  </si>
+  <si>
+    <t>AttachmentC__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedPrefix__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedFirstName__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedMiddleName__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedLastName__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedSuffix__c</t>
+  </si>
+  <si>
+    <t>TypeorPrintedTitle__c</t>
+  </si>
+  <si>
+    <t>EmailAddress2__c</t>
+  </si>
+  <si>
+    <t>PeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>PeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>TypeOfFederalInterest__c</t>
+  </si>
+  <si>
+    <t>DescriptionofRealProperty__c</t>
+  </si>
+  <si>
+    <t>ZoningInformation__c</t>
+  </si>
+  <si>
+    <t>GPSLocationLongitude__c</t>
+  </si>
+  <si>
+    <t>GPSLocationLatitude__c</t>
+  </si>
+  <si>
+    <t>LandAcreageAmount__c</t>
+  </si>
+  <si>
+    <t>Units__c</t>
+  </si>
+  <si>
+    <t>SquareFootageGross__c</t>
+  </si>
+  <si>
+    <t>SquareFootageUsable__c</t>
+  </si>
+  <si>
+    <t>Unit2__c</t>
+  </si>
+  <si>
+    <t>Owned__c</t>
+  </si>
+  <si>
+    <t>FederalSharePercentage__c</t>
+  </si>
+  <si>
+    <t>NonFederalShare__c</t>
+  </si>
+  <si>
+    <t>Non_FederalSharePercentage__c</t>
+  </si>
+  <si>
+    <t>HasaDeed__c</t>
+  </si>
+  <si>
+    <t>FederallyRequiredInsurance__c</t>
+  </si>
+  <si>
+    <t>EnvironmentalComplianceRequirements__c</t>
+  </si>
+  <si>
+    <t>NationalHistoricPreservation__c</t>
+  </si>
+  <si>
+    <t>NHPADescription__c</t>
+  </si>
+  <si>
+    <t>SignificantChange__c</t>
+  </si>
+  <si>
+    <t>SignificantChangeDescription__c</t>
+  </si>
+  <si>
+    <t>RealPropertyDispositionStatus__c</t>
+  </si>
+  <si>
+    <t>FundsOwed__c</t>
+  </si>
+  <si>
+    <t>NetProceeds__c</t>
+  </si>
+  <si>
+    <t>FederalAgencyOwes__c</t>
+  </si>
+  <si>
+    <t>AElectrickWh__c</t>
+  </si>
+  <si>
+    <t>BPetroleumGal__c</t>
+  </si>
+  <si>
+    <t>CNaturalGascuft__c</t>
+  </si>
+  <si>
+    <t>OtherDescribe__c</t>
+  </si>
+  <si>
+    <t>Btu__c</t>
+  </si>
+  <si>
+    <t>DOther__c</t>
+  </si>
+  <si>
+    <t>SF429B__c</t>
+  </si>
+  <si>
+    <t>Selectunits__c</t>
+  </si>
+  <si>
+    <t>Select_units__c</t>
+  </si>
+  <si>
+    <t>EnvironmentalDescription__c</t>
+  </si>
+  <si>
+    <t>NoneoftheAbove__c</t>
+  </si>
+  <si>
+    <t>Electric429B__c</t>
+  </si>
+  <si>
+    <t>Petroleum429B__c</t>
+  </si>
+  <si>
+    <t>NaturalGas429B__c</t>
+  </si>
+  <si>
+    <t>Other429B__c</t>
+  </si>
+  <si>
+    <t>Specify__c</t>
+  </si>
+  <si>
+    <t>Electric__c</t>
+  </si>
+  <si>
+    <t>Petroleum__c</t>
+  </si>
+  <si>
+    <t>NaturalGas__c</t>
+  </si>
+  <si>
+    <t>or_Btu_429B__c</t>
+  </si>
+  <si>
+    <t>orBtu__c</t>
+  </si>
+  <si>
+    <t>OtherEnergy__c</t>
+  </si>
+  <si>
+    <t>Description429C__c</t>
+  </si>
+  <si>
+    <t>DispositionPreferenceSF429C__c</t>
+  </si>
+  <si>
+    <t>GrantNumber__c</t>
+  </si>
+  <si>
+    <t>TitleSF428__c</t>
+  </si>
+  <si>
+    <t>IntendedUse__c</t>
+  </si>
+  <si>
+    <t>EncumberedParties__c</t>
+  </si>
+  <si>
+    <t>RequestReasons__c</t>
+  </si>
+  <si>
+    <t>TypeOfRequest__c</t>
+  </si>
+  <si>
+    <t>BasisOfRequest__c</t>
+  </si>
+  <si>
+    <t>PartialPaymentRequest__c</t>
+  </si>
+  <si>
+    <t>FinancialAssistance__c</t>
+  </si>
+  <si>
+    <t>PayeeOrganizationName__c</t>
+  </si>
+  <si>
+    <t>PayeeStreet1__c</t>
+  </si>
+  <si>
+    <t>PayeeStreet2__c</t>
+  </si>
+  <si>
+    <t>PayeeCity__c</t>
+  </si>
+  <si>
+    <t>PayeeCounty__c</t>
+  </si>
+  <si>
+    <t>PayeeState__c</t>
+  </si>
+  <si>
+    <t>PayeeProvince__c</t>
+  </si>
+  <si>
+    <t>PayeeZipCode__c</t>
+  </si>
+  <si>
+    <t>Programs__c</t>
+  </si>
+  <si>
+    <t>Functions__c</t>
+  </si>
+  <si>
+    <t>Activities__c</t>
+  </si>
+  <si>
+    <t>ProgramPercentage__c</t>
+  </si>
+  <si>
+    <t>FunctionPercentage__c</t>
+  </si>
+  <si>
+    <t>ActivityPercentage__c</t>
+  </si>
+  <si>
+    <t>TotalPercentage271__c</t>
+  </si>
+  <si>
+    <t>SignatureofAuthorized__c</t>
+  </si>
+  <si>
+    <t>FL: Florida</t>
   </si>
 </sst>
 </file>
@@ -1208,8 +1064,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF1F1F1F"/>
+      <sz val="7"/>
+      <color rgb="FF454545"/>
       <name val="Courier New"/>
       <family val="3"/>
     </font>
@@ -1577,11 +1433,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1648,7 +1504,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1714,7 +1570,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>32</v>
@@ -1725,7 +1581,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>33</v>
@@ -1739,7 +1595,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1805,7 +1661,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>34</v>
@@ -1816,7 +1672,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>36</v>
@@ -1848,10 +1704,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="158" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1915,7 +1771,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>267</v>
+        <v>130</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1926,7 +1782,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>268</v>
+        <v>131</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -1940,10 +1796,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C922EE-7D55-45ED-84C0-E643E295F423}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1995,7 +1851,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="C5" s="3">
         <v>-2</v>
@@ -2006,7 +1862,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>20</v>
@@ -2020,10 +1876,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2064,7 +1920,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="C4" s="3">
         <v>-2</v>
@@ -2075,7 +1931,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>20</v>
@@ -2089,10 +1945,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2114,7 +1970,7 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2165,11 +2021,11 @@
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" t="s">
         <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2177,10 +2033,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
         <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2188,10 +2044,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2202,9 +2058,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2362,10 +2218,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2387,7 +2243,7 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2439,10 +2295,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" t="s">
         <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2450,10 +2306,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
         <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2461,10 +2317,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2475,10 +2331,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2500,7 +2356,7 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2552,10 +2408,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" t="s">
         <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2563,10 +2419,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
         <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2574,10 +2430,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2588,10 +2444,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5CE5DD-3172-4B5D-9DF0-D4E246B7968A}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2599,10 +2455,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2610,7 +2466,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2621,7 +2477,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2632,7 +2488,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>273</v>
+        <v>137</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2643,7 +2499,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>138</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2654,7 +2510,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>277</v>
+        <v>139</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2665,7 +2521,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>278</v>
+        <v>140</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2676,7 +2532,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>279</v>
+        <v>141</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2687,7 +2543,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>280</v>
+        <v>142</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2698,7 +2554,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>281</v>
+        <v>143</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2709,10 +2565,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>282</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2720,7 +2576,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>283</v>
+        <v>145</v>
       </c>
       <c r="C12" s="10">
         <v>9999.99</v>
@@ -2731,7 +2587,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>284</v>
+        <v>146</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -2742,7 +2598,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>285</v>
+        <v>147</v>
       </c>
       <c r="C14" s="10">
         <v>9999.99</v>
@@ -2753,7 +2609,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>286</v>
+        <v>148</v>
       </c>
       <c r="C15" s="10">
         <v>1000</v>
@@ -2764,7 +2620,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>287</v>
+        <v>149</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>5</v>
@@ -2775,10 +2631,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>288</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2786,10 +2642,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>289</v>
+        <v>151</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2797,10 +2653,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>290</v>
+        <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2808,7 +2664,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>291</v>
+        <v>153</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>5</v>
@@ -2819,7 +2675,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>292</v>
+        <v>154</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>5</v>
@@ -2830,10 +2686,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>293</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2841,7 +2697,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>294</v>
+        <v>156</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2852,10 +2708,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>295</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2863,7 +2719,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>296</v>
+        <v>158</v>
       </c>
       <c r="C25">
         <v>8967045891</v>
@@ -2874,10 +2730,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>297</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2885,10 +2741,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>298</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2900,10 +2756,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2982,9 +2838,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB2637BC-983B-4C46-AEC7-148BA71B263A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3004,7 +2860,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -3018,10 +2874,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3029,10 +2885,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3040,7 +2896,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -3051,7 +2907,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -3062,7 +2918,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>273</v>
+        <v>137</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -3073,7 +2929,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>138</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -3084,7 +2940,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>277</v>
+        <v>139</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -3095,7 +2951,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>278</v>
+        <v>140</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -3106,7 +2962,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>279</v>
+        <v>141</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -3117,7 +2973,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>280</v>
+        <v>142</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -3128,7 +2984,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>281</v>
+        <v>143</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -3139,7 +2995,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>287</v>
+        <v>149</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>5</v>
@@ -3150,10 +3006,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>289</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3161,10 +3017,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>290</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3172,7 +3028,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>291</v>
+        <v>153</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -3183,7 +3039,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>292</v>
+        <v>154</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -3194,10 +3050,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>293</v>
+        <v>155</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3205,7 +3061,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>294</v>
+        <v>156</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3216,10 +3072,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>295</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3227,7 +3083,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>296</v>
+        <v>158</v>
       </c>
       <c r="C19">
         <v>8967045891</v>
@@ -3238,10 +3094,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>297</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3249,10 +3105,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>298</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3263,7 +3119,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
@@ -3274,10 +3130,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3285,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3296,10 +3152,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3307,10 +3163,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>350</v>
+        <v>162</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3318,10 +3174,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>351</v>
+        <v>163</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3329,7 +3185,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>302</v>
+        <v>164</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -3340,7 +3196,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>294</v>
+        <v>156</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -3351,7 +3207,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>352</v>
+        <v>165</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3362,10 +3218,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>322</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3373,7 +3229,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>323</v>
+        <v>167</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3384,10 +3240,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>324</v>
+        <v>168</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3395,10 +3251,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>325</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3406,10 +3262,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>326</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3417,10 +3273,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>327</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3428,10 +3284,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>328</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3439,10 +3295,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>329</v>
+        <v>173</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3450,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>330</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3461,10 +3317,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>353</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3472,7 +3328,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>354</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3483,10 +3339,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>336</v>
+        <v>177</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3494,10 +3350,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>337</v>
+        <v>178</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3505,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>338</v>
+        <v>179</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3516,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>339</v>
+        <v>180</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3527,10 +3383,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>340</v>
+        <v>181</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3538,10 +3394,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>341</v>
+        <v>182</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3549,10 +3405,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>342</v>
+        <v>183</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3560,7 +3416,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>312</v>
+        <v>184</v>
       </c>
       <c r="C27">
         <v>2122342342</v>
@@ -3571,10 +3427,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>298</v>
+        <v>160</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3582,7 +3438,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>355</v>
+        <v>185</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3597,9 +3453,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785359D0-8BDB-4028-AD4B-2C0A4BB56435}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3608,10 +3464,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3619,10 +3475,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>348</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3630,10 +3486,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>322</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3641,7 +3497,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>349</v>
+        <v>187</v>
       </c>
       <c r="C4" s="11">
         <v>50</v>
@@ -3659,7 +3515,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B546E08-B445-4CFC-AE7C-A360990A58B3}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
@@ -3670,10 +3526,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3681,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>64789390</v>
@@ -3692,7 +3548,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>332</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3703,7 +3559,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>333</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3714,7 +3570,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>334</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3728,10 +3584,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08315C1-DA1D-48F4-A0A8-4BB13DC3E452}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="125.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="125.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3739,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3750,10 +3606,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>299</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3761,10 +3617,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>300</v>
+        <v>192</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3775,7 +3631,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3783,10 +3639,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>301</v>
+        <v>193</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3794,7 +3650,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>302</v>
+        <v>164</v>
       </c>
       <c r="C6" s="3">
         <v>25</v>
@@ -3805,10 +3661,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>303</v>
+        <v>194</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3816,7 +3672,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="C8" s="13">
         <v>9999.99</v>
@@ -3827,10 +3683,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>305</v>
+        <v>196</v>
       </c>
       <c r="C9" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3842,10 +3698,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048DF57C-BB9A-45F0-8668-498DC1298DA0}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3853,10 +3709,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3864,7 +3720,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -3875,7 +3731,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>306</v>
+        <v>197</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3886,7 +3742,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>198</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3897,7 +3753,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>308</v>
+        <v>199</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3908,7 +3764,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>309</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -3919,10 +3775,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>313</v>
+        <v>201</v>
       </c>
       <c r="C7" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3930,7 +3786,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>310</v>
+        <v>202</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -3941,7 +3797,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>273</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -3952,7 +3808,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>311</v>
+        <v>203</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -3963,7 +3819,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -3974,10 +3830,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>282</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3985,7 +3841,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>314</v>
+        <v>204</v>
       </c>
       <c r="C13">
         <v>85</v>
@@ -3996,7 +3852,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>284</v>
+        <v>146</v>
       </c>
       <c r="C14">
         <v>85</v>
@@ -4007,7 +3863,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>285</v>
+        <v>147</v>
       </c>
       <c r="C15">
         <v>9999.99</v>
@@ -4018,7 +3874,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>286</v>
+        <v>148</v>
       </c>
       <c r="C16">
         <v>9999.99</v>
@@ -4029,10 +3885,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>288</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4040,10 +3896,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>289</v>
+        <v>151</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4051,10 +3907,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>290</v>
+        <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4062,7 +3918,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>291</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -4073,7 +3929,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>292</v>
+        <v>154</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -4084,10 +3940,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>293</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4095,7 +3951,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>294</v>
+        <v>156</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -4106,10 +3962,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>295</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4117,7 +3973,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>312</v>
+        <v>184</v>
       </c>
       <c r="C25">
         <v>9867589302</v>
@@ -4128,10 +3984,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>297</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4139,10 +3995,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>298</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -4154,10 +4010,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8693D5-27C5-4228-92A0-224F98BEF54A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4165,10 +4021,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4176,7 +4032,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -4187,7 +4043,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>306</v>
+        <v>197</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -4198,7 +4054,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>198</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4209,7 +4065,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>308</v>
+        <v>199</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4220,7 +4076,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>309</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -4231,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>310</v>
+        <v>202</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -4242,7 +4098,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>137</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -4253,7 +4109,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>311</v>
+        <v>203</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -4264,7 +4120,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -4275,10 +4131,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>288</v>
+        <v>150</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4286,10 +4142,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>289</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4297,10 +4153,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>290</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4308,7 +4164,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>291</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4319,7 +4175,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>292</v>
+        <v>154</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4330,10 +4186,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>293</v>
+        <v>155</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4341,7 +4197,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>294</v>
+        <v>156</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -4352,10 +4208,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>295</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4363,7 +4219,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>312</v>
+        <v>184</v>
       </c>
       <c r="C19">
         <v>9867589302</v>
@@ -4374,10 +4230,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>297</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4385,10 +4241,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>298</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -4400,10 +4256,10 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702E2C7F-ACEF-451E-A257-8D7A1D64246B}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4411,10 +4267,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4422,10 +4278,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4433,7 +4289,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>205</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4444,10 +4300,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>322</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4455,7 +4311,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>167</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4466,10 +4322,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>324</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4477,10 +4333,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>325</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4488,10 +4344,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>326</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4499,10 +4355,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>327</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4510,10 +4366,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>328</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4521,10 +4377,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>329</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4532,10 +4388,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>330</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4543,7 +4399,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>331</v>
+        <v>206</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4554,7 +4410,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>332</v>
+        <v>188</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4565,7 +4421,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>333</v>
+        <v>189</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4576,7 +4432,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>334</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -4587,7 +4443,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>335</v>
+        <v>207</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
@@ -4598,10 +4454,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>319</v>
+        <v>208</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4609,10 +4465,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>336</v>
+        <v>177</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4620,10 +4476,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>337</v>
+        <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4631,10 +4487,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>338</v>
+        <v>179</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4642,10 +4498,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>339</v>
+        <v>180</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4653,10 +4509,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>340</v>
+        <v>181</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4664,10 +4520,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>341</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4675,10 +4531,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>342</v>
+        <v>183</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4686,7 +4542,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>312</v>
+        <v>184</v>
       </c>
       <c r="C26">
         <v>2122342342</v>
@@ -4697,10 +4553,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>298</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4708,7 +4564,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>343</v>
+        <v>209</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4719,10 +4575,10 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>344</v>
+        <v>210</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -4734,10 +4590,10 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18586F6-6D9E-4DD3-97F2-036CA4FFCAFA}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4745,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4756,10 +4612,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4767,7 +4623,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>205</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4778,10 +4634,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>322</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4789,7 +4645,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>167</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4800,10 +4656,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>324</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4811,10 +4667,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>325</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4822,10 +4678,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>326</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4833,10 +4689,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>327</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4844,10 +4700,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>328</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4855,10 +4711,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>329</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4866,10 +4722,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>330</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4877,7 +4733,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>331</v>
+        <v>206</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4888,7 +4744,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>335</v>
+        <v>207</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
@@ -4899,10 +4755,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>319</v>
+        <v>208</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4910,10 +4766,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>336</v>
+        <v>177</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4921,10 +4777,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>337</v>
+        <v>178</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4932,10 +4788,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>338</v>
+        <v>179</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4943,10 +4799,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>339</v>
+        <v>180</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4954,10 +4810,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>340</v>
+        <v>181</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4965,10 +4821,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>341</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4976,10 +4832,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>342</v>
+        <v>183</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4987,7 +4843,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>312</v>
+        <v>184</v>
       </c>
       <c r="C23">
         <v>2122342342</v>
@@ -4998,10 +4854,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>298</v>
+        <v>160</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5009,7 +4865,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>343</v>
+        <v>209</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -5020,10 +4876,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>344</v>
+        <v>210</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -5034,11 +4890,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5093,10 +4949,10 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5115,10 +4971,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5126,7 +4982,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -5137,10 +4993,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5148,7 +5004,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5159,10 +5015,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5170,10 +5026,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5181,10 +5037,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5192,10 +5048,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5203,10 +5059,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5214,10 +5070,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5225,10 +5081,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5236,7 +5092,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -5247,7 +5103,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>188</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -5258,7 +5114,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -5269,7 +5125,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -5280,10 +5136,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5291,10 +5147,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5302,10 +5158,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5313,10 +5169,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5324,10 +5180,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5335,10 +5191,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>181</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5346,10 +5202,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5357,10 +5213,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5368,7 +5224,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="C25">
         <v>2122342342</v>
@@ -5379,10 +5235,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5390,7 +5246,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5401,10 +5257,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -5415,9 +5271,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5426,10 +5282,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5437,7 +5293,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>315</v>
+        <v>211</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -5448,10 +5304,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>316</v>
+        <v>212</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>150</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5459,10 +5315,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>317</v>
+        <v>213</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>151</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5470,7 +5326,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>318</v>
+        <v>214</v>
       </c>
       <c r="C5">
         <v>1111</v>
@@ -5481,10 +5337,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>319</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -5495,10 +5351,10 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5DAE-E2BF-47B3-A1C9-7C4F12E126E5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5506,10 +5362,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5517,10 +5373,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>345</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5531,7 +5387,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5539,7 +5395,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>346</v>
+        <v>216</v>
       </c>
       <c r="C4">
         <v>76578</v>
@@ -5550,7 +5406,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>347</v>
+        <v>217</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -5561,7 +5417,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -5575,10 +5431,10 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF0C752-B8E1-4378-AC7E-8304285A9B90}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5597,10 +5453,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5608,7 +5464,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>152</v>
+        <v>218</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5619,10 +5475,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>153</v>
+        <v>219</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5630,7 +5486,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5641,10 +5497,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5652,10 +5508,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5663,10 +5519,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5674,10 +5530,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>98</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5685,10 +5541,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5696,10 +5552,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5707,10 +5563,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5718,10 +5574,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5729,10 +5585,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5740,10 +5596,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5751,10 +5607,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5762,10 +5618,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>115</v>
+        <v>181</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5773,10 +5629,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5784,7 +5640,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -5795,7 +5651,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>154</v>
+        <v>220</v>
       </c>
       <c r="C20">
         <v>150</v>
@@ -5806,7 +5662,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>155</v>
+        <v>221</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
@@ -5817,7 +5673,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>156</v>
+        <v>222</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
@@ -5828,7 +5684,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -5839,10 +5695,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>158</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5850,7 +5706,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -5861,10 +5717,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5872,10 +5728,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5883,10 +5739,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>161</v>
+        <v>226</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5894,10 +5750,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>162</v>
+        <v>227</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5905,10 +5761,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>163</v>
+        <v>228</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5916,10 +5772,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5927,10 +5783,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5938,7 +5794,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="C33" s="15">
         <v>2122342342</v>
@@ -5949,10 +5805,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5960,7 +5816,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5971,7 +5827,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -5984,14 +5840,14 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E20211-1D84-48FF-8A84-AC0AE11DA487}">
-  <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6002,169 +5858,170 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>100</v>
+      </c>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>152</v>
+        <v>218</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>153</v>
+        <v>219</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6172,10 +6029,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>115</v>
+        <v>181</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6183,10 +6040,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6194,7 +6051,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -6205,10 +6062,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6216,10 +6073,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6227,10 +6084,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>161</v>
+        <v>226</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6238,10 +6095,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>162</v>
+        <v>227</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6249,10 +6106,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>163</v>
+        <v>228</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6260,10 +6117,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6271,10 +6128,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6282,7 +6139,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="C27" s="15">
         <v>2122342342</v>
@@ -6293,10 +6150,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6304,7 +6161,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6318,10 +6175,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDEAA85-D896-403F-9A59-1E6EC90F5CC2}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6340,7 +6197,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6351,7 +6208,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -6362,7 +6219,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -6373,10 +6230,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>168</v>
+        <v>233</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>169</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6384,10 +6241,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6395,7 +6252,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C7">
         <v>123</v>
@@ -6406,10 +6263,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6417,10 +6274,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6428,10 +6285,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6439,10 +6296,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>98</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6450,10 +6307,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6461,10 +6318,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6472,10 +6329,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6483,7 +6340,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="C15">
         <v>1234</v>
@@ -6494,7 +6351,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="C16">
         <v>48</v>
@@ -6505,7 +6362,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="C17">
         <v>35</v>
@@ -6516,7 +6373,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -6527,10 +6384,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>177</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6538,7 +6395,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -6549,7 +6406,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6560,10 +6417,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6571,7 +6428,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -6582,7 +6439,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="C24">
         <v>789</v>
@@ -6593,7 +6450,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -6604,7 +6461,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="C26">
         <v>456</v>
@@ -6615,7 +6472,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -6626,10 +6483,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>186</v>
+        <v>247</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>187</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6637,7 +6494,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="C29" t="s">
         <v>51</v>
@@ -6648,7 +6505,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="C30" t="s">
         <v>51</v>
@@ -6659,7 +6516,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="C31" t="s">
         <v>51</v>
@@ -6670,7 +6527,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -6681,10 +6538,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6692,7 +6549,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>192</v>
+        <v>252</v>
       </c>
       <c r="C34" t="s">
         <v>45</v>
@@ -6703,10 +6560,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6714,10 +6571,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6725,7 +6582,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>196</v>
+        <v>255</v>
       </c>
       <c r="C37">
         <v>10000</v>
@@ -6736,7 +6593,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>197</v>
+        <v>256</v>
       </c>
       <c r="C38">
         <v>8000</v>
@@ -6747,7 +6604,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="C39">
         <v>6000</v>
@@ -6758,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>199</v>
+        <v>258</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -6769,7 +6626,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="C41">
         <v>300</v>
@@ -6780,7 +6637,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -6791,10 +6648,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -6805,10 +6662,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3C73BB-4FB2-4E8F-8651-A6AF93AAD260}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6827,7 +6684,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6838,7 +6695,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -6849,10 +6706,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6860,10 +6717,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6871,10 +6728,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6882,10 +6739,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>98</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6893,10 +6750,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6904,10 +6761,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6915,7 +6772,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C10" s="12">
         <v>1234</v>
@@ -6926,7 +6783,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="C11">
         <v>-8</v>
@@ -6937,7 +6794,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="C12">
         <v>-300</v>
@@ -6948,7 +6805,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="C13">
         <v>-200</v>
@@ -6959,7 +6816,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>203</v>
+        <v>261</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -6970,7 +6827,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="C15">
         <v>-818</v>
@@ -6981,7 +6838,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="C16">
         <v>-8</v>
@@ -6992,7 +6849,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="C17">
         <v>-767</v>
@@ -7003,7 +6860,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -7014,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>186</v>
+        <v>247</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>45</v>
@@ -7025,7 +6882,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -7036,7 +6893,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -7047,7 +6904,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>192</v>
+        <v>252</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -7058,10 +6915,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7069,7 +6926,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>196</v>
+        <v>255</v>
       </c>
       <c r="C24">
         <v>-1000</v>
@@ -7080,7 +6937,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>197</v>
+        <v>256</v>
       </c>
       <c r="C25">
         <v>-700</v>
@@ -7091,7 +6948,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="C26">
         <v>-500</v>
@@ -7102,7 +6959,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>199</v>
+        <v>258</v>
       </c>
       <c r="C27">
         <v>-300</v>
@@ -7113,7 +6970,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>204</v>
+        <v>262</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -7124,7 +6981,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="C29">
         <v>-150</v>
@@ -7135,7 +6992,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -7146,7 +7003,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>202</v>
+        <v>263</v>
       </c>
       <c r="C31">
         <v>-40</v>
@@ -7160,10 +7017,10 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7695C766-C8BF-4FC6-94BA-EF5703D41976}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7182,7 +7039,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7193,10 +7050,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7204,7 +7061,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7215,10 +7072,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7226,10 +7083,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7237,10 +7094,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7248,10 +7105,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>98</v>
+        <v>171</v>
+      </c>
+      <c r="C8" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7259,10 +7116,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7270,10 +7127,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7281,10 +7138,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7292,7 +7149,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -7303,7 +7160,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -7314,7 +7171,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -7325,10 +7182,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>205</v>
+        <v>264</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7336,7 +7193,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -7347,7 +7204,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -7358,7 +7215,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -7369,10 +7226,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>177</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7380,7 +7237,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -7391,7 +7248,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -7402,10 +7259,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7413,7 +7270,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="C23">
         <v>789</v>
@@ -7424,7 +7281,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="C24">
         <v>86</v>
@@ -7435,7 +7292,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="C25">
         <v>456</v>
@@ -7446,7 +7303,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="C26">
         <v>74</v>
@@ -7457,7 +7314,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
@@ -7468,7 +7325,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -7479,10 +7336,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>206</v>
+        <v>267</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7490,7 +7347,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -7501,10 +7358,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7512,7 +7369,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -7523,7 +7380,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -7534,7 +7391,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>138</v>
+        <v>203</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -7545,7 +7402,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -7556,7 +7413,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>207</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -7567,7 +7424,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>208</v>
+        <v>269</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -7578,7 +7435,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7589,7 +7446,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -7600,7 +7457,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -7611,10 +7468,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="C41" t="s">
-        <v>213</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7622,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>214</v>
+        <v>274</v>
       </c>
       <c r="C42">
         <v>400</v>
@@ -7633,7 +7490,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7644,7 +7501,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>216</v>
+        <v>276</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -7655,10 +7512,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -7670,10 +7527,10 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89650214-A8DD-44FC-9DFA-301D63E80C53}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7692,7 +7549,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7703,7 +7560,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -7714,10 +7571,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7725,10 +7582,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7736,10 +7593,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7747,10 +7604,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>98</v>
+        <v>171</v>
+      </c>
+      <c r="C7" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7758,10 +7615,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7769,10 +7626,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7780,10 +7637,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -7794,10 +7651,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE9724B-3165-4EC7-A43C-010FD17B4AF6}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7816,7 +7673,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7827,10 +7684,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7838,7 +7695,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7849,10 +7706,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7860,10 +7717,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7871,10 +7728,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7882,10 +7739,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>98</v>
+        <v>171</v>
+      </c>
+      <c r="C8" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7893,10 +7750,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7904,10 +7761,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7915,7 +7772,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C11" s="12">
         <v>1234</v>
@@ -7926,7 +7783,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>203</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -7937,7 +7794,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="C13">
         <v>-466</v>
@@ -7948,7 +7805,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="C14">
         <v>-500</v>
@@ -7959,7 +7816,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="C15">
         <v>-400</v>
@@ -7970,7 +7827,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="C16">
         <v>-789</v>
@@ -7981,7 +7838,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="C17">
         <v>-200</v>
@@ -7992,7 +7849,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="C18">
         <v>-456</v>
@@ -8003,7 +7860,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="C19">
         <v>-74</v>
@@ -8014,7 +7871,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
@@ -8025,7 +7882,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -8036,7 +7893,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>208</v>
+        <v>269</v>
       </c>
       <c r="C22">
         <v>-400</v>
@@ -8047,7 +7904,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>228</v>
+        <v>277</v>
       </c>
       <c r="C23">
         <v>-200</v>
@@ -8058,7 +7915,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="C24">
         <v>-100</v>
@@ -8069,7 +7926,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="C25">
         <v>-200</v>
@@ -8080,7 +7937,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="C26">
         <v>-50</v>
@@ -8091,7 +7948,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>214</v>
+        <v>274</v>
       </c>
       <c r="C27">
         <v>-400</v>
@@ -8102,7 +7959,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>229</v>
+        <v>278</v>
       </c>
       <c r="C28">
         <v>-200</v>
@@ -8113,7 +7970,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="C29">
         <v>-100</v>
@@ -8124,7 +7981,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>216</v>
+        <v>276</v>
       </c>
       <c r="C30">
         <v>-200</v>
@@ -8135,7 +7992,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -8150,11 +8007,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8209,10 +8066,10 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8231,7 +8088,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8242,10 +8099,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>219</v>
+        <v>280</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8253,7 +8110,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -8264,10 +8121,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8275,10 +8132,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8286,10 +8143,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8297,10 +8154,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>98</v>
+        <v>171</v>
+      </c>
+      <c r="C8" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8308,10 +8165,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8319,10 +8176,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8330,10 +8187,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8341,7 +8198,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -8352,7 +8209,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -8363,7 +8220,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -8374,7 +8231,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="C15">
         <v>500</v>
@@ -8385,10 +8242,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8396,7 +8253,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="C17">
         <v>1000</v>
@@ -8407,7 +8264,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="C18">
         <v>700</v>
@@ -8418,10 +8275,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8429,10 +8286,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>221</v>
+        <v>281</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>222</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8440,7 +8297,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>223</v>
+        <v>282</v>
       </c>
       <c r="C21">
         <v>1234</v>
@@ -8451,10 +8308,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8462,10 +8319,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>225</v>
+        <v>284</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8473,10 +8330,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8484,7 +8341,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="C25">
         <v>300</v>
@@ -8495,7 +8352,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="C26">
         <v>85</v>
@@ -8506,7 +8363,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -8517,7 +8374,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="C28">
         <v>76</v>
@@ -8528,7 +8385,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>192</v>
+        <v>252</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>45</v>
@@ -8539,7 +8396,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>45</v>
@@ -8550,10 +8407,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>206</v>
+        <v>267</v>
       </c>
       <c r="C31" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8561,7 +8418,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>45</v>
@@ -8572,10 +8429,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8583,7 +8440,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>226</v>
+        <v>285</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>26</v>
@@ -8594,7 +8451,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>26</v>
@@ -8605,7 +8462,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>26</v>
@@ -8619,10 +8476,10 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87CE4365-F4A6-44A6-8070-7113DA611997}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8641,7 +8498,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8652,7 +8509,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -8663,10 +8520,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8674,10 +8531,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8685,10 +8542,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8696,10 +8553,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>98</v>
+        <v>171</v>
+      </c>
+      <c r="C7" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8707,10 +8564,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8718,10 +8575,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8729,10 +8586,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -8743,10 +8600,10 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8765,7 +8622,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="C2" s="3">
         <v>1234</v>
@@ -8776,7 +8633,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3">
         <v>123</v>
@@ -8787,10 +8644,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8798,10 +8655,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8809,10 +8666,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8820,10 +8677,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>98</v>
+        <v>171</v>
+      </c>
+      <c r="C7" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8831,10 +8688,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8842,10 +8699,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8853,7 +8710,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C10" s="15">
         <v>12345</v>
@@ -8864,7 +8721,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="C11" s="3">
         <v>-500</v>
@@ -8875,7 +8732,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="C12" s="3">
         <v>-1000</v>
@@ -8886,7 +8743,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="C13" s="3">
         <v>-700</v>
@@ -8897,7 +8754,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="C14" s="3">
         <v>-300</v>
@@ -8908,7 +8765,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="C15" s="3">
         <v>-85</v>
@@ -8919,7 +8776,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="C16" s="3">
         <v>-200</v>
@@ -8930,7 +8787,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="C17" s="3">
         <v>-76</v>
@@ -8941,7 +8798,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>45</v>
@@ -8952,7 +8809,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>45</v>
@@ -8963,10 +8820,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>225</v>
+        <v>284</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8974,10 +8831,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>226</v>
+        <v>285</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8985,10 +8842,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8996,10 +8853,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -9011,10 +8868,10 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B75E61-DAA5-4C75-9938-082F14D489D1}">
   <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="40.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.08984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9022,7 +8879,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>249</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9033,10 +8890,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>231</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9044,10 +8901,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>247</v>
+        <v>288</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9055,10 +8912,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>232</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9066,7 +8923,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="C5" s="3">
         <v>1234</v>
@@ -9077,7 +8934,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="C6" s="3">
         <v>8967589</v>
@@ -9088,7 +8945,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="C7" s="3">
         <v>34567</v>
@@ -9099,7 +8956,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="C8" s="3">
         <v>50</v>
@@ -9110,7 +8967,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="C9" s="3">
         <v>100</v>
@@ -9121,10 +8978,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9132,7 +8989,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
@@ -9143,10 +9000,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9154,10 +9011,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9165,10 +9022,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9176,10 +9033,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>98</v>
+        <v>171</v>
+      </c>
+      <c r="C15" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9187,10 +9044,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9198,10 +9055,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9209,10 +9066,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>251</v>
+        <v>291</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>234</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9220,7 +9077,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>252</v>
+        <v>292</v>
       </c>
       <c r="C19" s="3">
         <v>123</v>
@@ -9231,10 +9088,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>253</v>
+        <v>293</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>235</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9242,10 +9099,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9253,10 +9110,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9264,10 +9121,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>98</v>
+        <v>296</v>
+      </c>
+      <c r="C23" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9275,10 +9132,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9286,10 +9143,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9297,10 +9154,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>236</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9308,10 +9165,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9319,10 +9176,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>261</v>
+        <v>301</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>238</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9330,7 +9187,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="C29" s="3">
         <v>75</v>
@@ -9341,7 +9198,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
@@ -9352,7 +9209,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="C31" s="3">
         <v>85</v>
@@ -9363,7 +9220,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>265</v>
+        <v>305</v>
       </c>
       <c r="C32" s="3">
         <v>55</v>
@@ -9374,7 +9231,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>5</v>
@@ -9385,10 +9242,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>239</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9396,7 +9253,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -9407,10 +9264,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9418,10 +9275,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9429,10 +9286,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9440,10 +9297,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>241</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9451,10 +9308,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>115</v>
+        <v>181</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9462,10 +9319,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9473,7 +9330,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="C42" s="3">
         <v>9869875890</v>
@@ -9484,10 +9341,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>266</v>
+        <v>306</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>242</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9495,7 +9352,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="C44" s="3">
         <v>20</v>
@@ -9506,10 +9363,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9517,10 +9374,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>243</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9528,10 +9385,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>161</v>
+        <v>226</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>244</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9539,10 +9396,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>162</v>
+        <v>227</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9550,10 +9407,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>245</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9561,7 +9418,7 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="C50" s="3">
         <v>9869875890</v>
@@ -9575,10 +9432,10 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F13134-7D58-41D3-85C8-A2B7688C4794}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9586,7 +9443,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>249</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9597,10 +9454,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>231</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9608,10 +9465,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>247</v>
+        <v>288</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9619,10 +9476,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>232</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9630,7 +9487,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="C5" s="3">
         <v>50</v>
@@ -9641,7 +9498,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="C6" s="3">
         <v>100</v>
@@ -9652,10 +9509,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9663,7 +9520,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C8" s="3">
         <v>123</v>
@@ -9674,10 +9531,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9685,10 +9542,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9696,10 +9553,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9707,10 +9564,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>171</v>
+      </c>
+      <c r="C12" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9718,10 +9575,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9729,7 +9586,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C14" s="3">
         <v>12345</v>
@@ -9740,10 +9597,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>251</v>
+        <v>291</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>234</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9751,7 +9608,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>252</v>
+        <v>292</v>
       </c>
       <c r="C16" s="3">
         <v>123</v>
@@ -9762,10 +9619,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>253</v>
+        <v>293</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>235</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9773,10 +9630,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9784,10 +9641,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9795,10 +9652,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>256</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>98</v>
+        <v>296</v>
+      </c>
+      <c r="C20" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9806,10 +9663,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9817,7 +9674,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="C22" s="3">
         <v>12345</v>
@@ -9828,10 +9685,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>236</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9839,10 +9696,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9850,10 +9707,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>261</v>
+        <v>301</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>238</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9861,7 +9718,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="C26" s="3">
         <v>-75</v>
@@ -9872,7 +9729,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="C27" s="3">
         <v>-65</v>
@@ -9883,7 +9740,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="C28" s="3">
         <v>-85</v>
@@ -9894,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>305</v>
       </c>
       <c r="C29" s="3">
         <v>-55</v>
@@ -9905,10 +9762,10 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>239</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9916,7 +9773,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -9927,10 +9784,10 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>266</v>
+        <v>306</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>242</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9938,7 +9795,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="C33" s="3">
         <v>20</v>
@@ -9952,11 +9809,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10011,9 +9868,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10069,7 +9926,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -10102,7 +9959,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>30</v>
@@ -10130,23 +9987,23 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" ht="16">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" ht="16">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>29</v>
@@ -10161,7 +10018,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -10204,7 +10061,7 @@
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
@@ -10222,23 +10079,23 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" ht="16">
       <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>269</v>
+      <c r="B6" t="s">
+        <v>132</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" ht="16">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>270</v>
+      <c r="B7" t="s">
+        <v>133</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>41</v>
@@ -10252,7 +10109,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -10307,7 +10164,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>37</v>
@@ -10318,7 +10175,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>38</v>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CC172E-E146-406E-9D54-BE05044B363E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BD7993-91EA-4148-B4F9-C14AE5DAF447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="7" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="6" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -33,30 +33,31 @@
     <sheet name="GrantCreate1" sheetId="17" r:id="rId18"/>
     <sheet name="SF428C_Form" sheetId="18" r:id="rId19"/>
     <sheet name="SF428C_half_fill" sheetId="47" r:id="rId20"/>
-    <sheet name="SF428C_Wrong_Data" sheetId="23" r:id="rId21"/>
-    <sheet name="SF425_Form" sheetId="19" r:id="rId22"/>
-    <sheet name="SF425A_Form" sheetId="20" r:id="rId23"/>
-    <sheet name="SF428S_Form" sheetId="21" r:id="rId24"/>
-    <sheet name="SF428S_Details_Individual" sheetId="22" r:id="rId25"/>
-    <sheet name="SF428B_Form" sheetId="24" r:id="rId26"/>
-    <sheet name="SF428B_2c_deselect" sheetId="26" r:id="rId27"/>
-    <sheet name="SF428_Form" sheetId="27" r:id="rId28"/>
-    <sheet name="SF428_field_not_filled" sheetId="28" r:id="rId29"/>
-    <sheet name="SF428_Supp_not_Selected" sheetId="34" r:id="rId30"/>
-    <sheet name="SF428A_Form" sheetId="31" r:id="rId31"/>
-    <sheet name="SF428A_Federal_Property" sheetId="33" r:id="rId32"/>
-    <sheet name="SF429_Form" sheetId="35" r:id="rId33"/>
-    <sheet name="SF429_half_fill" sheetId="51" r:id="rId34"/>
-    <sheet name="SF429A_Form" sheetId="37" r:id="rId35"/>
-    <sheet name="SF429A_Form_incorrect_data" sheetId="38" r:id="rId36"/>
-    <sheet name="SF429B_Form" sheetId="41" r:id="rId37"/>
-    <sheet name="SF429B_half_fill" sheetId="49" r:id="rId38"/>
-    <sheet name="SF429B_Form_incorrect_data" sheetId="40" r:id="rId39"/>
-    <sheet name="SF429C_Form" sheetId="42" r:id="rId40"/>
-    <sheet name="SF429C_half_fill" sheetId="50" r:id="rId41"/>
-    <sheet name="SF429C_Form_incorrect_data" sheetId="43" r:id="rId42"/>
-    <sheet name="SF271_Form" sheetId="46" r:id="rId43"/>
-    <sheet name="SF271_incorrect_data" sheetId="45" r:id="rId44"/>
+    <sheet name="Sheet1" sheetId="53" r:id="rId21"/>
+    <sheet name="SF428C_Wrong_Data" sheetId="23" r:id="rId22"/>
+    <sheet name="SF425_Form" sheetId="19" r:id="rId23"/>
+    <sheet name="SF425A_Form" sheetId="20" r:id="rId24"/>
+    <sheet name="SF428S_Form" sheetId="21" r:id="rId25"/>
+    <sheet name="SF428S_Details_Individual" sheetId="22" r:id="rId26"/>
+    <sheet name="SF428B_Form" sheetId="24" r:id="rId27"/>
+    <sheet name="SF428B_2c_deselect" sheetId="26" r:id="rId28"/>
+    <sheet name="SF428_Form" sheetId="27" r:id="rId29"/>
+    <sheet name="SF428_field_not_filled" sheetId="28" r:id="rId30"/>
+    <sheet name="SF428_Supp_not_Selected" sheetId="34" r:id="rId31"/>
+    <sheet name="SF428A_Form" sheetId="31" r:id="rId32"/>
+    <sheet name="SF428A_Federal_Property" sheetId="33" r:id="rId33"/>
+    <sheet name="SF429_Form" sheetId="35" r:id="rId34"/>
+    <sheet name="SF429_half_fill" sheetId="51" r:id="rId35"/>
+    <sheet name="SF429A_Form" sheetId="37" r:id="rId36"/>
+    <sheet name="SF429A_Form_incorrect_data" sheetId="38" r:id="rId37"/>
+    <sheet name="SF429B_Form" sheetId="41" r:id="rId38"/>
+    <sheet name="SF429B_half_fill" sheetId="49" r:id="rId39"/>
+    <sheet name="SF429B_Form_incorrect_data" sheetId="40" r:id="rId40"/>
+    <sheet name="SF429C_Form" sheetId="42" r:id="rId41"/>
+    <sheet name="SF429C_half_fill" sheetId="50" r:id="rId42"/>
+    <sheet name="SF429C_Form_incorrect_data" sheetId="43" r:id="rId43"/>
+    <sheet name="SF271_Form" sheetId="46" r:id="rId44"/>
+    <sheet name="SF271_incorrect_data" sheetId="45" r:id="rId45"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="306">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -165,12 +166,6 @@
     <t>Calendar</t>
   </si>
   <si>
-    <t>08/25/2023</t>
-  </si>
-  <si>
-    <t>08/25/2024</t>
-  </si>
-  <si>
     <t>Quarterly</t>
   </si>
   <si>
@@ -279,9 +274,6 @@
     <t>Construction</t>
   </si>
   <si>
-    <t>fieldInternalOrganization__c</t>
-  </si>
-  <si>
     <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
   </si>
   <si>
@@ -303,21 +295,6 @@
     <t>Automation award for PR</t>
   </si>
   <si>
-    <t>fieldFrequency__c</t>
-  </si>
-  <si>
-    <t>fieldGoverningOrganizationReportDate__c</t>
-  </si>
-  <si>
-    <t>fieldBoardInformation__c</t>
-  </si>
-  <si>
-    <t>fieldCalReportingStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldCalReportingEndDate__c</t>
-  </si>
-  <si>
     <t>fieldFederalGrantIdentifyingNumbe__c</t>
   </si>
   <si>
@@ -1018,6 +995,9 @@
   </si>
   <si>
     <t>CalReportingEndDate__c</t>
+  </si>
+  <si>
+    <t>InternalOrganization__c</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1535,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1585,10 +1565,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>303</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1596,10 +1576,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1626,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1676,10 +1656,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>303</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1687,10 +1667,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1786,7 +1766,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1797,7 +1777,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -1866,7 +1846,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>75</v>
+        <v>301</v>
       </c>
       <c r="C5" s="3">
         <v>-2</v>
@@ -1877,7 +1857,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>76</v>
+        <v>302</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>20</v>
@@ -1935,7 +1915,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>75</v>
+        <v>301</v>
       </c>
       <c r="C4" s="3">
         <v>-2</v>
@@ -1946,7 +1926,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>76</v>
+        <v>302</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>20</v>
@@ -1982,10 +1962,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1993,10 +1973,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2004,7 +1984,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2015,7 +1995,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2026,10 +2006,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2037,10 +2017,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>66</v>
+        <v>305</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2048,10 +2028,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2059,10 +2039,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2095,10 +2075,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2106,7 +2086,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2117,13 +2097,13 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2131,10 +2111,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2142,10 +2122,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2153,10 +2133,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2164,10 +2144,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2175,10 +2155,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2186,10 +2166,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2197,10 +2177,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2208,10 +2188,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -2219,10 +2199,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2255,10 +2235,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2266,10 +2246,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2277,7 +2257,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2288,7 +2268,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2299,10 +2279,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2310,10 +2290,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>66</v>
+        <v>305</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2321,10 +2301,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2332,10 +2312,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2368,10 +2348,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2379,10 +2359,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2390,7 +2370,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2401,7 +2381,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2412,10 +2392,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2423,10 +2403,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>66</v>
+        <v>305</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2434,10 +2414,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2445,10 +2425,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2481,7 +2461,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2492,7 +2472,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2503,7 +2483,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2514,7 +2494,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2525,7 +2505,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2536,7 +2516,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2547,7 +2527,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2558,7 +2538,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2569,7 +2549,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2580,10 +2560,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2591,7 +2571,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C12" s="10">
         <v>9999.99</v>
@@ -2602,7 +2582,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -2613,7 +2593,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C14" s="10">
         <v>9999.99</v>
@@ -2624,7 +2604,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C15" s="10">
         <v>1000</v>
@@ -2635,7 +2615,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>5</v>
@@ -2646,10 +2626,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2657,10 +2637,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2668,10 +2648,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2679,7 +2659,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>5</v>
@@ -2690,7 +2670,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>5</v>
@@ -2701,10 +2681,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2712,7 +2692,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2723,10 +2703,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2734,7 +2714,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C25">
         <v>8967045891</v>
@@ -2745,10 +2725,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2756,10 +2736,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2805,7 +2785,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -2875,7 +2855,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2887,6 +2867,15 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DCBC90C-98C6-4765-8620-3F07BF1C42BC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2911,7 +2900,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2922,7 +2911,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2933,7 +2922,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2944,7 +2933,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2955,7 +2944,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2966,7 +2955,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2977,7 +2966,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2988,7 +2977,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2999,7 +2988,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -3010,7 +2999,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>5</v>
@@ -3021,10 +3010,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3032,10 +3021,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3043,7 +3032,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -3054,7 +3043,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -3065,10 +3054,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3076,7 +3065,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3087,10 +3076,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3098,7 +3087,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C19">
         <v>8967045891</v>
@@ -3109,10 +3098,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3120,10 +3109,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3131,7 +3120,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3156,10 +3145,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3167,10 +3156,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3178,10 +3167,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3189,10 +3178,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3200,7 +3189,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -3211,7 +3200,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -3222,7 +3211,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3233,10 +3222,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3244,7 +3233,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3255,10 +3244,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3266,10 +3255,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3277,10 +3266,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3288,10 +3277,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3299,10 +3288,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3310,10 +3299,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3321,10 +3310,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3332,10 +3321,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3343,7 +3332,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3354,10 +3343,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3365,10 +3354,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3376,10 +3365,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3387,10 +3376,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3398,10 +3387,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3409,10 +3398,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3420,10 +3409,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3431,7 +3420,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C27">
         <v>2122342342</v>
@@ -3442,10 +3431,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3453,7 +3442,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3465,7 +3454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785359D0-8BDB-4028-AD4B-2C0A4BB56435}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3490,10 +3479,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3501,10 +3490,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3512,7 +3501,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C4" s="11">
         <v>50</v>
@@ -3527,7 +3516,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B546E08-B445-4CFC-AE7C-A360990A58B3}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3552,7 +3541,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>64789390</v>
@@ -3563,7 +3552,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3574,7 +3563,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3585,7 +3574,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3596,7 +3585,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08315C1-DA1D-48F4-A0A8-4BB13DC3E452}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3621,10 +3610,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" t="s">
         <v>155</v>
-      </c>
-      <c r="C2" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3632,10 +3621,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3643,10 +3632,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3654,10 +3643,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3665,7 +3654,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C6" s="3">
         <v>25</v>
@@ -3676,10 +3665,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3687,7 +3676,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C8" s="13">
         <v>9999.99</v>
@@ -3698,10 +3687,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -3710,7 +3699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048DF57C-BB9A-45F0-8668-498DC1298DA0}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3735,7 +3724,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -3746,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3757,7 +3746,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3768,7 +3757,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3779,7 +3768,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -3790,10 +3779,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3801,7 +3790,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -3812,7 +3801,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -3823,7 +3812,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -3834,7 +3823,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -3845,10 +3834,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3856,7 +3845,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C13">
         <v>85</v>
@@ -3867,7 +3856,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C14">
         <v>85</v>
@@ -3878,7 +3867,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C15">
         <v>9999.99</v>
@@ -3889,7 +3878,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C16">
         <v>9999.99</v>
@@ -3900,10 +3889,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3911,10 +3900,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3922,10 +3911,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3933,7 +3922,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -3944,7 +3933,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -3955,10 +3944,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3966,7 +3955,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3977,10 +3966,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3988,7 +3977,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C25">
         <v>9867589302</v>
@@ -3999,10 +3988,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4010,10 +3999,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -4022,7 +4011,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8693D5-27C5-4228-92A0-224F98BEF54A}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4047,7 +4036,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -4058,7 +4047,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -4069,7 +4058,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4080,7 +4069,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4091,7 +4080,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -4102,7 +4091,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -4113,7 +4102,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -4124,7 +4113,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -4135,7 +4124,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -4146,10 +4135,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4157,10 +4146,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4168,10 +4157,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4179,7 +4168,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4190,7 +4179,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4201,10 +4190,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4212,7 +4201,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -4223,10 +4212,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4234,7 +4223,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C19">
         <v>9867589302</v>
@@ -4245,10 +4234,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4256,10 +4245,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -4268,7 +4257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702E2C7F-ACEF-451E-A257-8D7A1D64246B}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4293,10 +4282,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4304,7 +4293,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4315,10 +4304,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4326,7 +4315,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4337,10 +4326,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4348,10 +4337,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4359,10 +4348,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4370,10 +4359,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4381,10 +4370,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4392,10 +4381,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4403,10 +4392,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4414,7 +4403,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4425,7 +4414,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4436,7 +4425,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4447,7 +4436,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -4458,10 +4447,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4469,10 +4458,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4480,10 +4469,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4491,10 +4480,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C20" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4502,10 +4491,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4513,10 +4502,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4524,10 +4513,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4535,10 +4524,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4546,10 +4535,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4557,7 +4546,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C26">
         <v>2122342342</v>
@@ -4568,10 +4557,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4579,7 +4568,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4590,315 +4579,15 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18586F6-6D9E-4DD3-97F2-036CA4FFCAFA}">
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C3">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>181</v>
-      </c>
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>136</v>
-      </c>
-      <c r="C19" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>138</v>
-      </c>
-      <c r="C20" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>142</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23">
-        <v>2122342342</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>183</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s">
-        <v>184</v>
-      </c>
-      <c r="C26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -4962,6 +4651,306 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18586F6-6D9E-4DD3-97F2-036CA4FFCAFA}">
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4986,10 +4975,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4997,7 +4986,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -5008,10 +4997,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5019,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5030,10 +5019,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5041,10 +5030,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5052,10 +5041,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5063,10 +5052,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5074,10 +5063,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5085,10 +5074,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5096,10 +5085,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5107,7 +5096,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -5118,7 +5107,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -5129,7 +5118,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -5140,7 +5129,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -5151,10 +5140,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5162,10 +5151,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5173,10 +5162,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5184,10 +5173,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5195,10 +5184,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C21" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5206,10 +5195,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5217,10 +5206,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5228,10 +5217,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5239,7 +5228,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C25">
         <v>2122342342</v>
@@ -5250,10 +5239,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5261,7 +5250,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5272,10 +5261,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -5283,7 +5272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5308,7 +5297,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -5319,10 +5308,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5330,10 +5319,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5341,7 +5330,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C5">
         <v>1111</v>
@@ -5352,10 +5341,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -5363,7 +5352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5DAE-E2BF-47B3-A1C9-7C4F12E126E5}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5388,10 +5377,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5399,10 +5388,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5410,7 +5399,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C4">
         <v>76578</v>
@@ -5421,7 +5410,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -5432,7 +5421,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -5443,7 +5432,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF0C752-B8E1-4378-AC7E-8304285A9B90}">
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5468,10 +5457,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5479,7 +5468,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5490,10 +5479,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5501,7 +5490,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5512,10 +5501,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5523,10 +5512,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5534,10 +5523,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5545,10 +5534,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5556,10 +5545,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5567,10 +5556,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5578,10 +5567,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5589,10 +5578,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5600,10 +5589,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5611,10 +5600,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5622,10 +5611,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5633,10 +5622,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5644,10 +5633,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5655,7 +5644,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -5666,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C20">
         <v>150</v>
@@ -5677,7 +5666,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
@@ -5688,7 +5677,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
@@ -5699,7 +5688,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -5710,10 +5699,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5721,7 +5710,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -5732,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5743,10 +5732,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5754,10 +5743,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5765,10 +5754,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5776,10 +5765,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5787,10 +5776,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5798,10 +5787,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5809,7 +5798,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C33" s="15">
         <v>2122342342</v>
@@ -5820,10 +5809,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5831,7 +5820,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5842,7 +5831,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -5853,7 +5842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E20211-1D84-48FF-8A84-AC0AE11DA487}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5878,10 +5867,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5889,7 +5878,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5900,10 +5889,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5911,7 +5900,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5922,10 +5911,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5933,10 +5922,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5944,10 +5933,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5955,10 +5944,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5966,10 +5955,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5977,10 +5966,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5988,10 +5977,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5999,10 +5988,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6010,10 +5999,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6021,10 +6010,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6032,10 +6021,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6043,10 +6032,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6054,10 +6043,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6065,7 +6054,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -6076,10 +6065,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6087,10 +6076,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6098,10 +6087,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6109,10 +6098,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6120,10 +6109,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6131,10 +6120,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6142,10 +6131,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6153,7 +6142,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C27" s="15">
         <v>2122342342</v>
@@ -6164,10 +6153,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6175,7 +6164,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6186,7 +6175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDEAA85-D896-403F-9A59-1E6EC90F5CC2}">
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6211,7 +6200,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6222,7 +6211,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -6233,7 +6222,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -6244,10 +6233,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6255,10 +6244,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6266,7 +6255,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C7">
         <v>123</v>
@@ -6277,10 +6266,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6288,10 +6277,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6299,10 +6288,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6310,10 +6299,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6321,10 +6310,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6332,10 +6321,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6343,10 +6332,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6354,7 +6343,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C15">
         <v>1234</v>
@@ -6365,7 +6354,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C16">
         <v>48</v>
@@ -6376,7 +6365,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C17">
         <v>35</v>
@@ -6387,7 +6376,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -6398,10 +6387,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6409,7 +6398,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -6420,7 +6409,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6431,10 +6420,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6442,7 +6431,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -6453,7 +6442,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C24">
         <v>789</v>
@@ -6464,7 +6453,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -6475,7 +6464,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C26">
         <v>456</v>
@@ -6486,7 +6475,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -6497,10 +6486,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6508,10 +6497,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6519,10 +6508,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6530,10 +6519,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6541,10 +6530,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6552,10 +6541,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6563,10 +6552,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6574,10 +6563,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6585,10 +6574,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6596,7 +6585,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C37">
         <v>10000</v>
@@ -6607,7 +6596,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C38">
         <v>8000</v>
@@ -6618,7 +6607,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C39">
         <v>6000</v>
@@ -6629,7 +6618,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -6640,7 +6629,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C41">
         <v>300</v>
@@ -6651,7 +6640,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -6662,10 +6651,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -6673,7 +6662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3C73BB-4FB2-4E8F-8651-A6AF93AAD260}">
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6698,7 +6687,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6709,7 +6698,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -6720,10 +6709,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6731,10 +6720,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6742,10 +6731,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6753,10 +6742,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6764,10 +6753,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6775,10 +6764,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6786,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C10" s="12">
         <v>1234</v>
@@ -6797,7 +6786,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C11">
         <v>-8</v>
@@ -6808,7 +6797,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C12">
         <v>-300</v>
@@ -6819,7 +6808,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C13">
         <v>-200</v>
@@ -6830,7 +6819,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -6841,7 +6830,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C15">
         <v>-818</v>
@@ -6852,7 +6841,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C16">
         <v>-8</v>
@@ -6863,7 +6852,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C17">
         <v>-767</v>
@@ -6874,7 +6863,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -6885,10 +6874,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6896,10 +6885,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6907,10 +6896,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6918,10 +6907,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6929,10 +6918,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6940,7 +6929,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C24">
         <v>-1000</v>
@@ -6951,7 +6940,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C25">
         <v>-700</v>
@@ -6962,7 +6951,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C26">
         <v>-500</v>
@@ -6973,7 +6962,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C27">
         <v>-300</v>
@@ -6984,7 +6973,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -6995,7 +6984,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C29">
         <v>-150</v>
@@ -7006,7 +6995,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -7017,7 +7006,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C31">
         <v>-40</v>
@@ -7028,7 +7017,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7695C766-C8BF-4FC6-94BA-EF5703D41976}">
   <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7053,7 +7042,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7064,10 +7053,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7075,7 +7064,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7086,10 +7075,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7097,10 +7086,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7108,10 +7097,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7119,10 +7108,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7130,10 +7119,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7141,10 +7130,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7152,10 +7141,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7163,7 +7152,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -7174,7 +7163,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -7185,7 +7174,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -7196,10 +7185,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7207,7 +7196,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -7218,7 +7207,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -7229,7 +7218,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -7240,10 +7229,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7251,7 +7240,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -7262,7 +7251,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -7273,10 +7262,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7284,7 +7273,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C23">
         <v>789</v>
@@ -7295,7 +7284,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C24">
         <v>86</v>
@@ -7306,7 +7295,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C25">
         <v>456</v>
@@ -7317,7 +7306,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C26">
         <v>74</v>
@@ -7328,10 +7317,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -7339,10 +7328,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7350,10 +7339,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7361,10 +7350,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -7372,10 +7361,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7383,7 +7372,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -7394,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -7405,7 +7394,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -7416,7 +7405,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -7427,7 +7416,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -7438,7 +7427,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -7449,7 +7438,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7460,7 +7449,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -7471,7 +7460,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -7482,10 +7471,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C41" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7493,7 +7482,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C42">
         <v>400</v>
@@ -7504,7 +7493,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7515,7 +7504,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -7526,10 +7515,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -7538,7 +7527,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89650214-A8DD-44FC-9DFA-301D63E80C53}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7563,7 +7552,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7574,7 +7563,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -7585,10 +7574,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7596,10 +7585,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7607,10 +7596,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7618,10 +7607,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7629,10 +7618,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7640,10 +7629,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7651,370 +7640,14 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE9724B-3165-4EC7-A43C-010FD17B4AF6}">
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="C3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="12">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13">
-        <v>-466</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C15">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16">
-        <v>-789</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C17">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C18">
-        <v>-456</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C19">
-        <v>-74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="C20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="C21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="C22">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="C23">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="C24">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="C25">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="C26">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="C27">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="C28">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="C29">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C30">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="C31">
-        <v>-50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8078,6 +7711,362 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE9724B-3165-4EC7-A43C-010FD17B4AF6}">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13">
+        <v>-466</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C14">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C15">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16">
+        <v>-789</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C17">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C18">
+        <v>-456</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19">
+        <v>-74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C22">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C23">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C24">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C26">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C27">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C28">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C30">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="C31">
+        <v>-50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8102,7 +8091,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8113,10 +8102,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8124,7 +8113,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -8135,10 +8124,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8146,10 +8135,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8157,10 +8146,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8168,10 +8157,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8179,10 +8168,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8190,10 +8179,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8201,10 +8190,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8212,7 +8201,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -8223,7 +8212,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -8234,7 +8223,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -8245,7 +8234,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C15">
         <v>500</v>
@@ -8256,10 +8245,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8267,7 +8256,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C17">
         <v>1000</v>
@@ -8278,7 +8267,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C18">
         <v>700</v>
@@ -8289,10 +8278,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8300,10 +8289,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8311,7 +8300,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C21">
         <v>1234</v>
@@ -8322,10 +8311,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C22" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8333,10 +8322,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8344,10 +8333,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8355,7 +8344,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C25">
         <v>300</v>
@@ -8366,7 +8355,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C26">
         <v>85</v>
@@ -8377,7 +8366,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -8388,7 +8377,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C28">
         <v>76</v>
@@ -8399,10 +8388,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8410,10 +8399,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -8421,10 +8410,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C31" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8432,10 +8421,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8443,10 +8432,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8454,7 +8443,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>26</v>
@@ -8465,7 +8454,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>26</v>
@@ -8476,7 +8465,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>26</v>
@@ -8487,7 +8476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87CE4365-F4A6-44A6-8070-7113DA611997}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8512,7 +8501,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8523,7 +8512,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -8534,10 +8523,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8545,10 +8534,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8556,10 +8545,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8567,10 +8556,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8578,10 +8567,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8589,10 +8578,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8600,10 +8589,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -8611,7 +8600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8636,7 +8625,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C2" s="3">
         <v>1234</v>
@@ -8647,7 +8636,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C3" s="3">
         <v>123</v>
@@ -8658,10 +8647,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8669,10 +8658,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8680,10 +8669,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8691,10 +8680,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8702,10 +8691,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8713,10 +8702,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8724,7 +8713,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C10" s="15">
         <v>12345</v>
@@ -8735,7 +8724,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C11" s="3">
         <v>-500</v>
@@ -8746,7 +8735,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C12" s="3">
         <v>-1000</v>
@@ -8757,7 +8746,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C13" s="3">
         <v>-700</v>
@@ -8768,7 +8757,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C14" s="3">
         <v>-300</v>
@@ -8779,7 +8768,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C15" s="3">
         <v>-85</v>
@@ -8790,7 +8779,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C16" s="3">
         <v>-200</v>
@@ -8801,7 +8790,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C17" s="3">
         <v>-76</v>
@@ -8812,10 +8801,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8823,10 +8812,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8834,10 +8823,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8845,10 +8834,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8856,10 +8845,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8867,10 +8856,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -8879,7 +8868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B75E61-DAA5-4C75-9938-082F14D489D1}">
   <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8893,7 +8882,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8904,10 +8893,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8915,10 +8904,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8926,10 +8915,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8937,7 +8926,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C5" s="3">
         <v>1234</v>
@@ -8948,7 +8937,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C6" s="3">
         <v>8967589</v>
@@ -8959,7 +8948,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C7" s="3">
         <v>34567</v>
@@ -8970,7 +8959,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C8" s="3">
         <v>50</v>
@@ -8981,7 +8970,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C9" s="3">
         <v>100</v>
@@ -8992,10 +8981,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9003,7 +8992,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
@@ -9014,10 +9003,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9025,10 +9014,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9036,10 +9025,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9047,10 +9036,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9058,10 +9047,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9069,10 +9058,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9080,10 +9069,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9091,7 +9080,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C19" s="3">
         <v>123</v>
@@ -9102,10 +9091,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9113,10 +9102,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9124,10 +9113,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9135,10 +9124,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9146,10 +9135,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9157,10 +9146,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9168,10 +9157,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9179,10 +9168,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9190,10 +9179,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9201,7 +9190,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C29" s="3">
         <v>75</v>
@@ -9212,7 +9201,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
@@ -9223,7 +9212,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C31" s="3">
         <v>85</v>
@@ -9234,7 +9223,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C32" s="3">
         <v>55</v>
@@ -9245,7 +9234,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>5</v>
@@ -9256,10 +9245,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9267,7 +9256,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -9278,10 +9267,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9289,10 +9278,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9300,10 +9289,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9311,10 +9300,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9322,10 +9311,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9333,10 +9322,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9344,7 +9333,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C42" s="3">
         <v>9869875890</v>
@@ -9355,10 +9344,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9366,7 +9355,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C44" s="3">
         <v>20</v>
@@ -9377,10 +9366,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9388,10 +9377,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9399,10 +9388,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9410,10 +9399,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9421,10 +9410,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9432,7 +9421,7 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C50" s="3">
         <v>9869875890</v>
@@ -9443,7 +9432,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F13134-7D58-41D3-85C8-A2B7688C4794}">
   <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9457,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9468,10 +9457,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9479,10 +9468,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9490,10 +9479,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9501,7 +9490,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C5" s="3">
         <v>50</v>
@@ -9512,7 +9501,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C6" s="3">
         <v>100</v>
@@ -9523,10 +9512,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9534,7 +9523,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C8" s="3">
         <v>123</v>
@@ -9545,10 +9534,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9556,10 +9545,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9567,10 +9556,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9578,10 +9567,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9589,10 +9578,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9600,7 +9589,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C14" s="3">
         <v>12345</v>
@@ -9611,10 +9600,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9622,7 +9611,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C16" s="3">
         <v>123</v>
@@ -9633,10 +9622,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9644,10 +9633,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9655,10 +9644,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9666,10 +9655,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9677,10 +9666,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9688,7 +9677,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C22" s="3">
         <v>12345</v>
@@ -9699,10 +9688,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9710,10 +9699,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9721,10 +9710,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9732,7 +9721,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C26" s="3">
         <v>-75</v>
@@ -9743,7 +9732,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C27" s="3">
         <v>-65</v>
@@ -9754,7 +9743,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C28" s="3">
         <v>-85</v>
@@ -9765,7 +9754,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C29" s="3">
         <v>-55</v>
@@ -9776,10 +9765,10 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9787,7 +9776,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -9798,10 +9787,10 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9809,7 +9798,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C33" s="3">
         <v>20</v>
@@ -9973,10 +9962,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -10006,10 +9995,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>28</v>
+        <v>303</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -10017,10 +10006,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>29</v>
+        <v>304</v>
+      </c>
+      <c r="C7" s="4">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -10068,7 +10057,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -10098,10 +10087,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -10109,10 +10098,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -10125,7 +10114,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10178,10 +10167,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>303</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -10189,10 +10178,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -10203,7 +10192,7 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CC172E-E146-406E-9D54-BE05044B363E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C0E552-0BCF-4018-BDFE-36B169AC4152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="7" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -1448,11 +1448,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1519,7 +1519,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1610,7 +1610,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1719,10 +1719,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="158" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1811,10 +1811,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C922EE-7D55-45ED-84C0-E643E295F423}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1891,10 +1891,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1935,7 +1935,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>75</v>
+        <v>309</v>
       </c>
       <c r="C4" s="3">
         <v>-2</v>
@@ -1946,7 +1946,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>76</v>
+        <v>310</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>20</v>
@@ -1960,10 +1960,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2073,9 +2073,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2233,10 +2233,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2346,10 +2346,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2459,10 +2459,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5CE5DD-3172-4B5D-9DF0-D4E246B7968A}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2771,10 +2771,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2853,9 +2853,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB2637BC-983B-4C46-AEC7-148BA71B263A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2889,10 +2889,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3134,7 +3134,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
@@ -3468,9 +3468,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785359D0-8BDB-4028-AD4B-2C0A4BB56435}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3530,7 +3530,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B546E08-B445-4CFC-AE7C-A360990A58B3}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
@@ -3599,10 +3599,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08315C1-DA1D-48F4-A0A8-4BB13DC3E452}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="125.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="125.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3713,10 +3713,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048DF57C-BB9A-45F0-8668-498DC1298DA0}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4025,10 +4025,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8693D5-27C5-4228-92A0-224F98BEF54A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4271,10 +4271,10 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702E2C7F-ACEF-451E-A257-8D7A1D64246B}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4605,10 +4605,10 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18586F6-6D9E-4DD3-97F2-036CA4FFCAFA}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4905,11 +4905,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4964,10 +4964,10 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5286,9 +5286,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5366,10 +5366,10 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5DAE-E2BF-47B3-A1C9-7C4F12E126E5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5446,10 +5446,10 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF0C752-B8E1-4378-AC7E-8304285A9B90}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5856,10 +5856,10 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E20211-1D84-48FF-8A84-AC0AE11DA487}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6189,10 +6189,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDEAA85-D896-403F-9A59-1E6EC90F5CC2}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6676,10 +6676,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3C73BB-4FB2-4E8F-8651-A6AF93AAD260}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7031,10 +7031,10 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7695C766-C8BF-4FC6-94BA-EF5703D41976}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7541,10 +7541,10 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89650214-A8DD-44FC-9DFA-301D63E80C53}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7665,10 +7665,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE9724B-3165-4EC7-A43C-010FD17B4AF6}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8021,11 +8021,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8080,10 +8080,10 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8490,10 +8490,10 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87CE4365-F4A6-44A6-8070-7113DA611997}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8614,10 +8614,10 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8882,10 +8882,10 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B75E61-DAA5-4C75-9938-082F14D489D1}">
   <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="40.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9446,10 +9446,10 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F13134-7D58-41D3-85C8-A2B7688C4794}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9823,11 +9823,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9882,9 +9882,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9940,7 +9940,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -10001,7 +10001,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" ht="15">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -10012,7 +10012,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" ht="15">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -10032,7 +10032,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -10093,7 +10093,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" ht="15">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" ht="15">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -10123,7 +10123,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C0E552-0BCF-4018-BDFE-36B169AC4152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B752C3-BEB4-4D28-A04C-9ACA13B3673D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="313">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -2770,7 +2770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2813,13 +2813,13 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2827,10 +2827,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2838,9 +2838,20 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B752C3-BEB4-4D28-A04C-9ACA13B3673D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B02E38-DF3D-4005-AF25-7BCAF6612C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="313">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -2770,7 +2770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2813,13 +2813,13 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2827,10 +2827,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2838,20 +2838,9 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BD7993-91EA-4148-B4F9-C14AE5DAF447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5501C066-5786-4AEF-AF55-737044AC0BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="6" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="12" activeTab="15" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="305">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -172,39 +172,15 @@
     <t>Semi-Annually</t>
   </si>
   <si>
-    <t>01/08/2021</t>
-  </si>
-  <si>
-    <t>01/12/2022</t>
-  </si>
-  <si>
-    <t>01/09/2021</t>
-  </si>
-  <si>
     <t>Bi-Monthly</t>
   </si>
   <si>
-    <t>12/01/2021</t>
-  </si>
-  <si>
-    <t>09/01/2023</t>
-  </si>
-  <si>
-    <t>12/01/2024</t>
-  </si>
-  <si>
     <t>Annually</t>
   </si>
   <si>
     <t>Monthly</t>
   </si>
   <si>
-    <t>12/31/2023</t>
-  </si>
-  <si>
-    <t>1/01/2023</t>
-  </si>
-  <si>
     <t>IsFinalReport__c</t>
   </si>
   <si>
@@ -998,6 +974,27 @@
   </si>
   <si>
     <t>InternalOrganization__c</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -1565,10 +1562,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>30</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1576,10 +1573,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>31</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -1626,7 +1623,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1656,10 +1653,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>32</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1667,10 +1664,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>34</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1766,7 +1763,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1777,7 +1774,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -1846,7 +1843,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C5" s="3">
         <v>-2</v>
@@ -1857,7 +1854,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>20</v>
@@ -1915,7 +1912,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C4" s="3">
         <v>-2</v>
@@ -1926,7 +1923,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>20</v>
@@ -1962,10 +1959,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1973,10 +1970,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1984,7 +1981,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1995,7 +1992,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2006,10 +2003,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2017,10 +2014,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2028,10 +2025,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2039,10 +2036,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2075,10 +2072,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2086,7 +2083,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2097,13 +2094,13 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2111,10 +2108,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2122,10 +2119,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2133,10 +2130,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2144,10 +2141,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2155,10 +2152,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2166,10 +2163,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2177,10 +2174,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2188,10 +2185,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -2199,10 +2196,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2235,10 +2232,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2246,10 +2243,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2257,7 +2254,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2268,7 +2265,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2279,10 +2276,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2290,10 +2287,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2301,10 +2298,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2312,10 +2309,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2348,10 +2345,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2359,10 +2356,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2370,7 +2367,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2381,7 +2378,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2392,10 +2389,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2403,10 +2400,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2414,10 +2411,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2425,10 +2422,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2461,7 +2458,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2472,7 +2469,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2483,7 +2480,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2494,7 +2491,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2505,7 +2502,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2516,7 +2513,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2527,7 +2524,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2538,7 +2535,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2549,7 +2546,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2560,10 +2557,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2571,7 +2568,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C12" s="10">
         <v>9999.99</v>
@@ -2582,7 +2579,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -2593,7 +2590,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C14" s="10">
         <v>9999.99</v>
@@ -2604,7 +2601,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C15" s="10">
         <v>1000</v>
@@ -2615,7 +2612,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>5</v>
@@ -2626,10 +2623,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2637,10 +2634,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2648,10 +2645,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2659,7 +2656,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>5</v>
@@ -2670,7 +2667,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>5</v>
@@ -2681,10 +2678,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2692,7 +2689,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2703,10 +2700,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2714,7 +2711,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C25">
         <v>8967045891</v>
@@ -2725,10 +2722,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2736,10 +2733,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2785,7 +2782,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -2855,7 +2852,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2900,7 +2897,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2911,7 +2908,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2922,7 +2919,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2933,7 +2930,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2944,7 +2941,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2955,7 +2952,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2966,7 +2963,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2977,7 +2974,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2988,7 +2985,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2999,7 +2996,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>5</v>
@@ -3010,10 +3007,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3021,10 +3018,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3032,7 +3029,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -3043,7 +3040,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -3054,10 +3051,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3065,7 +3062,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3076,10 +3073,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3087,7 +3084,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C19">
         <v>8967045891</v>
@@ -3098,10 +3095,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3109,10 +3106,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3145,10 +3142,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3156,10 +3153,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3167,10 +3164,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3178,10 +3175,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3189,7 +3186,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -3200,7 +3197,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -3211,7 +3208,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3222,10 +3219,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3233,7 +3230,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3244,10 +3241,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3255,10 +3252,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3266,10 +3263,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3277,10 +3274,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3288,10 +3285,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3299,10 +3296,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3310,10 +3307,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3321,10 +3318,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3332,7 +3329,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3343,10 +3340,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3354,10 +3351,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3365,10 +3362,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3376,10 +3373,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3387,10 +3384,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3398,10 +3395,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3409,10 +3406,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3420,7 +3417,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C27">
         <v>2122342342</v>
@@ -3431,10 +3428,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3442,7 +3439,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3479,10 +3476,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3490,10 +3487,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3501,7 +3498,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C4" s="11">
         <v>50</v>
@@ -3541,7 +3538,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>64789390</v>
@@ -3552,7 +3549,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3563,7 +3560,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3574,7 +3571,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3610,10 +3607,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" t="s">
         <v>147</v>
-      </c>
-      <c r="C2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3621,10 +3618,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3632,10 +3629,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3643,10 +3640,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C5" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3654,7 +3651,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C6" s="3">
         <v>25</v>
@@ -3665,10 +3662,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3676,7 +3673,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C8" s="13">
         <v>9999.99</v>
@@ -3687,10 +3684,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3724,7 +3721,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -3735,7 +3732,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3746,7 +3743,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3757,7 +3754,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3768,7 +3765,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -3779,10 +3776,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C7" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3790,7 +3787,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -3801,7 +3798,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -3812,7 +3809,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -3823,7 +3820,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -3834,10 +3831,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3845,7 +3842,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C13">
         <v>85</v>
@@ -3856,7 +3853,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C14">
         <v>85</v>
@@ -3867,7 +3864,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C15">
         <v>9999.99</v>
@@ -3878,7 +3875,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C16">
         <v>9999.99</v>
@@ -3889,10 +3886,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3900,10 +3897,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3911,10 +3908,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3922,7 +3919,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -3933,7 +3930,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -3944,10 +3941,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3955,7 +3952,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3966,10 +3963,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3977,7 +3974,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C25">
         <v>9867589302</v>
@@ -3988,10 +3985,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3999,10 +3996,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -4036,7 +4033,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -4047,7 +4044,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -4058,7 +4055,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4069,7 +4066,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4080,7 +4077,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -4091,7 +4088,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -4102,7 +4099,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -4113,7 +4110,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -4124,7 +4121,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -4135,10 +4132,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4146,10 +4143,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4157,10 +4154,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4168,7 +4165,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4179,7 +4176,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4190,10 +4187,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4201,7 +4198,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -4212,10 +4209,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4223,7 +4220,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C19">
         <v>9867589302</v>
@@ -4234,10 +4231,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4245,10 +4242,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -4282,10 +4279,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4293,7 +4290,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4304,10 +4301,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4315,7 +4312,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4326,10 +4323,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4337,10 +4334,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4348,10 +4345,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4359,10 +4356,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4370,10 +4367,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4381,10 +4378,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4392,10 +4389,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4403,7 +4400,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4414,7 +4411,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4425,7 +4422,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4436,7 +4433,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -4447,10 +4444,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4458,10 +4455,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4469,10 +4466,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4480,10 +4477,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4491,10 +4488,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4502,10 +4499,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4513,10 +4510,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4524,10 +4521,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4535,10 +4532,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4546,7 +4543,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C26">
         <v>2122342342</v>
@@ -4557,10 +4554,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4568,7 +4565,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4579,10 +4576,10 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4675,10 +4672,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4686,7 +4683,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4697,10 +4694,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4708,7 +4705,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4719,10 +4716,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4730,10 +4727,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4741,10 +4738,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4752,10 +4749,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4763,10 +4760,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4774,10 +4771,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4785,10 +4782,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4796,7 +4793,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4807,10 +4804,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4818,10 +4815,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4829,10 +4826,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4840,10 +4837,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4851,10 +4848,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4862,10 +4859,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4873,10 +4870,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4884,10 +4881,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4895,10 +4892,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4906,7 +4903,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C23">
         <v>2122342342</v>
@@ -4917,10 +4914,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4928,7 +4925,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -4939,10 +4936,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4975,10 +4972,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4986,7 +4983,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4997,10 +4994,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5008,7 +5005,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5019,10 +5016,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5030,10 +5027,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5041,10 +5038,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5052,10 +5049,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5063,10 +5060,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5074,10 +5071,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5085,10 +5082,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5096,7 +5093,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -5107,7 +5104,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -5118,7 +5115,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -5129,7 +5126,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -5140,10 +5137,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5151,10 +5148,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5162,10 +5159,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5173,10 +5170,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5184,10 +5181,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5195,10 +5192,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5206,10 +5203,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5217,10 +5214,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5228,7 +5225,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C25">
         <v>2122342342</v>
@@ -5239,10 +5236,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5250,7 +5247,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5261,10 +5258,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -5297,7 +5294,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -5308,10 +5305,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5319,10 +5316,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5330,7 +5327,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C5">
         <v>1111</v>
@@ -5341,10 +5338,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -5377,10 +5374,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5388,10 +5385,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5399,7 +5396,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C4">
         <v>76578</v>
@@ -5410,7 +5407,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -5421,7 +5418,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -5457,10 +5454,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5468,7 +5465,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5479,10 +5476,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5490,7 +5487,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5501,10 +5498,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5512,10 +5509,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5523,10 +5520,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5534,10 +5531,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5545,10 +5542,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5556,10 +5553,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5567,10 +5564,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5578,10 +5575,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5589,10 +5586,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5600,10 +5597,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5611,10 +5608,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5622,10 +5619,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5633,10 +5630,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5644,7 +5641,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -5655,7 +5652,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C20">
         <v>150</v>
@@ -5666,7 +5663,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
@@ -5677,7 +5674,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
@@ -5688,7 +5685,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -5699,10 +5696,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5710,7 +5707,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -5721,10 +5718,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5732,10 +5729,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5743,10 +5740,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5754,10 +5751,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5765,10 +5762,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5776,10 +5773,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5787,10 +5784,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5798,7 +5795,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C33" s="15">
         <v>2122342342</v>
@@ -5809,10 +5806,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5820,7 +5817,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5831,7 +5828,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -5867,10 +5864,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5878,7 +5875,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5889,10 +5886,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5900,7 +5897,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5911,10 +5908,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5922,10 +5919,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5933,10 +5930,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5944,10 +5941,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5955,10 +5952,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5966,10 +5963,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5977,10 +5974,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5988,10 +5985,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5999,10 +5996,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6010,10 +6007,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6021,10 +6018,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6032,10 +6029,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6043,10 +6040,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6054,7 +6051,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -6065,10 +6062,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6076,10 +6073,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6087,10 +6084,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6098,10 +6095,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6109,10 +6106,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6120,10 +6117,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6131,10 +6128,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6142,7 +6139,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C27" s="15">
         <v>2122342342</v>
@@ -6153,10 +6150,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6164,7 +6161,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6200,7 +6197,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6211,7 +6208,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -6222,7 +6219,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -6233,10 +6230,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6244,10 +6241,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6255,7 +6252,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>123</v>
@@ -6266,10 +6263,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6277,10 +6274,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6288,10 +6285,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6299,10 +6296,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6310,10 +6307,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6321,10 +6318,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6332,10 +6329,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6343,7 +6340,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C15">
         <v>1234</v>
@@ -6354,7 +6351,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C16">
         <v>48</v>
@@ -6365,7 +6362,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C17">
         <v>35</v>
@@ -6376,7 +6373,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -6387,10 +6384,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6398,7 +6395,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -6409,7 +6406,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6420,10 +6417,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6431,7 +6428,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -6442,7 +6439,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C24">
         <v>789</v>
@@ -6453,7 +6450,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -6464,7 +6461,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C26">
         <v>456</v>
@@ -6475,7 +6472,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -6486,10 +6483,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6497,10 +6494,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6508,10 +6505,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6519,10 +6516,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6530,10 +6527,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6541,10 +6538,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6552,10 +6549,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6563,10 +6560,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6574,10 +6571,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6585,7 +6582,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C37">
         <v>10000</v>
@@ -6596,7 +6593,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C38">
         <v>8000</v>
@@ -6607,7 +6604,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C39">
         <v>6000</v>
@@ -6618,7 +6615,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -6629,7 +6626,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C41">
         <v>300</v>
@@ -6640,7 +6637,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -6651,10 +6648,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -6687,7 +6684,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6698,7 +6695,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -6709,10 +6706,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6720,10 +6717,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6731,10 +6728,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6742,10 +6739,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6753,10 +6750,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6764,10 +6761,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6775,7 +6772,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C10" s="12">
         <v>1234</v>
@@ -6786,7 +6783,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C11">
         <v>-8</v>
@@ -6797,7 +6794,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C12">
         <v>-300</v>
@@ -6808,7 +6805,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C13">
         <v>-200</v>
@@ -6819,7 +6816,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -6830,7 +6827,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C15">
         <v>-818</v>
@@ -6841,7 +6838,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C16">
         <v>-8</v>
@@ -6852,7 +6849,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C17">
         <v>-767</v>
@@ -6863,7 +6860,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -6874,10 +6871,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6885,10 +6882,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6896,10 +6893,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6907,10 +6904,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6918,10 +6915,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6929,7 +6926,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C24">
         <v>-1000</v>
@@ -6940,7 +6937,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C25">
         <v>-700</v>
@@ -6951,7 +6948,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C26">
         <v>-500</v>
@@ -6962,7 +6959,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C27">
         <v>-300</v>
@@ -6973,7 +6970,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -6984,7 +6981,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C29">
         <v>-150</v>
@@ -6995,7 +6992,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -7006,7 +7003,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C31">
         <v>-40</v>
@@ -7042,7 +7039,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7053,10 +7050,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7064,7 +7061,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7075,10 +7072,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7086,10 +7083,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7097,10 +7094,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7108,10 +7105,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7119,10 +7116,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7130,10 +7127,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7141,10 +7138,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7152,7 +7149,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -7163,7 +7160,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -7174,7 +7171,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -7185,10 +7182,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7196,7 +7193,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -7207,7 +7204,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -7218,7 +7215,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -7229,10 +7226,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7240,7 +7237,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -7251,7 +7248,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -7262,10 +7259,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7273,7 +7270,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C23">
         <v>789</v>
@@ -7284,7 +7281,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C24">
         <v>86</v>
@@ -7295,7 +7292,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C25">
         <v>456</v>
@@ -7306,7 +7303,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C26">
         <v>74</v>
@@ -7317,10 +7314,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -7328,10 +7325,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7339,10 +7336,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7350,10 +7347,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -7361,10 +7358,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7372,7 +7369,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -7383,7 +7380,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -7394,7 +7391,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -7405,7 +7402,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -7416,7 +7413,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -7427,7 +7424,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -7438,7 +7435,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7449,7 +7446,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -7460,7 +7457,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -7471,10 +7468,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C41" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7482,7 +7479,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C42">
         <v>400</v>
@@ -7493,7 +7490,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7504,7 +7501,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -7515,10 +7512,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C45" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -7552,7 +7549,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7563,7 +7560,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -7574,10 +7571,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7585,10 +7582,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7596,10 +7593,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7607,10 +7604,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7618,10 +7615,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7629,10 +7626,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7640,10 +7637,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -7735,7 +7732,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7746,10 +7743,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7757,7 +7754,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7768,10 +7765,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7779,10 +7776,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7790,10 +7787,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7801,10 +7798,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7812,10 +7809,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7823,10 +7820,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7834,7 +7831,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C11" s="12">
         <v>1234</v>
@@ -7845,7 +7842,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -7856,7 +7853,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C13">
         <v>-466</v>
@@ -7867,7 +7864,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C14">
         <v>-500</v>
@@ -7878,7 +7875,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C15">
         <v>-400</v>
@@ -7889,7 +7886,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C16">
         <v>-789</v>
@@ -7900,7 +7897,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C17">
         <v>-200</v>
@@ -7911,7 +7908,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C18">
         <v>-456</v>
@@ -7922,7 +7919,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C19">
         <v>-74</v>
@@ -7933,10 +7930,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7944,10 +7941,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7955,7 +7952,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C22">
         <v>-400</v>
@@ -7966,7 +7963,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C23">
         <v>-200</v>
@@ -7977,7 +7974,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C24">
         <v>-100</v>
@@ -7988,7 +7985,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C25">
         <v>-200</v>
@@ -7999,7 +7996,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C26">
         <v>-50</v>
@@ -8010,7 +8007,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C27">
         <v>-400</v>
@@ -8021,7 +8018,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C28">
         <v>-200</v>
@@ -8032,7 +8029,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C29">
         <v>-100</v>
@@ -8043,7 +8040,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C30">
         <v>-200</v>
@@ -8054,7 +8051,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -8091,7 +8088,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8102,10 +8099,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8113,7 +8110,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -8124,10 +8121,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8135,10 +8132,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8146,10 +8143,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8157,10 +8154,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8168,10 +8165,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8179,10 +8176,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8190,10 +8187,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8201,7 +8198,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -8212,7 +8209,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -8223,7 +8220,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -8234,7 +8231,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C15">
         <v>500</v>
@@ -8245,10 +8242,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8256,7 +8253,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C17">
         <v>1000</v>
@@ -8267,7 +8264,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C18">
         <v>700</v>
@@ -8278,10 +8275,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8289,10 +8286,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8300,7 +8297,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C21">
         <v>1234</v>
@@ -8311,10 +8308,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C22" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8322,10 +8319,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8333,10 +8330,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8344,7 +8341,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C25">
         <v>300</v>
@@ -8355,7 +8352,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C26">
         <v>85</v>
@@ -8366,7 +8363,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -8377,7 +8374,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C28">
         <v>76</v>
@@ -8388,10 +8385,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8399,10 +8396,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -8410,10 +8407,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C31" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8421,10 +8418,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8432,10 +8429,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8443,7 +8440,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>26</v>
@@ -8454,7 +8451,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>26</v>
@@ -8465,7 +8462,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>26</v>
@@ -8501,7 +8498,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8512,7 +8509,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -8523,10 +8520,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8534,10 +8531,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8545,10 +8542,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8556,10 +8553,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8567,10 +8564,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8578,10 +8575,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8589,10 +8586,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -8625,7 +8622,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C2" s="3">
         <v>1234</v>
@@ -8636,7 +8633,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3">
         <v>123</v>
@@ -8647,10 +8644,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8658,10 +8655,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8669,10 +8666,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8680,10 +8677,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8691,10 +8688,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8702,10 +8699,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8713,7 +8710,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C10" s="15">
         <v>12345</v>
@@ -8724,7 +8721,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C11" s="3">
         <v>-500</v>
@@ -8735,7 +8732,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C12" s="3">
         <v>-1000</v>
@@ -8746,7 +8743,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C13" s="3">
         <v>-700</v>
@@ -8757,7 +8754,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C14" s="3">
         <v>-300</v>
@@ -8768,7 +8765,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C15" s="3">
         <v>-85</v>
@@ -8779,7 +8776,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C16" s="3">
         <v>-200</v>
@@ -8790,7 +8787,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C17" s="3">
         <v>-76</v>
@@ -8801,10 +8798,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8812,10 +8809,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8823,10 +8820,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8834,10 +8831,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8845,10 +8842,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8856,10 +8853,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -8882,7 +8879,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8893,10 +8890,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8904,10 +8901,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8915,10 +8912,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8926,7 +8923,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C5" s="3">
         <v>1234</v>
@@ -8937,7 +8934,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C6" s="3">
         <v>8967589</v>
@@ -8948,7 +8945,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C7" s="3">
         <v>34567</v>
@@ -8959,7 +8956,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C8" s="3">
         <v>50</v>
@@ -8970,7 +8967,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C9" s="3">
         <v>100</v>
@@ -8981,10 +8978,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8992,7 +8989,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
@@ -9003,10 +9000,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9014,10 +9011,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9025,10 +9022,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9036,10 +9033,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9047,10 +9044,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9058,10 +9055,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9069,10 +9066,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9080,7 +9077,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C19" s="3">
         <v>123</v>
@@ -9091,10 +9088,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9102,10 +9099,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9113,10 +9110,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9124,10 +9121,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9135,10 +9132,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9146,10 +9143,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9157,10 +9154,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9168,10 +9165,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9179,10 +9176,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9190,7 +9187,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C29" s="3">
         <v>75</v>
@@ -9201,7 +9198,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
@@ -9212,7 +9209,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C31" s="3">
         <v>85</v>
@@ -9223,7 +9220,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C32" s="3">
         <v>55</v>
@@ -9234,7 +9231,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>5</v>
@@ -9245,10 +9242,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9256,7 +9253,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -9267,10 +9264,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9278,10 +9275,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9289,10 +9286,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9300,10 +9297,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9311,10 +9308,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9322,10 +9319,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9333,7 +9330,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C42" s="3">
         <v>9869875890</v>
@@ -9344,10 +9341,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9355,7 +9352,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C44" s="3">
         <v>20</v>
@@ -9366,10 +9363,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9377,10 +9374,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9388,10 +9385,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9399,10 +9396,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9410,10 +9407,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9421,7 +9418,7 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C50" s="3">
         <v>9869875890</v>
@@ -9446,7 +9443,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9457,10 +9454,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9468,10 +9465,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9479,10 +9476,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9490,7 +9487,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C5" s="3">
         <v>50</v>
@@ -9501,7 +9498,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C6" s="3">
         <v>100</v>
@@ -9512,10 +9509,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9523,7 +9520,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C8" s="3">
         <v>123</v>
@@ -9534,10 +9531,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9545,10 +9542,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9556,10 +9553,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9567,10 +9564,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9578,10 +9575,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9589,7 +9586,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3">
         <v>12345</v>
@@ -9600,10 +9597,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9611,7 +9608,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C16" s="3">
         <v>123</v>
@@ -9622,10 +9619,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9633,10 +9630,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9644,10 +9641,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9655,10 +9652,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9666,10 +9663,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9677,7 +9674,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C22" s="3">
         <v>12345</v>
@@ -9688,10 +9685,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9699,10 +9696,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9710,10 +9707,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9721,7 +9718,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C26" s="3">
         <v>-75</v>
@@ -9732,7 +9729,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C27" s="3">
         <v>-65</v>
@@ -9743,7 +9740,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C28" s="3">
         <v>-85</v>
@@ -9754,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C29" s="3">
         <v>-55</v>
@@ -9765,10 +9762,10 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9776,7 +9773,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -9787,10 +9784,10 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9798,7 +9795,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C33" s="3">
         <v>20</v>
@@ -9995,7 +9992,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
@@ -10006,7 +10003,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C7" s="4">
         <v>365</v>
@@ -10023,7 +10020,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10057,7 +10054,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -10087,10 +10084,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>40</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -10098,10 +10095,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>39</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -10167,10 +10164,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>35</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -10178,10 +10175,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>36</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -10192,7 +10189,7 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D775C669-45A3-44A9-86E8-573819BF62BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10821544-74DF-440E-93F7-27DB01B8CBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="39" activeTab="17" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="40" activeTab="43" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="302">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1415,11 +1415,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1577,7 +1577,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1686,10 +1686,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="158" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1778,10 +1778,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C922EE-7D55-45ED-84C0-E643E295F423}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1858,10 +1858,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1927,10 +1927,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2040,9 +2040,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2200,10 +2200,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2313,10 +2313,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2426,10 +2426,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5CE5DD-3172-4B5D-9DF0-D4E246B7968A}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2738,10 +2738,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2820,9 +2820,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB2637BC-983B-4C46-AEC7-148BA71B263A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2856,10 +2856,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3101,7 +3101,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
@@ -3435,9 +3435,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785359D0-8BDB-4028-AD4B-2C0A4BB56435}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3497,7 +3497,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B546E08-B445-4CFC-AE7C-A360990A58B3}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
@@ -3566,10 +3566,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08315C1-DA1D-48F4-A0A8-4BB13DC3E452}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="125.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="125.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3680,10 +3680,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048DF57C-BB9A-45F0-8668-498DC1298DA0}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3992,10 +3992,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8693D5-27C5-4228-92A0-224F98BEF54A}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4238,10 +4238,10 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702E2C7F-ACEF-451E-A257-8D7A1D64246B}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4572,10 +4572,10 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18586F6-6D9E-4DD3-97F2-036CA4FFCAFA}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4872,11 +4872,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4931,10 +4931,10 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5253,9 +5253,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5333,10 +5333,10 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5DAE-E2BF-47B3-A1C9-7C4F12E126E5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5413,10 +5413,10 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF0C752-B8E1-4378-AC7E-8304285A9B90}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5823,10 +5823,10 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E20211-1D84-48FF-8A84-AC0AE11DA487}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6157,10 +6157,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDEAA85-D896-403F-9A59-1E6EC90F5CC2}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="44.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6644,10 +6644,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3C73BB-4FB2-4E8F-8651-A6AF93AAD260}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6999,10 +6999,10 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7695C766-C8BF-4FC6-94BA-EF5703D41976}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7509,10 +7509,10 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89650214-A8DD-44FC-9DFA-301D63E80C53}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7633,10 +7633,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE9724B-3165-4EC7-A43C-010FD17B4AF6}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7989,11 +7989,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8048,10 +8048,10 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8458,10 +8458,10 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87CE4365-F4A6-44A6-8070-7113DA611997}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8582,10 +8582,10 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8849,11 +8849,11 @@
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B75E61-DAA5-4C75-9938-082F14D489D1}">
-  <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="40.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.08984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9048,10 +9048,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>280</v>
+        <v>162</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9059,10 +9059,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C19" s="3">
-        <v>123</v>
+        <v>280</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9070,10 +9070,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>107</v>
+        <v>281</v>
+      </c>
+      <c r="C20" s="3">
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9081,10 +9081,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9092,7 +9092,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>68</v>
@@ -9103,10 +9103,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C23" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9114,10 +9114,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>68</v>
+        <v>285</v>
+      </c>
+      <c r="C24" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9125,10 +9125,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9136,10 +9136,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9147,10 +9147,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9158,10 +9158,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9169,10 +9169,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="C29" s="3">
-        <v>75</v>
+        <v>290</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -9180,10 +9180,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C30" s="3">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9191,10 +9191,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C31" s="3">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -9202,10 +9202,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C32" s="3">
-        <v>55</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9213,10 +9213,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>5</v>
+        <v>294</v>
+      </c>
+      <c r="C33" s="3">
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -9224,10 +9224,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>111</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9235,10 +9235,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C35" s="3">
-        <v>0</v>
+        <v>172</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -9246,10 +9246,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>71</v>
+        <v>174</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9257,10 +9257,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9268,10 +9268,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9279,10 +9279,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9290,10 +9290,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9301,10 +9301,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9312,10 +9312,10 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C42" s="3">
-        <v>9869875890</v>
+        <v>171</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -9323,10 +9323,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>114</v>
+        <v>173</v>
+      </c>
+      <c r="C43" s="3">
+        <v>9869875890</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9334,10 +9334,10 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C44" s="3">
-        <v>20</v>
+        <v>295</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -9345,10 +9345,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>71</v>
+        <v>154</v>
+      </c>
+      <c r="C45" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9356,10 +9356,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9367,10 +9367,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9378,10 +9378,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9389,10 +9389,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9400,9 +9400,20 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C51" s="3">
         <v>9869875890</v>
       </c>
     </row>
@@ -9413,11 +9424,11 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F13134-7D58-41D3-85C8-A2B7688C4794}">
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9578,11 +9589,11 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>280</v>
+      <c r="B15" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9590,10 +9601,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>281</v>
-      </c>
-      <c r="C16" s="3">
-        <v>123</v>
+        <v>280</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9601,10 +9612,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>282</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>107</v>
+        <v>281</v>
+      </c>
+      <c r="C17" s="3">
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9612,10 +9623,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9623,7 +9634,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>68</v>
@@ -9634,10 +9645,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>285</v>
-      </c>
-      <c r="C20" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9645,10 +9656,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>286</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>68</v>
+        <v>285</v>
+      </c>
+      <c r="C21" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9656,10 +9667,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>287</v>
-      </c>
-      <c r="C22" s="3">
-        <v>12345</v>
+        <v>286</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9667,10 +9678,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>288</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>108</v>
+        <v>287</v>
+      </c>
+      <c r="C23" s="3">
+        <v>12345</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9678,10 +9689,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9689,10 +9700,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9700,10 +9711,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>291</v>
-      </c>
-      <c r="C26" s="3">
-        <v>-75</v>
+        <v>290</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9711,10 +9722,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C27" s="3">
-        <v>-65</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9722,10 +9733,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C28" s="3">
-        <v>-85</v>
+        <v>-65</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9733,10 +9744,10 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C29" s="3">
-        <v>-55</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -9744,10 +9755,10 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>111</v>
+        <v>294</v>
+      </c>
+      <c r="C30" s="3">
+        <v>-55</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9755,10 +9766,10 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>174</v>
-      </c>
-      <c r="C31" s="3">
-        <v>0</v>
+        <v>172</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -9766,10 +9777,10 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>295</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>114</v>
+        <v>174</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9777,9 +9788,20 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
+        <v>295</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" t="s">
         <v>154</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C34" s="3">
         <v>20</v>
       </c>
     </row>
@@ -9791,11 +9813,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9850,9 +9872,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9908,7 +9930,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -9969,7 +9991,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15">
+    <row r="6" spans="1:3" ht="16">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9980,7 +10002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15">
+    <row r="7" spans="1:3" ht="16">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -10000,7 +10022,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -10061,7 +10083,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15">
+    <row r="6" spans="1:3" ht="16">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -10072,7 +10094,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15">
+    <row r="7" spans="1:3" ht="16">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -10091,7 +10113,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10821544-74DF-440E-93F7-27DB01B8CBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7D0FD7-3549-440E-A400-4337A0B30842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="40" activeTab="43" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D775C669-45A3-44A9-86E8-573819BF62BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A39F3E-B527-439F-8A23-F11328BF2F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="39" activeTab="17" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\ProductClassic\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B29898-1937-483A-AD2F-AC155DB4E0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C05C2F-1316-47EE-B34A-33C5C3065C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="10" activeTab="12" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="6" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="307">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -157,12 +157,6 @@
   </si>
   <si>
     <t>Calendar</t>
-  </si>
-  <si>
-    <t>08/25/2023</t>
-  </si>
-  <si>
-    <t>08/25/2024</t>
   </si>
   <si>
     <t>Quarterly</t>
@@ -1126,9 +1120,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1166,7 +1160,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1272,7 +1266,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1414,7 +1408,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1530,7 +1524,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1560,10 +1554,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1571,10 +1565,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1621,7 +1615,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1651,10 +1645,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1662,10 +1656,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1761,7 +1755,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C6" s="3">
         <v>-2</v>
@@ -1772,7 +1766,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -1841,7 +1835,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C5" s="3">
         <v>-2</v>
@@ -1852,7 +1846,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>20</v>
@@ -1910,7 +1904,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C4" s="3">
         <v>-2</v>
@@ -1921,7 +1915,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>20</v>
@@ -1957,10 +1951,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1968,10 +1962,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1979,7 +1973,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1990,7 +1984,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2001,10 +1995,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2012,10 +2006,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2023,10 +2017,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2034,10 +2028,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2070,10 +2064,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2081,7 +2075,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2092,13 +2086,13 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2106,10 +2100,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2117,10 +2111,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2128,10 +2122,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2139,10 +2133,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2150,10 +2144,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2161,10 +2155,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2172,10 +2166,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2183,10 +2177,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -2194,10 +2188,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2230,10 +2224,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2241,10 +2235,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2252,7 +2246,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2263,7 +2257,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2274,10 +2268,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2285,10 +2279,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2296,10 +2290,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2307,10 +2301,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2343,10 +2337,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2354,10 +2348,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2365,7 +2359,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2376,7 +2370,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2387,10 +2381,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2398,10 +2392,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2409,10 +2403,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2420,10 +2414,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2456,7 +2450,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2467,7 +2461,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2478,7 +2472,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2489,7 +2483,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2500,7 +2494,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2511,7 +2505,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2522,7 +2516,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2533,7 +2527,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2544,7 +2538,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2555,10 +2549,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2566,7 +2560,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C12" s="10">
         <v>9999.99</v>
@@ -2577,7 +2571,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -2588,7 +2582,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C14" s="10">
         <v>9999.99</v>
@@ -2599,7 +2593,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C15" s="10">
         <v>1000</v>
@@ -2610,7 +2604,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>5</v>
@@ -2621,10 +2615,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2632,10 +2626,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2643,10 +2637,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2654,7 +2648,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>5</v>
@@ -2665,7 +2659,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>5</v>
@@ -2676,10 +2670,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2687,7 +2681,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2698,10 +2692,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2709,7 +2703,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C25">
         <v>8967045891</v>
@@ -2720,10 +2714,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2731,10 +2725,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2780,7 +2774,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -2850,7 +2844,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2886,7 +2880,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>1567838</v>
@@ -2897,7 +2891,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
@@ -2908,7 +2902,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
@@ -2919,7 +2913,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
@@ -2930,7 +2924,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
@@ -2941,7 +2935,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
@@ -2952,7 +2946,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>5</v>
@@ -2963,7 +2957,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>5</v>
@@ -2974,7 +2968,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>5</v>
@@ -2985,7 +2979,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>5</v>
@@ -2996,10 +2990,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3007,10 +3001,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3018,7 +3012,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -3029,7 +3023,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -3040,10 +3034,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3051,7 +3045,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3062,10 +3056,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3073,7 +3067,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C19">
         <v>8967045891</v>
@@ -3084,10 +3078,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3095,10 +3089,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -3131,10 +3125,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3142,10 +3136,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3153,10 +3147,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3164,10 +3158,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3175,7 +3169,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -3186,7 +3180,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -3197,7 +3191,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -3208,10 +3202,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3219,7 +3213,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3230,10 +3224,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3241,10 +3235,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3252,10 +3246,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3263,10 +3257,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3274,10 +3268,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3285,10 +3279,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3296,10 +3290,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3307,10 +3301,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3318,7 +3312,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3329,10 +3323,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3340,10 +3334,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3351,10 +3345,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3362,10 +3356,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3373,10 +3367,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3384,10 +3378,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3395,10 +3389,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3406,7 +3400,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C27">
         <v>2122342342</v>
@@ -3417,10 +3411,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3428,7 +3422,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3465,10 +3459,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3476,10 +3470,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3487,7 +3481,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C4" s="11">
         <v>50</v>
@@ -3527,7 +3521,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>64789390</v>
@@ -3538,7 +3532,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3549,7 +3543,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3560,7 +3554,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3596,10 +3590,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3607,10 +3601,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3618,10 +3612,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3629,10 +3623,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3640,7 +3634,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C6" s="3">
         <v>25</v>
@@ -3651,10 +3645,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3662,7 +3656,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C8" s="13">
         <v>9999.99</v>
@@ -3673,10 +3667,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -3710,7 +3704,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -3721,7 +3715,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -3732,7 +3726,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -3743,7 +3737,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -3754,7 +3748,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -3765,10 +3759,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3776,7 +3770,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -3787,7 +3781,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -3798,7 +3792,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -3809,7 +3803,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -3820,10 +3814,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3831,7 +3825,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C13">
         <v>85</v>
@@ -3842,7 +3836,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C14">
         <v>85</v>
@@ -3853,7 +3847,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C15">
         <v>9999.99</v>
@@ -3864,7 +3858,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C16">
         <v>9999.99</v>
@@ -3875,10 +3869,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3886,10 +3880,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3897,10 +3891,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3908,7 +3902,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -3919,7 +3913,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -3930,10 +3924,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3941,7 +3935,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3952,10 +3946,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3963,7 +3957,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C25">
         <v>9867589302</v>
@@ -3974,10 +3968,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3985,10 +3979,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -4022,7 +4016,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -4033,7 +4027,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -4044,7 +4038,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -4055,7 +4049,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -4066,7 +4060,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -4077,7 +4071,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -4088,7 +4082,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -4099,7 +4093,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -4110,7 +4104,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -4121,10 +4115,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4132,10 +4126,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4143,10 +4137,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4154,7 +4148,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4165,7 +4159,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4176,10 +4170,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4187,7 +4181,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -4198,10 +4192,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4209,7 +4203,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C19">
         <v>9867589302</v>
@@ -4220,10 +4214,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4231,10 +4225,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -4268,10 +4262,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4279,7 +4273,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4290,10 +4284,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4301,7 +4295,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4312,10 +4306,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4323,10 +4317,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4334,10 +4328,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4345,10 +4339,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4356,10 +4350,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4367,10 +4361,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4378,10 +4372,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4389,7 +4383,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4400,7 +4394,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -4411,7 +4405,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -4422,7 +4416,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -4433,10 +4427,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4444,10 +4438,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4455,10 +4449,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4466,10 +4460,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C20" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4477,10 +4471,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4488,10 +4482,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4499,10 +4493,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4510,10 +4504,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4521,10 +4515,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4532,7 +4526,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C26">
         <v>2122342342</v>
@@ -4543,10 +4537,10 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4554,7 +4548,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4565,10 +4559,10 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4602,10 +4596,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4613,7 +4607,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4624,10 +4618,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4635,7 +4629,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4646,10 +4640,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4657,10 +4651,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4668,10 +4662,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4679,10 +4673,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4690,10 +4684,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4701,10 +4695,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4712,10 +4706,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4723,7 +4717,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -4734,10 +4728,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4745,10 +4739,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4756,10 +4750,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4767,10 +4761,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4778,10 +4772,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4789,10 +4783,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4800,10 +4794,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4811,10 +4805,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4822,10 +4816,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4833,7 +4827,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C23">
         <v>2122342342</v>
@@ -4844,10 +4838,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4855,7 +4849,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -4866,10 +4860,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4961,10 +4955,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4972,7 +4966,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C3">
         <v>1234</v>
@@ -4983,10 +4977,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4994,7 +4988,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5005,10 +4999,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5016,10 +5010,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5027,10 +5021,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5038,10 +5032,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5049,10 +5043,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5060,10 +5054,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5071,10 +5065,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5082,7 +5076,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C13">
         <v>1111</v>
@@ -5093,7 +5087,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -5104,7 +5098,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -5115,7 +5109,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -5126,10 +5120,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5137,10 +5131,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5148,10 +5142,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5159,10 +5153,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5170,10 +5164,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5181,10 +5175,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5192,10 +5186,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5203,10 +5197,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5214,7 +5208,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C25">
         <v>2122342342</v>
@@ -5225,10 +5219,10 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5236,7 +5230,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5247,10 +5241,10 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5283,7 +5277,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -5294,10 +5288,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5305,10 +5299,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5316,7 +5310,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C5">
         <v>1111</v>
@@ -5327,10 +5321,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5363,10 +5357,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5374,10 +5368,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5385,7 +5379,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C4">
         <v>76578</v>
@@ -5396,7 +5390,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -5407,7 +5401,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -5443,10 +5437,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5454,7 +5448,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5465,10 +5459,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5476,7 +5470,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5487,10 +5481,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5498,10 +5492,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5509,10 +5503,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5520,10 +5514,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5531,10 +5525,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5542,10 +5536,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5553,10 +5547,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5564,10 +5558,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5575,10 +5569,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5586,10 +5580,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5597,10 +5591,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5608,10 +5602,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5619,10 +5613,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5630,7 +5624,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -5641,7 +5635,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C20">
         <v>150</v>
@@ -5652,7 +5646,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>5</v>
@@ -5663,7 +5657,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>5</v>
@@ -5674,7 +5668,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -5685,10 +5679,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5696,7 +5690,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>5</v>
@@ -5707,10 +5701,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5718,10 +5712,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5729,10 +5723,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5740,10 +5734,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5751,10 +5745,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5762,10 +5756,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5773,10 +5767,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5784,7 +5778,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C33" s="15">
         <v>2122342342</v>
@@ -5795,10 +5789,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5806,7 +5800,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5817,7 +5811,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -5853,10 +5847,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5864,7 +5858,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C3" s="12">
         <v>1234</v>
@@ -5875,10 +5869,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5886,7 +5880,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C5" s="12">
         <v>123</v>
@@ -5897,10 +5891,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5908,10 +5902,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5919,10 +5913,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5930,10 +5924,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5941,10 +5935,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5952,10 +5946,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5963,10 +5957,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5974,10 +5968,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5985,10 +5979,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5996,10 +5990,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6007,10 +6001,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6018,10 +6012,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6029,10 +6023,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6040,7 +6034,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C19" s="15">
         <v>2122342342</v>
@@ -6051,10 +6045,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6062,10 +6056,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6073,10 +6067,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6084,10 +6078,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6095,10 +6089,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6106,10 +6100,10 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6117,10 +6111,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6128,7 +6122,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C27" s="15">
         <v>2122342342</v>
@@ -6139,10 +6133,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6150,7 +6144,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6186,7 +6180,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6197,7 +6191,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -6208,7 +6202,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C4">
         <v>150</v>
@@ -6219,10 +6213,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6230,10 +6224,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6241,7 +6235,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C7">
         <v>123</v>
@@ -6252,10 +6246,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6263,10 +6257,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6274,10 +6268,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6285,10 +6279,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6296,10 +6290,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6307,10 +6301,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6318,10 +6312,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6329,7 +6323,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C15">
         <v>1234</v>
@@ -6340,7 +6334,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C16">
         <v>48</v>
@@ -6351,7 +6345,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C17">
         <v>35</v>
@@ -6362,7 +6356,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -6373,10 +6367,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6384,7 +6378,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -6395,7 +6389,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6406,10 +6400,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6417,7 +6411,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -6428,7 +6422,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C24">
         <v>789</v>
@@ -6439,7 +6433,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -6450,7 +6444,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C26">
         <v>456</v>
@@ -6461,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -6472,10 +6466,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6483,10 +6477,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6494,10 +6488,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6505,10 +6499,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6516,10 +6510,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6527,10 +6521,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6538,10 +6532,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6549,10 +6543,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6560,10 +6554,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6571,7 +6565,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C37">
         <v>10000</v>
@@ -6582,7 +6576,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C38">
         <v>8000</v>
@@ -6593,7 +6587,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C39">
         <v>6000</v>
@@ -6604,7 +6598,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -6615,7 +6609,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C41">
         <v>300</v>
@@ -6626,7 +6620,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -6637,10 +6631,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -6673,7 +6667,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -6684,7 +6678,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -6695,10 +6689,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6706,10 +6700,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6717,10 +6711,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6728,10 +6722,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6739,10 +6733,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6750,10 +6744,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6761,7 +6755,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C10" s="12">
         <v>1234</v>
@@ -6772,7 +6766,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C11">
         <v>-8</v>
@@ -6783,7 +6777,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C12">
         <v>-300</v>
@@ -6794,7 +6788,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C13">
         <v>-200</v>
@@ -6805,7 +6799,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -6816,7 +6810,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C15">
         <v>-818</v>
@@ -6827,7 +6821,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C16">
         <v>-8</v>
@@ -6838,7 +6832,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C17">
         <v>-767</v>
@@ -6849,7 +6843,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -6860,10 +6854,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6871,10 +6865,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6882,10 +6876,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6893,10 +6887,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6904,10 +6898,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6915,7 +6909,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24">
         <v>-1000</v>
@@ -6926,7 +6920,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C25">
         <v>-700</v>
@@ -6937,7 +6931,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C26">
         <v>-500</v>
@@ -6948,7 +6942,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C27">
         <v>-300</v>
@@ -6959,7 +6953,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -6970,7 +6964,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C29">
         <v>-150</v>
@@ -6981,7 +6975,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -6992,7 +6986,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C31">
         <v>-40</v>
@@ -7028,7 +7022,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7039,10 +7033,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7050,7 +7044,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7061,10 +7055,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7072,10 +7066,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7083,10 +7077,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7094,10 +7088,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7105,10 +7099,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7116,10 +7110,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7127,10 +7121,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7138,7 +7132,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C12">
         <v>1234</v>
@@ -7149,7 +7143,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C13">
         <v>48</v>
@@ -7160,7 +7154,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C14">
         <v>35</v>
@@ -7171,10 +7165,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7182,7 +7176,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -7193,7 +7187,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -7204,7 +7198,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C18">
         <v>466</v>
@@ -7215,10 +7209,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7226,7 +7220,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -7237,7 +7231,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -7248,10 +7242,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7259,7 +7253,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C23">
         <v>789</v>
@@ -7270,7 +7264,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C24">
         <v>86</v>
@@ -7281,7 +7275,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C25">
         <v>456</v>
@@ -7292,7 +7286,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C26">
         <v>74</v>
@@ -7303,10 +7297,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -7314,10 +7308,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7325,10 +7319,10 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7336,10 +7330,10 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -7347,10 +7341,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7358,7 +7352,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -7369,7 +7363,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -7380,7 +7374,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -7391,7 +7385,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -7402,7 +7396,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -7413,7 +7407,7 @@
         <v>14</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -7424,7 +7418,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -7435,7 +7429,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -7446,7 +7440,7 @@
         <v>14</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -7457,10 +7451,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C41" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7468,7 +7462,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C42">
         <v>400</v>
@@ -7479,7 +7473,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7490,7 +7484,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -7501,10 +7495,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -7538,7 +7532,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7549,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -7560,10 +7554,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7571,10 +7565,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7582,10 +7576,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7593,10 +7587,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7604,10 +7598,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7615,10 +7609,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7626,10 +7620,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -7662,7 +7656,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -7673,10 +7667,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7684,7 +7678,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -7695,10 +7689,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7706,10 +7700,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7717,10 +7711,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7728,10 +7722,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7739,10 +7733,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7750,10 +7744,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7761,7 +7755,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C11" s="12">
         <v>1234</v>
@@ -7772,7 +7766,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -7783,7 +7777,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C13">
         <v>-466</v>
@@ -7794,7 +7788,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C14">
         <v>-500</v>
@@ -7805,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C15">
         <v>-400</v>
@@ -7816,7 +7810,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C16">
         <v>-789</v>
@@ -7827,7 +7821,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C17">
         <v>-200</v>
@@ -7838,7 +7832,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C18">
         <v>-456</v>
@@ -7849,7 +7843,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C19">
         <v>-74</v>
@@ -7860,10 +7854,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7871,10 +7865,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7882,7 +7876,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C22">
         <v>-400</v>
@@ -7893,7 +7887,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C23">
         <v>-200</v>
@@ -7904,7 +7898,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C24">
         <v>-100</v>
@@ -7915,7 +7909,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C25">
         <v>-200</v>
@@ -7926,7 +7920,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C26">
         <v>-50</v>
@@ -7937,7 +7931,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C27">
         <v>-400</v>
@@ -7948,7 +7942,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C28">
         <v>-200</v>
@@ -7959,7 +7953,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C29">
         <v>-100</v>
@@ -7970,7 +7964,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C30">
         <v>-200</v>
@@ -7981,7 +7975,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -8077,7 +8071,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C2">
         <v>1234</v>
@@ -8088,10 +8082,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8099,7 +8093,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C4">
         <v>123</v>
@@ -8110,10 +8104,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8121,10 +8115,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8132,10 +8126,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8143,10 +8137,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8154,10 +8148,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row 